--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R64"/>
+  <dimension ref="A1:R106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3761,6 +3761,2088 @@
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>RACE</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Ferrari N.V.</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>368.34</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>90</v>
+      </c>
+      <c r="I65" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>224.97</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>87</v>
+      </c>
+      <c r="I66" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>341.65</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>86</v>
+      </c>
+      <c r="I67" t="n">
+        <v>18</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DSGX</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>The Descartes Systems Group Inc.</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>79</v>
+      </c>
+      <c r="I68" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>USLM</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>United States Lime &amp; Minerals, Inc.</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>101.76</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>90</v>
+      </c>
+      <c r="I69" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>QLYS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Qualys, Inc.</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>128.32</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>90</v>
+      </c>
+      <c r="I70" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Autodesk, Inc.</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>195.24</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>90</v>
+      </c>
+      <c r="I71" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DXCM</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DexCom, Inc.</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>69.98</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>90</v>
+      </c>
+      <c r="I72" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>RMD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ResMed Inc.</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>198.43</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>90</v>
+      </c>
+      <c r="I73" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PAYC</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Paycom Software, Inc.</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>127.18</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>90</v>
+      </c>
+      <c r="I74" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Adobe Inc.</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>206.43</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>90</v>
+      </c>
+      <c r="I75" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>KNSL</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Kinsale Capital Group, Inc.</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>332.02</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>90</v>
+      </c>
+      <c r="I76" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>NTES</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NetEase, Inc.</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>129.16</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>87</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>International Business Machines Corporation</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>278</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>87</v>
+      </c>
+      <c r="I78" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>WTKWY</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Wolters Kluwer N.V.</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>64.95</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>87</v>
+      </c>
+      <c r="I79" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>PayPal Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>44.38</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>87</v>
+      </c>
+      <c r="I80" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DECK</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Deckers Outdoor Corporation</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>101.28</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>86</v>
+      </c>
+      <c r="I81" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Mastercard Incorporated</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>509.64</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>86</v>
+      </c>
+      <c r="I82" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NextEra Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>88.66</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>86</v>
+      </c>
+      <c r="I83" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>105.73</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>86</v>
+      </c>
+      <c r="I84" t="n">
+        <v>11</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>266.4</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>86</v>
+      </c>
+      <c r="I85" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Novo Nordisk A/S</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>86</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>PDD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>PDD Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>76.54000000000001</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>86</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CYATY</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Contemporary Amperex Technology Co., Limited</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>86</v>
+      </c>
+      <c r="I88" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>PRDO</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Perdoceo Education Corporation</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>83</v>
+      </c>
+      <c r="I89" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>HIG</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>The Hartford Insurance Group, Inc.</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>133.49</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>83</v>
+      </c>
+      <c r="I90" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>UHS</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Universal Health Services, Inc.</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>147.02</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>83</v>
+      </c>
+      <c r="I91" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MELI</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>MercadoLibre, Inc.</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1683.13</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>82</v>
+      </c>
+      <c r="I92" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ServiceNow, Inc.</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>82</v>
+      </c>
+      <c r="I93" t="n">
+        <v>11</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ACGL</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Arch Capital Group Ltd.</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>98.06</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>82</v>
+      </c>
+      <c r="I94" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Salesforce, Inc.</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>82</v>
+      </c>
+      <c r="I95" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TMUS</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>T-Mobile US, Inc.</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>173.97</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>79</v>
+      </c>
+      <c r="I96" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Broadridge Financial Solutions, Inc.</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>135.44</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>79</v>
+      </c>
+      <c r="I97" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TRAK</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ReposiTrak, Inc.</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>79</v>
+      </c>
+      <c r="I98" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NICE</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NICE Ltd.</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>78</v>
+      </c>
+      <c r="I99" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>KOF</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Coca-Cola FEMSA, S.A.B. de C.V.</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>107.37</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>78</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>NFG</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>National Fuel Gas Company</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>78.58</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>71</v>
+      </c>
+      <c r="I101" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>GSK</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>GSK plc</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>52.81</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>71</v>
+      </c>
+      <c r="I102" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>WES</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Western Midstream Partners, LP</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>43.39</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>67</v>
+      </c>
+      <c r="I103" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>BABA</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Alibaba Group Holding Limited</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>58</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>(不在總表)</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="n">
+        <v>5</v>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>UAN</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>CVR Partners, LP</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>112.41</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>67</v>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R106"/>
+  <dimension ref="A1:R107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5843,6 +5843,56 @@
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>4635</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>65</v>
+      </c>
+      <c r="I107" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R107"/>
+  <dimension ref="A1:R110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5893,6 +5893,144 @@
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>134</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>78</v>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>全友</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>75</v>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>407</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>62</v>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R110"/>
+  <dimension ref="A1:R171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6031,6 +6031,3030 @@
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>97</v>
+      </c>
+      <c r="I111" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>516</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>96</v>
+      </c>
+      <c r="I112" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>123</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>91</v>
+      </c>
+      <c r="I113" t="n">
+        <v>15</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>360</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>90</v>
+      </c>
+      <c r="I114" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>87</v>
+      </c>
+      <c r="I115" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>147</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>77</v>
+      </c>
+      <c r="I116" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>237</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>77</v>
+      </c>
+      <c r="I117" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1185</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>76</v>
+      </c>
+      <c r="I118" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>68</v>
+      </c>
+      <c r="I119" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>2450</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>100</v>
+      </c>
+      <c r="I120" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>883</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>100</v>
+      </c>
+      <c r="I121" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>2440</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>100</v>
+      </c>
+      <c r="I122" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>103</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>97</v>
+      </c>
+      <c r="I123" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>123</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>94</v>
+      </c>
+      <c r="I124" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>94</v>
+      </c>
+      <c r="I125" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>94</v>
+      </c>
+      <c r="I126" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>94</v>
+      </c>
+      <c r="I127" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>92</v>
+      </c>
+      <c r="I128" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>1175</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>90</v>
+      </c>
+      <c r="I129" t="n">
+        <v>25</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>475.5</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>90</v>
+      </c>
+      <c r="I130" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>144</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>90</v>
+      </c>
+      <c r="I131" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>84</v>
+      </c>
+      <c r="I132" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>2455</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>80</v>
+      </c>
+      <c r="I133" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>970</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>80</v>
+      </c>
+      <c r="I134" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>79</v>
+      </c>
+      <c r="I135" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>78</v>
+      </c>
+      <c r="I136" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>77</v>
+      </c>
+      <c r="I137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>373</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>65</v>
+      </c>
+      <c r="I138" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>62</v>
+      </c>
+      <c r="I139" t="n">
+        <v>10</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>60</v>
+      </c>
+      <c r="I140" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>79</v>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>404</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>77</v>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>77</v>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>69</v>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ASML Holding N.V.</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>1769.32</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>86</v>
+      </c>
+      <c r="I145" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J145" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>LIN</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Linde plc</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>546.64</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>83</v>
+      </c>
+      <c r="I146" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J146" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Ecolab Inc.</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>283.36</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>83</v>
+      </c>
+      <c r="I147" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="J147" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Walmart Inc.</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>111.84</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>71</v>
+      </c>
+      <c r="I148" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="J148" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ANET</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Arista Networks, Inc.</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>90</v>
+      </c>
+      <c r="I149" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>434.16</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>90</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>90</v>
+      </c>
+      <c r="I151" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>390.49</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>90</v>
+      </c>
+      <c r="I152" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>WPM</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Wheaton Precious Metals Corp.</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>115.73</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>90</v>
+      </c>
+      <c r="I153" t="n">
+        <v>22</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>IDCC</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>InterDigital, Inc.</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>281.4</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>90</v>
+      </c>
+      <c r="I154" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>582.9</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>90</v>
+      </c>
+      <c r="I155" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>NBIX</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Neurocrine Biosciences, Inc.</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>174.26</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>90</v>
+      </c>
+      <c r="I156" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>360.45</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>86</v>
+      </c>
+      <c r="I157" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>HWM</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Howmet Aerospace Inc.</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>270.41</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>86</v>
+      </c>
+      <c r="I158" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>APH</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Amphenol Corporation</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>164.59</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>86</v>
+      </c>
+      <c r="I159" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>EXEL</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Exelixis, Inc.</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>86</v>
+      </c>
+      <c r="I160" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AXP</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>American Express Company</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>351.96</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>82</v>
+      </c>
+      <c r="I161" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>194.83</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>80</v>
+      </c>
+      <c r="I162" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Eli Lilly and Company</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>1210.5</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>80</v>
+      </c>
+      <c r="I163" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>80</v>
+      </c>
+      <c r="I164" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>AMG</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Affiliated Managers Group, Inc.</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>344.6</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>71</v>
+      </c>
+      <c r="I165" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>AER</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>AerCap Holdings N.V.</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>147.84</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>70</v>
+      </c>
+      <c r="I166" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Micron Technology, Inc.</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>975.5599999999999</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>67</v>
+      </c>
+      <c r="I167" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>First Solar, Inc.</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>224.57</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>66</v>
+      </c>
+      <c r="I168" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>CLS</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Celestica Inc.</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>336.21</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>64</v>
+      </c>
+      <c r="I169" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>62</v>
+      </c>
+      <c r="I170" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>517.8200000000001</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>59</v>
+      </c>
+      <c r="I171" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R171"/>
+  <dimension ref="A1:R172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9055,6 +9055,56 @@
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>5050</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>65</v>
+      </c>
+      <c r="I172" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R172"/>
+  <dimension ref="A1:R206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9105,6 +9105,1690 @@
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>157</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>97</v>
+      </c>
+      <c r="I173" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J173" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>556</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>96</v>
+      </c>
+      <c r="I174" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J174" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>91</v>
+      </c>
+      <c r="I175" t="n">
+        <v>15</v>
+      </c>
+      <c r="J175" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>334.5</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>90</v>
+      </c>
+      <c r="I176" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J176" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>87</v>
+      </c>
+      <c r="I177" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J177" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>158</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>77</v>
+      </c>
+      <c r="I178" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J178" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>239</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>77</v>
+      </c>
+      <c r="I179" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J179" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>1105</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>76</v>
+      </c>
+      <c r="I180" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J180" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>68</v>
+      </c>
+      <c r="I181" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J181" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>2165</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>100</v>
+      </c>
+      <c r="I182" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>895</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>100</v>
+      </c>
+      <c r="I183" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>2440</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>100</v>
+      </c>
+      <c r="I184" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>103</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>97</v>
+      </c>
+      <c r="I185" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>117</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>94</v>
+      </c>
+      <c r="I186" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>28.65</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>94</v>
+      </c>
+      <c r="I187" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>112</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>94</v>
+      </c>
+      <c r="I188" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>177</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>94</v>
+      </c>
+      <c r="I189" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>92</v>
+      </c>
+      <c r="I190" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>1145</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>90</v>
+      </c>
+      <c r="I191" t="n">
+        <v>25</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>426</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>90</v>
+      </c>
+      <c r="I192" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>139</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>90</v>
+      </c>
+      <c r="I193" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>84</v>
+      </c>
+      <c r="I194" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>2340</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>80</v>
+      </c>
+      <c r="I195" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>896</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>80</v>
+      </c>
+      <c r="I196" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>79</v>
+      </c>
+      <c r="I197" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>78</v>
+      </c>
+      <c r="I198" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>77</v>
+      </c>
+      <c r="I199" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>381</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>65</v>
+      </c>
+      <c r="I200" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>62</v>
+      </c>
+      <c r="I201" t="n">
+        <v>10</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>1515</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>60</v>
+      </c>
+      <c r="I202" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>79</v>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>408</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>77</v>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>77</v>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>69</v>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R206"/>
+  <dimension ref="A1:R207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10789,6 +10789,56 @@
       <c r="P206" t="inlineStr"/>
       <c r="Q206" t="inlineStr"/>
       <c r="R206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>5115</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>65</v>
+      </c>
+      <c r="I207" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R207"/>
+  <dimension ref="A1:R241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10839,6 +10839,1690 @@
       <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>97</v>
+      </c>
+      <c r="I208" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>559</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>96</v>
+      </c>
+      <c r="I209" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J209" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>120</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>91</v>
+      </c>
+      <c r="I210" t="n">
+        <v>15</v>
+      </c>
+      <c r="J210" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>90</v>
+      </c>
+      <c r="I211" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>87</v>
+      </c>
+      <c r="I212" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J212" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>143</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
+        <v>77</v>
+      </c>
+      <c r="I213" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J213" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>257.5</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
+        <v>77</v>
+      </c>
+      <c r="I214" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
+        <v>76</v>
+      </c>
+      <c r="I215" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J215" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>63</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
+        <v>68</v>
+      </c>
+      <c r="I216" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>2440</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
+        <v>100</v>
+      </c>
+      <c r="I217" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>858</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
+        <v>100</v>
+      </c>
+      <c r="I218" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>2405</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H219" t="n">
+        <v>100</v>
+      </c>
+      <c r="I219" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>104</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H220" t="n">
+        <v>97</v>
+      </c>
+      <c r="I220" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
+      <c r="R220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>110</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H221" t="n">
+        <v>94</v>
+      </c>
+      <c r="I221" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H222" t="n">
+        <v>94</v>
+      </c>
+      <c r="I222" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H223" t="n">
+        <v>94</v>
+      </c>
+      <c r="I223" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
+      <c r="R223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>176</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H224" t="n">
+        <v>94</v>
+      </c>
+      <c r="I224" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H225" t="n">
+        <v>92</v>
+      </c>
+      <c r="I225" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>1180</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H226" t="n">
+        <v>90</v>
+      </c>
+      <c r="I226" t="n">
+        <v>25</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>406</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H227" t="n">
+        <v>90</v>
+      </c>
+      <c r="I227" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H228" t="n">
+        <v>90</v>
+      </c>
+      <c r="I228" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr"/>
+      <c r="R228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H229" t="n">
+        <v>84</v>
+      </c>
+      <c r="I229" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>2325</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H230" t="n">
+        <v>80</v>
+      </c>
+      <c r="I230" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>923</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H231" t="n">
+        <v>80</v>
+      </c>
+      <c r="I231" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H232" t="n">
+        <v>79</v>
+      </c>
+      <c r="I232" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H233" t="n">
+        <v>78</v>
+      </c>
+      <c r="I233" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H234" t="n">
+        <v>77</v>
+      </c>
+      <c r="I234" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>336</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H235" t="n">
+        <v>65</v>
+      </c>
+      <c r="I235" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H236" t="n">
+        <v>62</v>
+      </c>
+      <c r="I236" t="n">
+        <v>10</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
+      <c r="R236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>1405</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H237" t="n">
+        <v>60</v>
+      </c>
+      <c r="I237" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
+        <v>79</v>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr"/>
+      <c r="R238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>378.5</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
+        <v>77</v>
+      </c>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H240" t="n">
+        <v>77</v>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr"/>
+      <c r="R240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>210</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H241" t="n">
+        <v>69</v>
+      </c>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R241"/>
+  <dimension ref="A1:R242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12523,6 +12523,56 @@
       <c r="P241" t="inlineStr"/>
       <c r="Q241" t="inlineStr"/>
       <c r="R241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>5730</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H242" t="n">
+        <v>65</v>
+      </c>
+      <c r="I242" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr"/>
+      <c r="R242" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,13 +468,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="C2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-9.449999999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-7.84</v>
+      </c>
+      <c r="F2" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-32.03</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,9 +542,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>市場</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>區間</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>筆數</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>勝率%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>平均報酬%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>34</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-9.449999999999999</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -681,8 +740,12 @@
       <c r="J2" t="n">
         <v>1.29</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>143</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-5.61</v>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -731,8 +794,12 @@
       <c r="J3" t="n">
         <v>1.11</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>491.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-8.81</v>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -781,8 +848,12 @@
       <c r="J4" t="n">
         <v>1.26</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.84</v>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -831,8 +902,12 @@
       <c r="J5" t="n">
         <v>1.22</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>277.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-19.45</v>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -881,8 +956,12 @@
       <c r="J6" t="n">
         <v>1.36</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>84</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-7.89</v>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -931,8 +1010,12 @@
       <c r="J7" t="n">
         <v>1.11</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-19.23</v>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -981,8 +1064,12 @@
       <c r="J8" t="n">
         <v>1.16</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>237</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-3.85</v>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -1031,8 +1118,12 @@
       <c r="J9" t="n">
         <v>1.03</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>847</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-14.96</v>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1081,8 +1172,12 @@
       <c r="J10" t="n">
         <v>1.35</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-6.22</v>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1131,8 +1226,12 @@
       <c r="J11" t="n">
         <v>0.66</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>2095</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-8.91</v>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1181,8 +1280,12 @@
       <c r="J12" t="n">
         <v>0.4</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>671</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-29.74</v>
+      </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -1231,8 +1334,12 @@
       <c r="J13" t="n">
         <v>0.78</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>2200</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-7.17</v>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1281,8 +1388,12 @@
       <c r="J14" t="n">
         <v>0.73</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.95</v>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
@@ -1331,8 +1442,12 @@
       <c r="J15" t="n">
         <v>0.64</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-13.28</v>
+      </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1381,8 +1496,12 @@
       <c r="J16" t="n">
         <v>0.42</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-19.15</v>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -1431,8 +1550,12 @@
       <c r="J17" t="n">
         <v>0.76</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-7.79</v>
+      </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1481,8 +1604,12 @@
       <c r="J18" t="n">
         <v>0.59</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>176</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-6.88</v>
+      </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -1531,8 +1658,12 @@
       <c r="J19" t="n">
         <v>0.84</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-5.58</v>
+      </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1581,8 +1712,12 @@
       <c r="J20" t="n">
         <v>0.67</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>981</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-19.26</v>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -1631,8 +1766,12 @@
       <c r="J21" t="n">
         <v>0.92</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-32.03</v>
+      </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -1681,8 +1820,12 @@
       <c r="J22" t="n">
         <v>0.73</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-9.779999999999999</v>
+      </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1731,8 +1874,12 @@
       <c r="J23" t="n">
         <v>0.2</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-9.49</v>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1781,8 +1928,12 @@
       <c r="J24" t="n">
         <v>0.82</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>1910</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-18.38</v>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -1831,8 +1982,12 @@
       <c r="J25" t="n">
         <v>0.75</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>855</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-14.07</v>
+      </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -1881,8 +2036,12 @@
       <c r="J26" t="n">
         <v>0.36</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-7.2</v>
+      </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -1931,8 +2090,12 @@
       <c r="J27" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.39</v>
+      </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -1981,8 +2144,12 @@
       <c r="J28" t="n">
         <v>0.71</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-21.07</v>
+      </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
@@ -2031,8 +2198,12 @@
       <c r="J29" t="n">
         <v>0.49</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-15.67</v>
+      </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
@@ -2081,8 +2252,12 @@
       <c r="J30" t="n">
         <v>0.31</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>9.710000000000001</v>
+      </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -2131,8 +2306,12 @@
       <c r="J31" t="n">
         <v>0.36</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-1.69</v>
+      </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2177,8 +2356,12 @@
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-5.75</v>
+      </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -2223,8 +2406,12 @@
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>394</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-2.48</v>
+      </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2269,8 +2456,12 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-5.85</v>
+      </c>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2315,8 +2506,12 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>222.5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>14.99</v>
+      </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
@@ -12585,7 +12780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12683,6 +12878,1130 @@
         <is>
           <t>最終報酬%</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>69</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>222.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>62</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K3" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>9.710000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>97</v>
+      </c>
+      <c r="I4" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K4" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>91</v>
+      </c>
+      <c r="I5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K5" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>78</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1475</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>60</v>
+      </c>
+      <c r="I7" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>404</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>77</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>394</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>-2.48</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>246.5</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>77</v>
+      </c>
+      <c r="I9" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K9" t="n">
+        <v>237</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>-3.85</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>92</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K10" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-5.58</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>-5.58</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>97</v>
+      </c>
+      <c r="I11" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K11" t="n">
+        <v>143</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-5.61</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>-5.61</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>79</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>-5.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>77</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>-5.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>68</v>
+      </c>
+      <c r="I14" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K14" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-6.22</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>-6.22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>189</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>94</v>
+      </c>
+      <c r="I15" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K15" t="n">
+        <v>176</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-6.88</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>-6.88</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2370</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2200</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-7.17</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>-7.17</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>93</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>79</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K17" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>-7.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>94</v>
+      </c>
+      <c r="I18" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K18" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-7.79</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>-7.79</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>87</v>
+      </c>
+      <c r="I19" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-7.89</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>-7.89</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>539</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>96</v>
+      </c>
+      <c r="I20" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K20" t="n">
+        <v>491.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-8.81</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>-8.81</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>100</v>
+      </c>
+      <c r="I21" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2095</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-8.91</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>-8.91</v>
       </c>
     </row>
   </sheetData>
@@ -12696,7 +14015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12796,6 +14115,1146 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>499.5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>90</v>
+      </c>
+      <c r="I2" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K2" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-32.03</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>-32.03</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>955</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>671</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-29.74</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>-29.74</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>77</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K4" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-21.07</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>-21.07</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>90</v>
+      </c>
+      <c r="I5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K5" t="n">
+        <v>277.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-19.45</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>-19.45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1215</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K6" t="n">
+        <v>981</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-19.26</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>-19.26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>143</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>77</v>
+      </c>
+      <c r="I7" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K7" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-19.23</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>-19.23</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>94</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K8" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-19.15</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>-19.15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2340</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>80</v>
+      </c>
+      <c r="I9" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1910</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-18.38</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>-18.38</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>367</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K10" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-15.67</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>-15.67</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>996</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>76</v>
+      </c>
+      <c r="I11" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K11" t="n">
+        <v>847</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-14.96</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>-14.96</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>995</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>80</v>
+      </c>
+      <c r="I12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>855</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-14.07</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>-14.07</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>94</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K13" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-13.28</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>-13.28</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>90</v>
+      </c>
+      <c r="I14" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K14" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-9.779999999999999</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>-9.779999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>84</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-9.49</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>-9.49</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2095</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-8.91</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>-8.91</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>539</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>96</v>
+      </c>
+      <c r="I17" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K17" t="n">
+        <v>491.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-8.81</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>-8.81</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>87</v>
+      </c>
+      <c r="I18" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-7.89</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>-7.89</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>94</v>
+      </c>
+      <c r="I19" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K19" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-7.79</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>-7.79</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>93</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>79</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K20" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>-7.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2370</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>100</v>
+      </c>
+      <c r="I21" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2200</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-7.17</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>-7.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>11.8</v>
+        <v>14.3</v>
       </c>
       <c r="D2" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.01</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.84</v>
+        <v>-7.79</v>
       </c>
       <c r="F2" t="n">
         <v>14.99</v>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" t="n">
-        <v>11.8</v>
+        <v>14.3</v>
       </c>
       <c r="E2" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.01</v>
       </c>
     </row>
   </sheetData>
@@ -6080,8 +6080,12 @@
       <c r="J107" t="n">
         <v>0.26</v>
       </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
+      <c r="K107" t="n">
+        <v>4900</v>
+      </c>
+      <c r="L107" t="n">
+        <v>5.72</v>
+      </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
@@ -12992,7 +12996,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -13001,16 +13005,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>97.40000000000001</v>
+        <v>4635</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -13019,23 +13023,23 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="I4" t="n">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0.73</v>
+        <v>0.26</v>
       </c>
       <c r="K4" t="n">
-        <v>99.3</v>
+        <v>4900</v>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>5.72</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -13044,7 +13048,7 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>1.95</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="5">
@@ -13058,20 +13062,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>119.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -13080,19 +13084,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>12.4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.26</v>
+        <v>0.73</v>
       </c>
       <c r="K5" t="n">
-        <v>120.5</v>
+        <v>99.3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.84</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -13101,7 +13105,7 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>0.84</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="6">
@@ -13115,41 +13119,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71.7</v>
+        <v>119.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I6" t="n">
-        <v>6.8</v>
+        <v>15</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.26</v>
       </c>
       <c r="K6" t="n">
-        <v>70.7</v>
+        <v>120.5</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.39</v>
+        <v>0.84</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -13158,7 +13162,7 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>-1.39</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="7">
@@ -13172,16 +13176,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1475</v>
+        <v>71.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -13190,23 +13194,23 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="I7" t="n">
-        <v>11.9</v>
+        <v>6.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.36</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>1450</v>
+        <v>70.7</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.69</v>
+        <v>-1.39</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -13215,7 +13219,7 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>-1.69</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="8">
@@ -13229,37 +13233,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>404</v>
+        <v>1475</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>77</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.36</v>
+      </c>
       <c r="K8" t="n">
-        <v>394</v>
+        <v>1450</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.48</v>
+        <v>-1.69</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -13268,7 +13276,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>-2.48</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="9">
@@ -13282,20 +13290,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>246.5</v>
+        <v>404</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -13306,17 +13314,13 @@
       <c r="H9" t="n">
         <v>77</v>
       </c>
-      <c r="I9" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.16</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>237</v>
+        <v>394</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.85</v>
+        <v>-2.48</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -13325,7 +13329,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>-3.85</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="10">
@@ -13339,41 +13343,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>43.9</v>
+        <v>246.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I10" t="n">
-        <v>7.6</v>
+        <v>15.3</v>
       </c>
       <c r="J10" t="n">
-        <v>0.84</v>
+        <v>1.16</v>
       </c>
       <c r="K10" t="n">
-        <v>41.45</v>
+        <v>237</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.58</v>
+        <v>-3.85</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -13382,7 +13386,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-5.58</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="11">
@@ -13396,20 +13400,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>151.5</v>
+        <v>43.9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -13418,19 +13422,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I11" t="n">
-        <v>14.7</v>
+        <v>7.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1.29</v>
+        <v>0.84</v>
       </c>
       <c r="K11" t="n">
-        <v>143</v>
+        <v>41.45</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.61</v>
+        <v>-5.58</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -13439,7 +13443,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-5.61</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="12">
@@ -13453,37 +13457,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>78.3</v>
+        <v>151.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>79</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="I12" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.29</v>
+      </c>
       <c r="K12" t="n">
-        <v>73.8</v>
+        <v>143</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.75</v>
+        <v>-5.61</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -13492,7 +13500,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-5.75</v>
+        <v>-5.61</v>
       </c>
     </row>
     <row r="13">
@@ -13506,16 +13514,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>23.95</v>
+        <v>78.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -13528,15 +13536,15 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>22.55</v>
+        <v>73.8</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.85</v>
+        <v>-5.75</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -13545,7 +13553,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-5.85</v>
+        <v>-5.75</v>
       </c>
     </row>
     <row r="14">
@@ -13559,20 +13567,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>64.3</v>
+        <v>23.95</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -13581,19 +13589,15 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>68</v>
-      </c>
-      <c r="I14" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.35</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>60.3</v>
+        <v>22.55</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.22</v>
+        <v>-5.85</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -13602,7 +13606,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-6.22</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="15">
@@ -13616,41 +13620,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>189</v>
+        <v>64.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="I15" t="n">
-        <v>11.4</v>
+        <v>21.3</v>
       </c>
       <c r="J15" t="n">
-        <v>0.59</v>
+        <v>1.35</v>
       </c>
       <c r="K15" t="n">
-        <v>176</v>
+        <v>60.3</v>
       </c>
       <c r="L15" t="n">
-        <v>-6.88</v>
+        <v>-6.22</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -13659,7 +13663,7 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-6.88</v>
+        <v>-6.22</v>
       </c>
     </row>
     <row r="16">
@@ -13673,16 +13677,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2370</v>
+        <v>189</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -13695,19 +13699,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I16" t="n">
-        <v>23.6</v>
+        <v>11.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0.78</v>
+        <v>0.59</v>
       </c>
       <c r="K16" t="n">
-        <v>2200</v>
+        <v>176</v>
       </c>
       <c r="L16" t="n">
-        <v>-7.17</v>
+        <v>-6.88</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -13716,7 +13720,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-7.17</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="17">
@@ -13730,16 +13734,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>93</v>
+        <v>2370</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -13748,23 +13752,23 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>8.6</v>
+        <v>23.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.36</v>
+        <v>0.78</v>
       </c>
       <c r="K17" t="n">
-        <v>86.3</v>
+        <v>2200</v>
       </c>
       <c r="L17" t="n">
-        <v>-7.2</v>
+        <v>-7.17</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -13773,7 +13777,7 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-7.2</v>
+        <v>-7.17</v>
       </c>
     </row>
     <row r="18">
@@ -13787,16 +13791,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>115.5</v>
+        <v>93</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -13805,23 +13809,23 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I18" t="n">
-        <v>10.7</v>
+        <v>8.6</v>
       </c>
       <c r="J18" t="n">
-        <v>0.76</v>
+        <v>0.36</v>
       </c>
       <c r="K18" t="n">
-        <v>106.5</v>
+        <v>86.3</v>
       </c>
       <c r="L18" t="n">
-        <v>-7.79</v>
+        <v>-7.2</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -13830,7 +13834,7 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-7.79</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="19">
@@ -13844,20 +13848,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>91.2</v>
+        <v>115.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -13866,19 +13870,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="I19" t="n">
-        <v>16.7</v>
+        <v>10.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1.36</v>
+        <v>0.76</v>
       </c>
       <c r="K19" t="n">
-        <v>84</v>
+        <v>106.5</v>
       </c>
       <c r="L19" t="n">
-        <v>-7.89</v>
+        <v>-7.79</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -13887,7 +13891,7 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-7.89</v>
+        <v>-7.79</v>
       </c>
     </row>
     <row r="20">
@@ -13901,16 +13905,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>539</v>
+        <v>91.2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -13923,19 +13927,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I20" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="K20" t="n">
-        <v>491.5</v>
+        <v>84</v>
       </c>
       <c r="L20" t="n">
-        <v>-8.81</v>
+        <v>-7.89</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -13944,7 +13948,7 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-8.81</v>
+        <v>-7.89</v>
       </c>
     </row>
     <row r="21">
@@ -13958,20 +13962,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2300</v>
+        <v>539</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -13980,19 +13984,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I21" t="n">
-        <v>24.6</v>
+        <v>17.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0.66</v>
+        <v>1.11</v>
       </c>
       <c r="K21" t="n">
-        <v>2095</v>
+        <v>491.5</v>
       </c>
       <c r="L21" t="n">
-        <v>-8.91</v>
+        <v>-8.81</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -14001,7 +14005,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-8.91</v>
+        <v>-8.81</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R242"/>
+  <dimension ref="A1:R276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12772,6 +12772,1690 @@
       <c r="P242" t="inlineStr"/>
       <c r="Q242" t="inlineStr"/>
       <c r="R242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>148</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H243" t="n">
+        <v>97</v>
+      </c>
+      <c r="I243" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J243" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr"/>
+      <c r="R243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>500</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H244" t="n">
+        <v>96</v>
+      </c>
+      <c r="I244" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J244" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>123</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H245" t="n">
+        <v>91</v>
+      </c>
+      <c r="I245" t="n">
+        <v>15</v>
+      </c>
+      <c r="J245" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>289</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H246" t="n">
+        <v>90</v>
+      </c>
+      <c r="I246" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J246" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H247" t="n">
+        <v>87</v>
+      </c>
+      <c r="I247" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J247" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr"/>
+      <c r="R247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>122</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H248" t="n">
+        <v>77</v>
+      </c>
+      <c r="I248" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J248" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr"/>
+      <c r="P248" t="inlineStr"/>
+      <c r="Q248" t="inlineStr"/>
+      <c r="R248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H249" t="n">
+        <v>77</v>
+      </c>
+      <c r="I249" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J249" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr"/>
+      <c r="P249" t="inlineStr"/>
+      <c r="Q249" t="inlineStr"/>
+      <c r="R249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>821</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H250" t="n">
+        <v>76</v>
+      </c>
+      <c r="I250" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J250" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" t="inlineStr"/>
+      <c r="Q250" t="inlineStr"/>
+      <c r="R250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H251" t="n">
+        <v>68</v>
+      </c>
+      <c r="I251" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J251" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr"/>
+      <c r="R251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>2320</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H252" t="n">
+        <v>100</v>
+      </c>
+      <c r="I252" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="inlineStr"/>
+      <c r="R252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>707</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H253" t="n">
+        <v>100</v>
+      </c>
+      <c r="I253" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J253" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr"/>
+      <c r="R253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>2425</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H254" t="n">
+        <v>100</v>
+      </c>
+      <c r="I254" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J254" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr"/>
+      <c r="Q254" t="inlineStr"/>
+      <c r="R254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H255" t="n">
+        <v>97</v>
+      </c>
+      <c r="I255" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
+      <c r="R255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>105</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H256" t="n">
+        <v>94</v>
+      </c>
+      <c r="I256" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J256" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="inlineStr"/>
+      <c r="R256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H257" t="n">
+        <v>94</v>
+      </c>
+      <c r="I257" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="inlineStr"/>
+      <c r="Q257" t="inlineStr"/>
+      <c r="R257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>104</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H258" t="n">
+        <v>94</v>
+      </c>
+      <c r="I258" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J258" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr"/>
+      <c r="P258" t="inlineStr"/>
+      <c r="Q258" t="inlineStr"/>
+      <c r="R258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H259" t="n">
+        <v>94</v>
+      </c>
+      <c r="I259" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr"/>
+      <c r="Q259" t="inlineStr"/>
+      <c r="R259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H260" t="n">
+        <v>92</v>
+      </c>
+      <c r="I260" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
+      <c r="P260" t="inlineStr"/>
+      <c r="Q260" t="inlineStr"/>
+      <c r="R260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>1045</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H261" t="n">
+        <v>90</v>
+      </c>
+      <c r="I261" t="n">
+        <v>25</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
+      <c r="P261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr"/>
+      <c r="R261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>369</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H262" t="n">
+        <v>90</v>
+      </c>
+      <c r="I262" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="inlineStr"/>
+      <c r="Q262" t="inlineStr"/>
+      <c r="R262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>131</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H263" t="n">
+        <v>90</v>
+      </c>
+      <c r="I263" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr"/>
+      <c r="P263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr"/>
+      <c r="R263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H264" t="n">
+        <v>84</v>
+      </c>
+      <c r="I264" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr"/>
+      <c r="R264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>2125</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H265" t="n">
+        <v>80</v>
+      </c>
+      <c r="I265" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr"/>
+      <c r="P265" t="inlineStr"/>
+      <c r="Q265" t="inlineStr"/>
+      <c r="R265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>902</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H266" t="n">
+        <v>80</v>
+      </c>
+      <c r="I266" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr"/>
+      <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr"/>
+      <c r="R266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>79</v>
+      </c>
+      <c r="I267" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr"/>
+      <c r="P267" t="inlineStr"/>
+      <c r="Q267" t="inlineStr"/>
+      <c r="R267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
+        <v>78</v>
+      </c>
+      <c r="I268" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr"/>
+      <c r="Q268" t="inlineStr"/>
+      <c r="R268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
+        <v>77</v>
+      </c>
+      <c r="I269" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr"/>
+      <c r="P269" t="inlineStr"/>
+      <c r="Q269" t="inlineStr"/>
+      <c r="R269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
+        <v>65</v>
+      </c>
+      <c r="I270" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr"/>
+      <c r="P270" t="inlineStr"/>
+      <c r="Q270" t="inlineStr"/>
+      <c r="R270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>176</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
+        <v>62</v>
+      </c>
+      <c r="I271" t="n">
+        <v>10</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr"/>
+      <c r="P271" t="inlineStr"/>
+      <c r="Q271" t="inlineStr"/>
+      <c r="R271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>1315</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>60</v>
+      </c>
+      <c r="I272" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr"/>
+      <c r="P272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr"/>
+      <c r="R272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>79</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr"/>
+      <c r="P273" t="inlineStr"/>
+      <c r="Q273" t="inlineStr"/>
+      <c r="R273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>398.5</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>77</v>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr"/>
+      <c r="P274" t="inlineStr"/>
+      <c r="Q274" t="inlineStr"/>
+      <c r="R274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>77</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr"/>
+      <c r="P275" t="inlineStr"/>
+      <c r="Q275" t="inlineStr"/>
+      <c r="R275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>223</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>69</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr"/>
+      <c r="P276" t="inlineStr"/>
+      <c r="Q276" t="inlineStr"/>
+      <c r="R276" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C2" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="D2" t="n">
-        <v>-9.01</v>
+        <v>-9.06</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.79</v>
+        <v>-7.84</v>
       </c>
       <c r="F2" t="n">
         <v>14.99</v>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="E2" t="n">
-        <v>-9.01</v>
+        <v>-9.06</v>
       </c>
     </row>
   </sheetData>
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R276"/>
+  <dimension ref="A1:R277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6130,8 +6130,12 @@
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
+      <c r="K108" t="n">
+        <v>119</v>
+      </c>
+      <c r="L108" t="n">
+        <v>-11.19</v>
+      </c>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
@@ -6176,8 +6180,12 @@
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
+      <c r="K109" t="n">
+        <v>31.95</v>
+      </c>
+      <c r="L109" t="n">
+        <v>-15.03</v>
+      </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
@@ -6222,8 +6230,12 @@
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
+      <c r="K110" t="n">
+        <v>396.5</v>
+      </c>
+      <c r="L110" t="n">
+        <v>-2.58</v>
+      </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
@@ -14456,6 +14468,56 @@
       <c r="P276" t="inlineStr"/>
       <c r="Q276" t="inlineStr"/>
       <c r="R276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>5925</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>65</v>
+      </c>
+      <c r="I277" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr"/>
+      <c r="P277" t="inlineStr"/>
+      <c r="Q277" t="inlineStr"/>
+      <c r="R277" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15018,7 +15080,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -15027,41 +15089,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>246.5</v>
+        <v>407</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>77</v>
-      </c>
-      <c r="I10" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.16</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>237</v>
+        <v>396.5</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.85</v>
+        <v>-2.58</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -15070,7 +15128,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-3.85</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="11">
@@ -15084,41 +15142,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>43.9</v>
+        <v>246.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I11" t="n">
-        <v>7.6</v>
+        <v>15.3</v>
       </c>
       <c r="J11" t="n">
-        <v>0.84</v>
+        <v>1.16</v>
       </c>
       <c r="K11" t="n">
-        <v>41.45</v>
+        <v>237</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.58</v>
+        <v>-3.85</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -15127,7 +15185,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-5.58</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="12">
@@ -15141,20 +15199,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>151.5</v>
+        <v>43.9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -15163,19 +15221,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I12" t="n">
-        <v>14.7</v>
+        <v>7.6</v>
       </c>
       <c r="J12" t="n">
-        <v>1.29</v>
+        <v>0.84</v>
       </c>
       <c r="K12" t="n">
-        <v>143</v>
+        <v>41.45</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.61</v>
+        <v>-5.58</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -15184,7 +15242,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-5.61</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="13">
@@ -15198,37 +15256,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>78.3</v>
+        <v>151.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>79</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="I13" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.29</v>
+      </c>
       <c r="K13" t="n">
-        <v>73.8</v>
+        <v>143</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.75</v>
+        <v>-5.61</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -15237,7 +15299,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-5.75</v>
+        <v>-5.61</v>
       </c>
     </row>
     <row r="14">
@@ -15251,16 +15313,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>23.95</v>
+        <v>78.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -15273,15 +15335,15 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>22.55</v>
+        <v>73.8</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.85</v>
+        <v>-5.75</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -15290,7 +15352,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-5.85</v>
+        <v>-5.75</v>
       </c>
     </row>
     <row r="15">
@@ -15304,20 +15366,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>64.3</v>
+        <v>23.95</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -15326,19 +15388,15 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>68</v>
-      </c>
-      <c r="I15" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.35</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>60.3</v>
+        <v>22.55</v>
       </c>
       <c r="L15" t="n">
-        <v>-6.22</v>
+        <v>-5.85</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -15347,7 +15405,7 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-6.22</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="16">
@@ -15361,41 +15419,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>189</v>
+        <v>64.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="I16" t="n">
-        <v>11.4</v>
+        <v>21.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.59</v>
+        <v>1.35</v>
       </c>
       <c r="K16" t="n">
-        <v>176</v>
+        <v>60.3</v>
       </c>
       <c r="L16" t="n">
-        <v>-6.88</v>
+        <v>-6.22</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -15404,7 +15462,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-6.88</v>
+        <v>-6.22</v>
       </c>
     </row>
     <row r="17">
@@ -15418,16 +15476,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2370</v>
+        <v>189</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -15440,19 +15498,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I17" t="n">
-        <v>23.6</v>
+        <v>11.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0.78</v>
+        <v>0.59</v>
       </c>
       <c r="K17" t="n">
-        <v>2200</v>
+        <v>176</v>
       </c>
       <c r="L17" t="n">
-        <v>-7.17</v>
+        <v>-6.88</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -15461,7 +15519,7 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-7.17</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="18">
@@ -15475,16 +15533,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>93</v>
+        <v>2370</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -15493,23 +15551,23 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>8.6</v>
+        <v>23.6</v>
       </c>
       <c r="J18" t="n">
-        <v>0.36</v>
+        <v>0.78</v>
       </c>
       <c r="K18" t="n">
-        <v>86.3</v>
+        <v>2200</v>
       </c>
       <c r="L18" t="n">
-        <v>-7.2</v>
+        <v>-7.17</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -15518,7 +15576,7 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-7.2</v>
+        <v>-7.17</v>
       </c>
     </row>
     <row r="19">
@@ -15532,16 +15590,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115.5</v>
+        <v>93</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -15550,23 +15608,23 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I19" t="n">
-        <v>10.7</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
-        <v>0.76</v>
+        <v>0.36</v>
       </c>
       <c r="K19" t="n">
-        <v>106.5</v>
+        <v>86.3</v>
       </c>
       <c r="L19" t="n">
-        <v>-7.79</v>
+        <v>-7.2</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -15575,7 +15633,7 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-7.79</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="20">
@@ -15589,20 +15647,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>91.2</v>
+        <v>115.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -15611,19 +15669,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="I20" t="n">
-        <v>16.7</v>
+        <v>10.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1.36</v>
+        <v>0.76</v>
       </c>
       <c r="K20" t="n">
-        <v>84</v>
+        <v>106.5</v>
       </c>
       <c r="L20" t="n">
-        <v>-7.89</v>
+        <v>-7.79</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -15632,7 +15690,7 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-7.89</v>
+        <v>-7.79</v>
       </c>
     </row>
     <row r="21">
@@ -15646,16 +15704,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>539</v>
+        <v>91.2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -15668,19 +15726,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I21" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="K21" t="n">
-        <v>491.5</v>
+        <v>84</v>
       </c>
       <c r="L21" t="n">
-        <v>-8.81</v>
+        <v>-7.89</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -15689,7 +15747,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-8.81</v>
+        <v>-7.89</v>
       </c>
     </row>
   </sheetData>
@@ -16318,7 +16376,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -16327,20 +16385,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>996</v>
+        <v>37.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -16349,19 +16407,15 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>76</v>
-      </c>
-      <c r="I11" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.03</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>847</v>
+        <v>31.95</v>
       </c>
       <c r="L11" t="n">
-        <v>-14.96</v>
+        <v>-15.03</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -16370,7 +16424,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-14.96</v>
+        <v>-15.03</v>
       </c>
     </row>
     <row r="12">
@@ -16384,41 +16438,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I12" t="n">
-        <v>21.8</v>
+        <v>38.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="L12" t="n">
-        <v>-14.07</v>
+        <v>-14.96</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -16427,7 +16481,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-14.07</v>
+        <v>-14.96</v>
       </c>
     </row>
     <row r="13">
@@ -16441,16 +16495,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>114.5</v>
+        <v>995</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -16463,19 +16517,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I13" t="n">
-        <v>12.3</v>
+        <v>21.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="K13" t="n">
-        <v>99.3</v>
+        <v>855</v>
       </c>
       <c r="L13" t="n">
-        <v>-13.28</v>
+        <v>-14.07</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -16484,7 +16538,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-13.28</v>
+        <v>-14.07</v>
       </c>
     </row>
     <row r="14">
@@ -16498,16 +16552,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>138</v>
+        <v>114.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -16520,19 +16574,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I14" t="n">
-        <v>14.1</v>
+        <v>12.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="K14" t="n">
-        <v>124.5</v>
+        <v>99.3</v>
       </c>
       <c r="L14" t="n">
-        <v>-9.779999999999999</v>
+        <v>-13.28</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -16541,12 +16595,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-9.779999999999999</v>
+        <v>-13.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -16555,41 +16609,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>40.55</v>
+        <v>134</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>84</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.2</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>36.7</v>
+        <v>119</v>
       </c>
       <c r="L15" t="n">
-        <v>-9.49</v>
+        <v>-11.19</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -16598,7 +16648,7 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-9.49</v>
+        <v>-11.19</v>
       </c>
     </row>
     <row r="16">
@@ -16612,16 +16662,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2300</v>
+        <v>138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -16634,19 +16684,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I16" t="n">
-        <v>24.6</v>
+        <v>14.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="K16" t="n">
-        <v>2095</v>
+        <v>124.5</v>
       </c>
       <c r="L16" t="n">
-        <v>-8.91</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -16655,7 +16705,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-8.91</v>
+        <v>-9.779999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -16669,20 +16719,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>539</v>
+        <v>40.55</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -16691,19 +16741,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I17" t="n">
-        <v>17.9</v>
+        <v>6.2</v>
       </c>
       <c r="J17" t="n">
-        <v>1.11</v>
+        <v>0.2</v>
       </c>
       <c r="K17" t="n">
-        <v>491.5</v>
+        <v>36.7</v>
       </c>
       <c r="L17" t="n">
-        <v>-8.81</v>
+        <v>-9.49</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -16712,7 +16762,7 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-8.81</v>
+        <v>-9.49</v>
       </c>
     </row>
     <row r="18">
@@ -16726,20 +16776,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>91.2</v>
+        <v>2300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -16748,19 +16798,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>16.7</v>
+        <v>24.6</v>
       </c>
       <c r="J18" t="n">
-        <v>1.36</v>
+        <v>0.66</v>
       </c>
       <c r="K18" t="n">
-        <v>84</v>
+        <v>2095</v>
       </c>
       <c r="L18" t="n">
-        <v>-7.89</v>
+        <v>-8.91</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -16769,7 +16819,7 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-7.89</v>
+        <v>-8.91</v>
       </c>
     </row>
     <row r="19">
@@ -16783,20 +16833,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>115.5</v>
+        <v>539</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -16805,19 +16855,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I19" t="n">
-        <v>10.7</v>
+        <v>17.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="K19" t="n">
-        <v>106.5</v>
+        <v>491.5</v>
       </c>
       <c r="L19" t="n">
-        <v>-7.79</v>
+        <v>-8.81</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -16826,7 +16876,7 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-7.79</v>
+        <v>-8.81</v>
       </c>
     </row>
     <row r="20">
@@ -16840,41 +16890,41 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>93</v>
+        <v>91.2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I20" t="n">
-        <v>8.6</v>
+        <v>16.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.36</v>
+        <v>1.36</v>
       </c>
       <c r="K20" t="n">
-        <v>86.3</v>
+        <v>84</v>
       </c>
       <c r="L20" t="n">
-        <v>-7.2</v>
+        <v>-7.89</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -16883,7 +16933,7 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-7.2</v>
+        <v>-7.89</v>
       </c>
     </row>
     <row r="21">
@@ -16897,16 +16947,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2370</v>
+        <v>115.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -16919,19 +16969,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I21" t="n">
-        <v>23.6</v>
+        <v>10.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="K21" t="n">
-        <v>2200</v>
+        <v>106.5</v>
       </c>
       <c r="L21" t="n">
-        <v>-7.17</v>
+        <v>-7.79</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -16940,7 +16990,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-7.17</v>
+        <v>-7.79</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,19 +468,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C2" t="n">
-        <v>13.2</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>-9.06</v>
+        <v>-5.35</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.84</v>
+        <v>-5.88</v>
       </c>
       <c r="F2" t="n">
-        <v>14.99</v>
+        <v>33.15</v>
       </c>
       <c r="G2" t="n">
         <v>-32.03</v>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>13.2</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>-9.06</v>
+        <v>-5.35</v>
       </c>
     </row>
   </sheetData>
@@ -6284,8 +6284,12 @@
       <c r="J111" t="n">
         <v>1.29</v>
       </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
+      <c r="K111" t="n">
+        <v>146</v>
+      </c>
+      <c r="L111" t="n">
+        <v>-7.89</v>
+      </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
@@ -6334,8 +6338,12 @@
       <c r="J112" t="n">
         <v>1.11</v>
       </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
+      <c r="K112" t="n">
+        <v>509</v>
+      </c>
+      <c r="L112" t="n">
+        <v>-1.36</v>
+      </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
@@ -6384,8 +6392,12 @@
       <c r="J113" t="n">
         <v>1.26</v>
       </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
+      <c r="K113" t="n">
+        <v>122</v>
+      </c>
+      <c r="L113" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
@@ -6434,8 +6446,12 @@
       <c r="J114" t="n">
         <v>1.22</v>
       </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
+      <c r="K114" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="L114" t="n">
+        <v>-12.08</v>
+      </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
@@ -6484,8 +6500,12 @@
       <c r="J115" t="n">
         <v>1.36</v>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
+      <c r="K115" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="L115" t="n">
+        <v>-9.5</v>
+      </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
@@ -6534,8 +6554,12 @@
       <c r="J116" t="n">
         <v>1.11</v>
       </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
+      <c r="K116" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="L116" t="n">
+        <v>-11.9</v>
+      </c>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
@@ -6584,8 +6608,12 @@
       <c r="J117" t="n">
         <v>1.16</v>
       </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
+      <c r="K117" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="L117" t="n">
+        <v>11.6</v>
+      </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
@@ -6634,8 +6662,12 @@
       <c r="J118" t="n">
         <v>1.03</v>
       </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
+      <c r="K118" t="n">
+        <v>1115</v>
+      </c>
+      <c r="L118" t="n">
+        <v>-5.91</v>
+      </c>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
@@ -6684,8 +6716,12 @@
       <c r="J119" t="n">
         <v>1.35</v>
       </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
+      <c r="K119" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
@@ -6734,8 +6770,12 @@
       <c r="J120" t="n">
         <v>0.66</v>
       </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
+      <c r="K120" t="n">
+        <v>2940</v>
+      </c>
+      <c r="L120" t="n">
+        <v>20</v>
+      </c>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
@@ -6784,8 +6824,12 @@
       <c r="J121" t="n">
         <v>0.4</v>
       </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
+      <c r="K121" t="n">
+        <v>836</v>
+      </c>
+      <c r="L121" t="n">
+        <v>-5.32</v>
+      </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
@@ -6834,8 +6878,12 @@
       <c r="J122" t="n">
         <v>0.78</v>
       </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
+      <c r="K122" t="n">
+        <v>2365</v>
+      </c>
+      <c r="L122" t="n">
+        <v>-3.07</v>
+      </c>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
@@ -6884,8 +6932,12 @@
       <c r="J123" t="n">
         <v>0.73</v>
       </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
+      <c r="K123" t="n">
+        <v>110</v>
+      </c>
+      <c r="L123" t="n">
+        <v>6.8</v>
+      </c>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
@@ -6934,8 +6986,12 @@
       <c r="J124" t="n">
         <v>0.64</v>
       </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
+      <c r="K124" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="L124" t="n">
+        <v>-10.16</v>
+      </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
@@ -6984,8 +7040,12 @@
       <c r="J125" t="n">
         <v>0.42</v>
       </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
+      <c r="K125" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="L125" t="n">
+        <v>-18.74</v>
+      </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
@@ -7034,8 +7094,12 @@
       <c r="J126" t="n">
         <v>0.76</v>
       </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
+      <c r="K126" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="L126" t="n">
+        <v>-3.59</v>
+      </c>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
@@ -7084,8 +7148,12 @@
       <c r="J127" t="n">
         <v>0.59</v>
       </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
+      <c r="K127" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
@@ -7134,8 +7202,12 @@
       <c r="J128" t="n">
         <v>0.84</v>
       </c>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
+      <c r="K128" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="L128" t="n">
+        <v>2</v>
+      </c>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
@@ -7184,8 +7256,12 @@
       <c r="J129" t="n">
         <v>0.67</v>
       </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
+      <c r="K129" t="n">
+        <v>1235</v>
+      </c>
+      <c r="L129" t="n">
+        <v>5.11</v>
+      </c>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
@@ -7234,8 +7310,12 @@
       <c r="J130" t="n">
         <v>0.92</v>
       </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
+      <c r="K130" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="L130" t="n">
+        <v>-16.4</v>
+      </c>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
@@ -7284,8 +7364,12 @@
       <c r="J131" t="n">
         <v>0.73</v>
       </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
+      <c r="K131" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="L131" t="n">
+        <v>7.29</v>
+      </c>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
@@ -7334,8 +7418,12 @@
       <c r="J132" t="n">
         <v>0.2</v>
       </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
+      <c r="K132" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="L132" t="n">
+        <v>-5.74</v>
+      </c>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
@@ -7384,8 +7472,12 @@
       <c r="J133" t="n">
         <v>0.82</v>
       </c>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
+      <c r="K133" t="n">
+        <v>2410</v>
+      </c>
+      <c r="L133" t="n">
+        <v>-1.83</v>
+      </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
@@ -7434,8 +7526,12 @@
       <c r="J134" t="n">
         <v>0.75</v>
       </c>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
+      <c r="K134" t="n">
+        <v>1060</v>
+      </c>
+      <c r="L134" t="n">
+        <v>9.279999999999999</v>
+      </c>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
@@ -7484,8 +7580,12 @@
       <c r="J135" t="n">
         <v>0.36</v>
       </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
+      <c r="K135" t="n">
+        <v>93</v>
+      </c>
+      <c r="L135" t="n">
+        <v>5.92</v>
+      </c>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
@@ -7534,8 +7634,12 @@
       <c r="J136" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
+      <c r="K136" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.66</v>
+      </c>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
@@ -7584,8 +7688,12 @@
       <c r="J137" t="n">
         <v>0.71</v>
       </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
+      <c r="K137" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="L137" t="n">
+        <v>-14.2</v>
+      </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
@@ -7634,8 +7742,12 @@
       <c r="J138" t="n">
         <v>0.49</v>
       </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
+      <c r="K138" t="n">
+        <v>302</v>
+      </c>
+      <c r="L138" t="n">
+        <v>-19.03</v>
+      </c>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
@@ -7684,8 +7796,12 @@
       <c r="J139" t="n">
         <v>0.31</v>
       </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
+      <c r="K139" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="L139" t="n">
+        <v>21.86</v>
+      </c>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
@@ -7734,8 +7850,12 @@
       <c r="J140" t="n">
         <v>0.36</v>
       </c>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
+      <c r="K140" t="n">
+        <v>1410</v>
+      </c>
+      <c r="L140" t="n">
+        <v>-6</v>
+      </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
@@ -7780,8 +7900,12 @@
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
+      <c r="K141" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="L141" t="n">
+        <v>-11.6</v>
+      </c>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
@@ -7826,8 +7950,12 @@
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
+      <c r="K142" t="n">
+        <v>421</v>
+      </c>
+      <c r="L142" t="n">
+        <v>4.21</v>
+      </c>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
@@ -7872,8 +8000,12 @@
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
+      <c r="K143" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="L143" t="n">
+        <v>-2.94</v>
+      </c>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
@@ -7918,8 +8050,12 @@
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
+      <c r="K144" t="n">
+        <v>247</v>
+      </c>
+      <c r="L144" t="n">
+        <v>33.15</v>
+      </c>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
@@ -14632,7 +14768,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -14650,7 +14786,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>193.5</v>
+        <v>185.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -14668,10 +14804,10 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>222.5</v>
+        <v>247</v>
       </c>
       <c r="L2" t="n">
-        <v>14.99</v>
+        <v>33.15</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -14680,12 +14816,12 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>14.99</v>
+        <v>33.15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -14703,7 +14839,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>154.5</v>
+        <v>155.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -14725,10 +14861,10 @@
         <v>0.31</v>
       </c>
       <c r="K3" t="n">
-        <v>169.5</v>
+        <v>189.5</v>
       </c>
       <c r="L3" t="n">
-        <v>9.710000000000001</v>
+        <v>21.86</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -14737,12 +14873,12 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9.710000000000001</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -14751,16 +14887,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4635</v>
+        <v>2450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -14769,23 +14905,23 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>9.6</v>
+        <v>24.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0.26</v>
+        <v>0.66</v>
       </c>
       <c r="K4" t="n">
-        <v>4900</v>
+        <v>2940</v>
       </c>
       <c r="L4" t="n">
-        <v>5.72</v>
+        <v>20</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -14794,7 +14930,7 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>5.72</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -14808,41 +14944,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>97.40000000000001</v>
+        <v>193.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>97</v>
-      </c>
-      <c r="I5" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.73</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>99.3</v>
+        <v>222.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>14.99</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -14851,12 +14983,12 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>1.95</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -14865,16 +14997,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>119.5</v>
+        <v>237</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -14883,23 +15015,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="K6" t="n">
-        <v>120.5</v>
+        <v>264.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.84</v>
+        <v>11.6</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -14908,7 +15040,7 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>0.84</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="7">
@@ -14922,16 +15054,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71.7</v>
+        <v>154.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -14940,23 +15072,23 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="I7" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="K7" t="n">
-        <v>70.7</v>
+        <v>169.5</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.39</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -14965,12 +15097,12 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>-1.39</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -14979,16 +15111,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1475</v>
+        <v>970</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -14997,23 +15129,23 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I8" t="n">
-        <v>11.9</v>
+        <v>21.8</v>
       </c>
       <c r="J8" t="n">
-        <v>0.36</v>
+        <v>0.75</v>
       </c>
       <c r="K8" t="n">
-        <v>1450</v>
+        <v>1060</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.69</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -15022,12 +15154,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>-1.69</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -15036,37 +15168,41 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>404</v>
+        <v>144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>77</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="I9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.73</v>
+      </c>
       <c r="K9" t="n">
-        <v>394</v>
+        <v>154.5</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.48</v>
+        <v>7.29</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -15075,12 +15211,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>-2.48</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -15089,37 +15225,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>407</v>
+        <v>103</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>62</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="I10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.73</v>
+      </c>
       <c r="K10" t="n">
-        <v>396.5</v>
+        <v>110</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.58</v>
+        <v>6.8</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -15128,12 +15268,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-2.58</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -15142,20 +15282,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>246.5</v>
+        <v>87.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -15164,19 +15304,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I11" t="n">
-        <v>15.3</v>
+        <v>8.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1.16</v>
+        <v>0.36</v>
       </c>
       <c r="K11" t="n">
-        <v>237</v>
+        <v>93</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.85</v>
+        <v>5.92</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -15185,12 +15325,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-3.85</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -15199,16 +15339,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>43.9</v>
+        <v>4635</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -15217,23 +15357,23 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="I12" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.84</v>
+        <v>0.26</v>
       </c>
       <c r="K12" t="n">
-        <v>41.45</v>
+        <v>4900</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.58</v>
+        <v>5.72</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -15242,12 +15382,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-5.58</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -15256,20 +15396,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>151.5</v>
+        <v>1175</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -15278,19 +15418,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
-        <v>14.7</v>
+        <v>25</v>
       </c>
       <c r="J13" t="n">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="K13" t="n">
-        <v>143</v>
+        <v>1235</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.61</v>
+        <v>5.11</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -15299,12 +15439,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-5.61</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -15313,16 +15453,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>78.3</v>
+        <v>404</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -15335,15 +15475,15 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>73.8</v>
+        <v>421</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.75</v>
+        <v>4.21</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -15352,12 +15492,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-5.75</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -15366,37 +15506,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>23.95</v>
+        <v>42.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>77</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.84</v>
+      </c>
       <c r="K15" t="n">
-        <v>22.55</v>
+        <v>43.25</v>
       </c>
       <c r="L15" t="n">
-        <v>-5.85</v>
+        <v>2</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -15405,7 +15549,7 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-5.85</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -15419,41 +15563,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>64.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="I16" t="n">
-        <v>21.3</v>
+        <v>12.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1.35</v>
+        <v>0.73</v>
       </c>
       <c r="K16" t="n">
-        <v>60.3</v>
+        <v>99.3</v>
       </c>
       <c r="L16" t="n">
-        <v>-6.22</v>
+        <v>1.95</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -15462,7 +15606,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-6.22</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="17">
@@ -15476,20 +15620,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>189</v>
+        <v>119.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -15498,19 +15642,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I17" t="n">
-        <v>11.4</v>
+        <v>15</v>
       </c>
       <c r="J17" t="n">
-        <v>0.59</v>
+        <v>1.26</v>
       </c>
       <c r="K17" t="n">
-        <v>176</v>
+        <v>120.5</v>
       </c>
       <c r="L17" t="n">
-        <v>-6.88</v>
+        <v>0.84</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -15519,12 +15663,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-6.88</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -15533,16 +15677,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2370</v>
+        <v>178.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -15555,19 +15699,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I18" t="n">
-        <v>23.6</v>
+        <v>11.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.78</v>
+        <v>0.59</v>
       </c>
       <c r="K18" t="n">
-        <v>2200</v>
+        <v>179.5</v>
       </c>
       <c r="L18" t="n">
-        <v>-7.17</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -15576,12 +15720,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-7.17</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -15590,20 +15734,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>93</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -15612,19 +15756,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>21.3</v>
       </c>
       <c r="J19" t="n">
-        <v>0.36</v>
+        <v>1.35</v>
       </c>
       <c r="K19" t="n">
-        <v>86.3</v>
+        <v>65.5</v>
       </c>
       <c r="L19" t="n">
-        <v>-7.2</v>
+        <v>0.15</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -15633,12 +15777,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-7.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -15647,16 +15791,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>115.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -15665,23 +15809,23 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="I20" t="n">
-        <v>10.7</v>
+        <v>6.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.76</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>106.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-7.79</v>
+        <v>-0.66</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -15690,12 +15834,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-7.79</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -15704,16 +15848,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>91.2</v>
+        <v>123</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -15726,19 +15870,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I21" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="K21" t="n">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="L21" t="n">
-        <v>-7.89</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -15747,7 +15891,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-7.89</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -16262,7 +16406,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -16271,16 +16415,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2340</v>
+        <v>373</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -16289,23 +16433,23 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="I9" t="n">
-        <v>30.7</v>
+        <v>13.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.82</v>
+        <v>0.49</v>
       </c>
       <c r="K9" t="n">
-        <v>1910</v>
+        <v>302</v>
       </c>
       <c r="L9" t="n">
-        <v>-18.38</v>
+        <v>-19.03</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -16314,12 +16458,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>-18.38</v>
+        <v>-19.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -16328,16 +16472,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>367</v>
+        <v>34.15</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -16346,23 +16490,23 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="I10" t="n">
-        <v>13.2</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="K10" t="n">
-        <v>309.5</v>
+        <v>27.75</v>
       </c>
       <c r="L10" t="n">
-        <v>-15.67</v>
+        <v>-18.74</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -16371,12 +16515,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-15.67</v>
+        <v>-18.74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46205</v>
+        <v>46202</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -16385,37 +16529,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>37.6</v>
+        <v>2340</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>75</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="I11" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.82</v>
+      </c>
       <c r="K11" t="n">
-        <v>31.95</v>
+        <v>1910</v>
       </c>
       <c r="L11" t="n">
-        <v>-15.03</v>
+        <v>-18.38</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -16424,12 +16572,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-15.03</v>
+        <v>-18.38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -16438,41 +16586,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>996</v>
+        <v>475.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
-        <v>38.8</v>
+        <v>21.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
       <c r="K12" t="n">
-        <v>847</v>
+        <v>397.5</v>
       </c>
       <c r="L12" t="n">
-        <v>-14.96</v>
+        <v>-16.4</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -16481,7 +16629,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-14.96</v>
+        <v>-16.4</v>
       </c>
     </row>
     <row r="13">
@@ -16495,16 +16643,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>995</v>
+        <v>367</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -16513,23 +16661,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="I13" t="n">
-        <v>21.8</v>
+        <v>13.2</v>
       </c>
       <c r="J13" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="K13" t="n">
-        <v>855</v>
+        <v>309.5</v>
       </c>
       <c r="L13" t="n">
-        <v>-14.07</v>
+        <v>-15.67</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -16538,12 +16686,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-14.07</v>
+        <v>-15.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -16552,41 +16700,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>114.5</v>
+        <v>37.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>94</v>
-      </c>
-      <c r="I14" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.64</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>99.3</v>
+        <v>31.95</v>
       </c>
       <c r="L14" t="n">
-        <v>-13.28</v>
+        <v>-15.03</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -16595,12 +16739,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-13.28</v>
+        <v>-15.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46205</v>
+        <v>46202</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -16609,20 +16753,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>134</v>
+        <v>996</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -16631,15 +16775,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>78</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="I15" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.03</v>
+      </c>
       <c r="K15" t="n">
-        <v>119</v>
+        <v>847</v>
       </c>
       <c r="L15" t="n">
-        <v>-11.19</v>
+        <v>-14.96</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -16648,12 +16796,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-11.19</v>
+        <v>-14.96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -16662,16 +16810,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>138</v>
+        <v>66.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -16680,23 +16828,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I16" t="n">
-        <v>14.1</v>
+        <v>10.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="K16" t="n">
-        <v>124.5</v>
+        <v>56.8</v>
       </c>
       <c r="L16" t="n">
-        <v>-9.779999999999999</v>
+        <v>-14.2</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -16705,7 +16853,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-9.779999999999999</v>
+        <v>-14.2</v>
       </c>
     </row>
     <row r="17">
@@ -16719,16 +16867,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>40.55</v>
+        <v>995</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -16741,19 +16889,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>21.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="K17" t="n">
-        <v>36.7</v>
+        <v>855</v>
       </c>
       <c r="L17" t="n">
-        <v>-9.49</v>
+        <v>-14.07</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -16762,7 +16910,7 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-9.49</v>
+        <v>-14.07</v>
       </c>
     </row>
     <row r="18">
@@ -16776,16 +16924,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2300</v>
+        <v>114.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -16798,19 +16946,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="I18" t="n">
-        <v>24.6</v>
+        <v>12.3</v>
       </c>
       <c r="J18" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="K18" t="n">
-        <v>2095</v>
+        <v>99.3</v>
       </c>
       <c r="L18" t="n">
-        <v>-8.91</v>
+        <v>-13.28</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -16819,12 +16967,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-8.91</v>
+        <v>-13.28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -16833,16 +16981,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>539</v>
+        <v>360</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -16855,19 +17003,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
-        <v>17.9</v>
+        <v>27.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="K19" t="n">
-        <v>491.5</v>
+        <v>316.5</v>
       </c>
       <c r="L19" t="n">
-        <v>-8.81</v>
+        <v>-12.08</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -16876,12 +17024,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-8.81</v>
+        <v>-12.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -16890,16 +17038,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>91.2</v>
+        <v>147</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -16908,23 +17056,23 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I20" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="J20" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="K20" t="n">
-        <v>84</v>
+        <v>129.5</v>
       </c>
       <c r="L20" t="n">
-        <v>-7.89</v>
+        <v>-11.9</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -16933,12 +17081,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-7.89</v>
+        <v>-11.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -16947,41 +17095,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>115.5</v>
+        <v>79.3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>94</v>
-      </c>
-      <c r="I21" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.76</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>106.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-7.79</v>
+        <v>-11.6</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -16990,7 +17134,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-7.79</v>
+        <v>-11.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>-5.35</v>
+        <v>-4.94</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.88</v>
+        <v>-5.85</v>
       </c>
       <c r="F2" t="n">
         <v>33.15</v>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.35</v>
+        <v>-4.94</v>
       </c>
     </row>
   </sheetData>
@@ -9444,8 +9444,12 @@
       <c r="J172" t="n">
         <v>0.26</v>
       </c>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
+      <c r="K172" t="n">
+        <v>6265</v>
+      </c>
+      <c r="L172" t="n">
+        <v>24.06</v>
+      </c>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
@@ -14821,7 +14825,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -14830,16 +14834,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>155.5</v>
+        <v>5050</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -14848,23 +14852,23 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="K3" t="n">
-        <v>189.5</v>
+        <v>6265</v>
       </c>
       <c r="L3" t="n">
-        <v>21.86</v>
+        <v>24.06</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -14873,7 +14877,7 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>21.86</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="4">
@@ -14887,16 +14891,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2450</v>
+        <v>155.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -14905,23 +14909,23 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="I4" t="n">
-        <v>24.6</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>0.66</v>
+        <v>0.31</v>
       </c>
       <c r="K4" t="n">
-        <v>2940</v>
+        <v>189.5</v>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>21.86</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -14930,12 +14934,12 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -14944,37 +14948,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>193.5</v>
+        <v>2450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>69</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I5" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.66</v>
+      </c>
       <c r="K5" t="n">
-        <v>222.5</v>
+        <v>2940</v>
       </c>
       <c r="L5" t="n">
-        <v>14.99</v>
+        <v>20</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -14983,12 +14991,12 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>14.99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -14997,20 +15005,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>237</v>
+        <v>193.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -15019,19 +15027,15 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>77</v>
-      </c>
-      <c r="I6" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.16</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>264.5</v>
+        <v>222.5</v>
       </c>
       <c r="L6" t="n">
-        <v>11.6</v>
+        <v>14.99</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -15040,12 +15044,12 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>11.6</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -15054,41 +15058,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>154.5</v>
+        <v>237</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>15.3</v>
       </c>
       <c r="J7" t="n">
-        <v>0.31</v>
+        <v>1.16</v>
       </c>
       <c r="K7" t="n">
-        <v>169.5</v>
+        <v>264.5</v>
       </c>
       <c r="L7" t="n">
-        <v>9.710000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -15097,12 +15101,12 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>9.710000000000001</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -15111,16 +15115,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>970</v>
+        <v>154.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -15129,23 +15133,23 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="I8" t="n">
-        <v>21.8</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>0.75</v>
+        <v>0.31</v>
       </c>
       <c r="K8" t="n">
-        <v>1060</v>
+        <v>169.5</v>
       </c>
       <c r="L8" t="n">
-        <v>9.279999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -15154,7 +15158,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>9.279999999999999</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -15168,16 +15172,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>144</v>
+        <v>970</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -15190,19 +15194,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I9" t="n">
-        <v>14.1</v>
+        <v>21.8</v>
       </c>
       <c r="J9" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="K9" t="n">
-        <v>154.5</v>
+        <v>1060</v>
       </c>
       <c r="L9" t="n">
-        <v>7.29</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -15211,7 +15215,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>7.29</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -15225,16 +15229,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -15247,19 +15251,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
-        <v>12.4</v>
+        <v>14.1</v>
       </c>
       <c r="J10" t="n">
         <v>0.73</v>
       </c>
       <c r="K10" t="n">
-        <v>110</v>
+        <v>154.5</v>
       </c>
       <c r="L10" t="n">
-        <v>6.8</v>
+        <v>7.29</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -15268,7 +15272,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>6.8</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="11">
@@ -15282,16 +15286,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>87.8</v>
+        <v>103</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -15300,23 +15304,23 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="I11" t="n">
-        <v>8.6</v>
+        <v>12.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="K11" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="L11" t="n">
-        <v>5.92</v>
+        <v>6.8</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -15325,12 +15329,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>5.92</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -15339,16 +15343,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4635</v>
+        <v>87.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -15361,19 +15365,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="I12" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="K12" t="n">
-        <v>4900</v>
+        <v>93</v>
       </c>
       <c r="L12" t="n">
-        <v>5.72</v>
+        <v>5.92</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -15382,12 +15386,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>5.72</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46210</v>
+        <v>46203</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -15396,16 +15400,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1175</v>
+        <v>4635</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -15414,23 +15418,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I13" t="n">
-        <v>25</v>
+        <v>9.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.67</v>
+        <v>0.26</v>
       </c>
       <c r="K13" t="n">
-        <v>1235</v>
+        <v>4900</v>
       </c>
       <c r="L13" t="n">
-        <v>5.11</v>
+        <v>5.72</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -15439,7 +15443,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>5.11</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="14">
@@ -15453,37 +15457,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>404</v>
+        <v>1175</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>77</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="I14" t="n">
+        <v>25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.67</v>
+      </c>
       <c r="K14" t="n">
-        <v>421</v>
+        <v>1235</v>
       </c>
       <c r="L14" t="n">
-        <v>4.21</v>
+        <v>5.11</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -15492,7 +15500,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>4.21</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="15">
@@ -15506,41 +15514,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>42.4</v>
+        <v>404</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>92</v>
-      </c>
-      <c r="I15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.84</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>43.25</v>
+        <v>421</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>4.21</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -15549,12 +15553,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -15563,16 +15567,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>97.40000000000001</v>
+        <v>42.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -15585,19 +15589,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I16" t="n">
-        <v>12.4</v>
+        <v>7.6</v>
       </c>
       <c r="J16" t="n">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="K16" t="n">
-        <v>99.3</v>
+        <v>43.25</v>
       </c>
       <c r="L16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -15606,7 +15610,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -15620,20 +15624,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>119.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -15642,19 +15646,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I17" t="n">
-        <v>15</v>
+        <v>12.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1.26</v>
+        <v>0.73</v>
       </c>
       <c r="K17" t="n">
-        <v>120.5</v>
+        <v>99.3</v>
       </c>
       <c r="L17" t="n">
-        <v>0.84</v>
+        <v>1.95</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -15663,12 +15667,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>0.84</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -15677,20 +15681,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>178.5</v>
+        <v>119.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -15699,19 +15703,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I18" t="n">
-        <v>11.4</v>
+        <v>15</v>
       </c>
       <c r="J18" t="n">
-        <v>0.59</v>
+        <v>1.26</v>
       </c>
       <c r="K18" t="n">
-        <v>179.5</v>
+        <v>120.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -15720,7 +15724,7 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="19">
@@ -15734,41 +15738,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65.40000000000001</v>
+        <v>178.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="I19" t="n">
-        <v>21.3</v>
+        <v>11.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.35</v>
+        <v>0.59</v>
       </c>
       <c r="K19" t="n">
-        <v>65.5</v>
+        <v>179.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.15</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -15777,7 +15781,7 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>0.15</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -15791,20 +15795,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>75.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -15813,19 +15817,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I20" t="n">
-        <v>6.8</v>
+        <v>21.3</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="K20" t="n">
-        <v>74.90000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.66</v>
+        <v>0.15</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -15834,7 +15838,7 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-0.66</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="21">
@@ -15848,41 +15852,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>123</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I21" t="n">
-        <v>15</v>
+        <v>6.8</v>
       </c>
       <c r="J21" t="n">
-        <v>1.26</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>122</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.66</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -15891,7 +15895,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R277"/>
+  <dimension ref="A1:R311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14658,6 +14658,1690 @@
       <c r="P277" t="inlineStr"/>
       <c r="Q277" t="inlineStr"/>
       <c r="R277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>147</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>97</v>
+      </c>
+      <c r="I278" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J278" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr"/>
+      <c r="P278" t="inlineStr"/>
+      <c r="Q278" t="inlineStr"/>
+      <c r="R278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>514</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>96</v>
+      </c>
+      <c r="I279" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J279" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
+      <c r="P279" t="inlineStr"/>
+      <c r="Q279" t="inlineStr"/>
+      <c r="R279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>91</v>
+      </c>
+      <c r="I280" t="n">
+        <v>15</v>
+      </c>
+      <c r="J280" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" t="inlineStr"/>
+      <c r="P280" t="inlineStr"/>
+      <c r="Q280" t="inlineStr"/>
+      <c r="R280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>309</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>90</v>
+      </c>
+      <c r="I281" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J281" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr"/>
+      <c r="P281" t="inlineStr"/>
+      <c r="Q281" t="inlineStr"/>
+      <c r="R281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>86</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H282" t="n">
+        <v>87</v>
+      </c>
+      <c r="I282" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J282" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr"/>
+      <c r="P282" t="inlineStr"/>
+      <c r="Q282" t="inlineStr"/>
+      <c r="R282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H283" t="n">
+        <v>77</v>
+      </c>
+      <c r="I283" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J283" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" t="inlineStr"/>
+      <c r="P283" t="inlineStr"/>
+      <c r="Q283" t="inlineStr"/>
+      <c r="R283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H284" t="n">
+        <v>77</v>
+      </c>
+      <c r="I284" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J284" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="inlineStr"/>
+      <c r="Q284" t="inlineStr"/>
+      <c r="R284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H285" t="n">
+        <v>76</v>
+      </c>
+      <c r="I285" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J285" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr"/>
+      <c r="P285" t="inlineStr"/>
+      <c r="Q285" t="inlineStr"/>
+      <c r="R285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>66</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H286" t="n">
+        <v>68</v>
+      </c>
+      <c r="I286" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J286" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="inlineStr"/>
+      <c r="Q286" t="inlineStr"/>
+      <c r="R286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>2765</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H287" t="n">
+        <v>100</v>
+      </c>
+      <c r="I287" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr"/>
+      <c r="P287" t="inlineStr"/>
+      <c r="Q287" t="inlineStr"/>
+      <c r="R287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>808</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H288" t="n">
+        <v>100</v>
+      </c>
+      <c r="I288" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J288" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr"/>
+      <c r="P288" t="inlineStr"/>
+      <c r="Q288" t="inlineStr"/>
+      <c r="R288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>2380</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H289" t="n">
+        <v>100</v>
+      </c>
+      <c r="I289" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr"/>
+      <c r="Q289" t="inlineStr"/>
+      <c r="R289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>109</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H290" t="n">
+        <v>97</v>
+      </c>
+      <c r="I290" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
+      <c r="O290" t="inlineStr"/>
+      <c r="P290" t="inlineStr"/>
+      <c r="Q290" t="inlineStr"/>
+      <c r="R290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H291" t="n">
+        <v>94</v>
+      </c>
+      <c r="I291" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" t="inlineStr"/>
+      <c r="P291" t="inlineStr"/>
+      <c r="Q291" t="inlineStr"/>
+      <c r="R291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H292" t="n">
+        <v>94</v>
+      </c>
+      <c r="I292" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J292" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
+      <c r="O292" t="inlineStr"/>
+      <c r="P292" t="inlineStr"/>
+      <c r="Q292" t="inlineStr"/>
+      <c r="R292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>109</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H293" t="n">
+        <v>94</v>
+      </c>
+      <c r="I293" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="inlineStr"/>
+      <c r="Q293" t="inlineStr"/>
+      <c r="R293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H294" t="n">
+        <v>94</v>
+      </c>
+      <c r="I294" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
+      <c r="O294" t="inlineStr"/>
+      <c r="P294" t="inlineStr"/>
+      <c r="Q294" t="inlineStr"/>
+      <c r="R294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H295" t="n">
+        <v>92</v>
+      </c>
+      <c r="I295" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr"/>
+      <c r="P295" t="inlineStr"/>
+      <c r="Q295" t="inlineStr"/>
+      <c r="R295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>1075</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H296" t="n">
+        <v>90</v>
+      </c>
+      <c r="I296" t="n">
+        <v>25</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
+      <c r="Q296" t="inlineStr"/>
+      <c r="R296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>401.5</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H297" t="n">
+        <v>90</v>
+      </c>
+      <c r="I297" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J297" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" t="inlineStr"/>
+      <c r="P297" t="inlineStr"/>
+      <c r="Q297" t="inlineStr"/>
+      <c r="R297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H298" t="n">
+        <v>90</v>
+      </c>
+      <c r="I298" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
+      <c r="O298" t="inlineStr"/>
+      <c r="P298" t="inlineStr"/>
+      <c r="Q298" t="inlineStr"/>
+      <c r="R298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H299" t="n">
+        <v>84</v>
+      </c>
+      <c r="I299" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" t="inlineStr"/>
+      <c r="P299" t="inlineStr"/>
+      <c r="Q299" t="inlineStr"/>
+      <c r="R299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>2165</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H300" t="n">
+        <v>80</v>
+      </c>
+      <c r="I300" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J300" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr"/>
+      <c r="O300" t="inlineStr"/>
+      <c r="P300" t="inlineStr"/>
+      <c r="Q300" t="inlineStr"/>
+      <c r="R300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H301" t="n">
+        <v>80</v>
+      </c>
+      <c r="I301" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr"/>
+      <c r="O301" t="inlineStr"/>
+      <c r="P301" t="inlineStr"/>
+      <c r="Q301" t="inlineStr"/>
+      <c r="R301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H302" t="n">
+        <v>79</v>
+      </c>
+      <c r="I302" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr"/>
+      <c r="P302" t="inlineStr"/>
+      <c r="Q302" t="inlineStr"/>
+      <c r="R302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H303" t="n">
+        <v>78</v>
+      </c>
+      <c r="I303" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J303" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr"/>
+      <c r="O303" t="inlineStr"/>
+      <c r="P303" t="inlineStr"/>
+      <c r="Q303" t="inlineStr"/>
+      <c r="R303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H304" t="n">
+        <v>77</v>
+      </c>
+      <c r="I304" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J304" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
+      <c r="O304" t="inlineStr"/>
+      <c r="P304" t="inlineStr"/>
+      <c r="Q304" t="inlineStr"/>
+      <c r="R304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>313.5</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H305" t="n">
+        <v>65</v>
+      </c>
+      <c r="I305" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
+      <c r="O305" t="inlineStr"/>
+      <c r="P305" t="inlineStr"/>
+      <c r="Q305" t="inlineStr"/>
+      <c r="R305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>193</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H306" t="n">
+        <v>62</v>
+      </c>
+      <c r="I306" t="n">
+        <v>10</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr"/>
+      <c r="P306" t="inlineStr"/>
+      <c r="Q306" t="inlineStr"/>
+      <c r="R306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H307" t="n">
+        <v>60</v>
+      </c>
+      <c r="I307" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J307" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
+      <c r="O307" t="inlineStr"/>
+      <c r="P307" t="inlineStr"/>
+      <c r="Q307" t="inlineStr"/>
+      <c r="R307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H308" t="n">
+        <v>79</v>
+      </c>
+      <c r="I308" t="inlineStr"/>
+      <c r="J308" t="inlineStr"/>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="inlineStr"/>
+      <c r="Q308" t="inlineStr"/>
+      <c r="R308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>411</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H309" t="n">
+        <v>77</v>
+      </c>
+      <c r="I309" t="inlineStr"/>
+      <c r="J309" t="inlineStr"/>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
+      <c r="O309" t="inlineStr"/>
+      <c r="P309" t="inlineStr"/>
+      <c r="Q309" t="inlineStr"/>
+      <c r="R309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H310" t="n">
+        <v>77</v>
+      </c>
+      <c r="I310" t="inlineStr"/>
+      <c r="J310" t="inlineStr"/>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="inlineStr"/>
+      <c r="Q310" t="inlineStr"/>
+      <c r="R310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H311" t="n">
+        <v>69</v>
+      </c>
+      <c r="I311" t="inlineStr"/>
+      <c r="J311" t="inlineStr"/>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr"/>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr"/>
+      <c r="O311" t="inlineStr"/>
+      <c r="P311" t="inlineStr"/>
+      <c r="Q311" t="inlineStr"/>
+      <c r="R311" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R311"/>
+  <dimension ref="A1:R312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16342,6 +16342,56 @@
       <c r="P311" t="inlineStr"/>
       <c r="Q311" t="inlineStr"/>
       <c r="R311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>6025</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H312" t="n">
+        <v>65</v>
+      </c>
+      <c r="I312" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J312" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr"/>
+      <c r="O312" t="inlineStr"/>
+      <c r="P312" t="inlineStr"/>
+      <c r="Q312" t="inlineStr"/>
+      <c r="R312" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,19 +468,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>30.8</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.94</v>
+        <v>-3.05</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.85</v>
+        <v>-5.34</v>
       </c>
       <c r="F2" t="n">
-        <v>33.15</v>
+        <v>49.42</v>
       </c>
       <c r="G2" t="n">
         <v>-32.03</v>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>30.8</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.94</v>
+        <v>-3.05</v>
       </c>
     </row>
   </sheetData>
@@ -9498,8 +9498,12 @@
       <c r="J173" t="n">
         <v>1.29</v>
       </c>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
+      <c r="K173" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="L173" t="n">
+        <v>-4.14</v>
+      </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
@@ -9548,8 +9552,12 @@
       <c r="J174" t="n">
         <v>1.11</v>
       </c>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
+      <c r="K174" t="n">
+        <v>521</v>
+      </c>
+      <c r="L174" t="n">
+        <v>-6.29</v>
+      </c>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
@@ -9598,8 +9606,12 @@
       <c r="J175" t="n">
         <v>1.26</v>
       </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
+      <c r="K175" t="n">
+        <v>123</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0.41</v>
+      </c>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
@@ -9648,8 +9660,12 @@
       <c r="J176" t="n">
         <v>1.22</v>
       </c>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
+      <c r="K176" t="n">
+        <v>307</v>
+      </c>
+      <c r="L176" t="n">
+        <v>-8.220000000000001</v>
+      </c>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
@@ -9698,8 +9714,12 @@
       <c r="J177" t="n">
         <v>1.36</v>
       </c>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
+      <c r="K177" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="L177" t="n">
+        <v>-7.59</v>
+      </c>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
@@ -9748,8 +9768,12 @@
       <c r="J178" t="n">
         <v>1.11</v>
       </c>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
+      <c r="K178" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="L178" t="n">
+        <v>-20.57</v>
+      </c>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
@@ -9798,8 +9822,12 @@
       <c r="J179" t="n">
         <v>1.16</v>
       </c>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
+      <c r="K179" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="L179" t="n">
+        <v>8.58</v>
+      </c>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
@@ -9848,8 +9876,12 @@
       <c r="J180" t="n">
         <v>1.03</v>
       </c>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
+      <c r="K180" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L180" t="n">
+        <v>-8.6</v>
+      </c>
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
@@ -9898,8 +9930,12 @@
       <c r="J181" t="n">
         <v>1.35</v>
       </c>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
+      <c r="K181" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="L181" t="n">
+        <v>14.4</v>
+      </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
@@ -9948,8 +9984,12 @@
       <c r="J182" t="n">
         <v>0.66</v>
       </c>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
+      <c r="K182" t="n">
+        <v>3235</v>
+      </c>
+      <c r="L182" t="n">
+        <v>49.42</v>
+      </c>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
@@ -9998,8 +10038,12 @@
       <c r="J183" t="n">
         <v>0.4</v>
       </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
+      <c r="K183" t="n">
+        <v>798</v>
+      </c>
+      <c r="L183" t="n">
+        <v>-10.84</v>
+      </c>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
@@ -10048,8 +10092,12 @@
       <c r="J184" t="n">
         <v>0.78</v>
       </c>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
+      <c r="K184" t="n">
+        <v>2395</v>
+      </c>
+      <c r="L184" t="n">
+        <v>-1.84</v>
+      </c>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
@@ -10098,8 +10146,12 @@
       <c r="J185" t="n">
         <v>0.73</v>
       </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
+      <c r="K185" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="L185" t="n">
+        <v>8.25</v>
+      </c>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
@@ -10148,8 +10200,12 @@
       <c r="J186" t="n">
         <v>0.64</v>
       </c>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
+      <c r="K186" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="L186" t="n">
+        <v>-6.41</v>
+      </c>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
@@ -10198,8 +10254,12 @@
       <c r="J187" t="n">
         <v>0.42</v>
       </c>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
+      <c r="K187" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="L187" t="n">
+        <v>-3.14</v>
+      </c>
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
@@ -10248,8 +10308,12 @@
       <c r="J188" t="n">
         <v>0.76</v>
       </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
+      <c r="K188" t="n">
+        <v>107</v>
+      </c>
+      <c r="L188" t="n">
+        <v>-4.46</v>
+      </c>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
@@ -10298,8 +10362,12 @@
       <c r="J189" t="n">
         <v>0.59</v>
       </c>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
+      <c r="K189" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="L189" t="n">
+        <v>3.11</v>
+      </c>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
@@ -10348,8 +10416,12 @@
       <c r="J190" t="n">
         <v>0.84</v>
       </c>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
+      <c r="K190" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="L190" t="n">
+        <v>-5.34</v>
+      </c>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
@@ -10398,8 +10470,12 @@
       <c r="J191" t="n">
         <v>0.67</v>
       </c>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
+      <c r="K191" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L191" t="n">
+        <v>-12.66</v>
+      </c>
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
@@ -10448,8 +10524,12 @@
       <c r="J192" t="n">
         <v>0.92</v>
       </c>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
+      <c r="K192" t="n">
+        <v>488</v>
+      </c>
+      <c r="L192" t="n">
+        <v>14.55</v>
+      </c>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
@@ -10498,8 +10578,12 @@
       <c r="J193" t="n">
         <v>0.73</v>
       </c>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
+      <c r="K193" t="n">
+        <v>146</v>
+      </c>
+      <c r="L193" t="n">
+        <v>5.04</v>
+      </c>
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
@@ -10548,8 +10632,12 @@
       <c r="J194" t="n">
         <v>0.2</v>
       </c>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
+      <c r="K194" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="L194" t="n">
+        <v>8.31</v>
+      </c>
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
@@ -10598,8 +10686,12 @@
       <c r="J195" t="n">
         <v>0.82</v>
       </c>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
+      <c r="K195" t="n">
+        <v>2300</v>
+      </c>
+      <c r="L195" t="n">
+        <v>-1.71</v>
+      </c>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
@@ -10648,8 +10740,12 @@
       <c r="J196" t="n">
         <v>0.75</v>
       </c>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
+      <c r="K196" t="n">
+        <v>1010</v>
+      </c>
+      <c r="L196" t="n">
+        <v>12.72</v>
+      </c>
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
@@ -10698,8 +10794,12 @@
       <c r="J197" t="n">
         <v>0.36</v>
       </c>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
+      <c r="K197" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0.23</v>
+      </c>
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
@@ -10748,8 +10848,12 @@
       <c r="J198" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
+      <c r="K198" t="n">
+        <v>61</v>
+      </c>
+      <c r="L198" t="n">
+        <v>-16.09</v>
+      </c>
       <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
@@ -10798,8 +10902,12 @@
       <c r="J199" t="n">
         <v>0.71</v>
       </c>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
+      <c r="K199" t="n">
+        <v>55</v>
+      </c>
+      <c r="L199" t="n">
+        <v>-9.69</v>
+      </c>
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
@@ -10848,8 +10956,12 @@
       <c r="J200" t="n">
         <v>0.49</v>
       </c>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
+      <c r="K200" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="L200" t="n">
+        <v>-14.04</v>
+      </c>
       <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr"/>
@@ -10898,8 +11010,12 @@
       <c r="J201" t="n">
         <v>0.31</v>
       </c>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
+      <c r="K201" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="L201" t="n">
+        <v>32.99</v>
+      </c>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
@@ -10948,8 +11064,12 @@
       <c r="J202" t="n">
         <v>0.36</v>
       </c>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
+      <c r="K202" t="n">
+        <v>1380</v>
+      </c>
+      <c r="L202" t="n">
+        <v>-8.91</v>
+      </c>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
@@ -10994,8 +11114,12 @@
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
+      <c r="K203" t="n">
+        <v>70</v>
+      </c>
+      <c r="L203" t="n">
+        <v>3.24</v>
+      </c>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
@@ -11040,8 +11164,12 @@
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
+      <c r="K204" t="n">
+        <v>402</v>
+      </c>
+      <c r="L204" t="n">
+        <v>-1.47</v>
+      </c>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
@@ -11086,8 +11214,12 @@
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
+      <c r="K205" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="L205" t="n">
+        <v>-2.51</v>
+      </c>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
@@ -11132,8 +11264,12 @@
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
+      <c r="K206" t="n">
+        <v>233</v>
+      </c>
+      <c r="L206" t="n">
+        <v>28.37</v>
+      </c>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
@@ -16506,7 +16642,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -16515,37 +16651,41 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185.5</v>
+        <v>2165</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>69</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I2" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.66</v>
+      </c>
       <c r="K2" t="n">
-        <v>247</v>
+        <v>3235</v>
       </c>
       <c r="L2" t="n">
-        <v>33.15</v>
+        <v>49.42</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -16554,12 +16694,12 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>33.15</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -16568,20 +16708,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5050</v>
+        <v>185.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -16590,19 +16730,15 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65</v>
-      </c>
-      <c r="I3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.26</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>6265</v>
+        <v>247</v>
       </c>
       <c r="L3" t="n">
-        <v>24.06</v>
+        <v>33.15</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -16611,12 +16747,12 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>24.06</v>
+        <v>33.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -16634,7 +16770,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>155.5</v>
+        <v>145.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -16656,10 +16792,10 @@
         <v>0.31</v>
       </c>
       <c r="K4" t="n">
-        <v>189.5</v>
+        <v>193.5</v>
       </c>
       <c r="L4" t="n">
-        <v>21.86</v>
+        <v>32.99</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -16668,12 +16804,12 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>21.86</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -16682,41 +16818,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2450</v>
+        <v>181.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
-      </c>
-      <c r="I5" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.66</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>2940</v>
+        <v>233</v>
       </c>
       <c r="L5" t="n">
-        <v>20</v>
+        <v>28.37</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -16725,12 +16857,12 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46202</v>
+        <v>46211</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -16739,20 +16871,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>193.5</v>
+        <v>5050</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -16761,15 +16893,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>69</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.26</v>
+      </c>
       <c r="K6" t="n">
-        <v>222.5</v>
+        <v>6265</v>
       </c>
       <c r="L6" t="n">
-        <v>14.99</v>
+        <v>24.06</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -16778,7 +16914,7 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>14.99</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="7">
@@ -16792,41 +16928,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>237</v>
+        <v>155.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="I7" t="n">
-        <v>15.3</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>1.16</v>
+        <v>0.31</v>
       </c>
       <c r="K7" t="n">
-        <v>264.5</v>
+        <v>189.5</v>
       </c>
       <c r="L7" t="n">
-        <v>11.6</v>
+        <v>21.86</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -16835,12 +16971,12 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>11.6</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -16849,16 +16985,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>154.5</v>
+        <v>2450</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -16867,23 +17003,23 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>24.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.31</v>
+        <v>0.66</v>
       </c>
       <c r="K8" t="n">
-        <v>169.5</v>
+        <v>2940</v>
       </c>
       <c r="L8" t="n">
-        <v>9.710000000000001</v>
+        <v>20</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -16892,12 +17028,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>9.710000000000001</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -16906,41 +17042,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>970</v>
+        <v>193.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>80</v>
-      </c>
-      <c r="I9" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.75</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>1060</v>
+        <v>222.5</v>
       </c>
       <c r="L9" t="n">
-        <v>9.279999999999999</v>
+        <v>14.99</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -16949,12 +17081,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>9.279999999999999</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -16963,16 +17095,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>144</v>
+        <v>426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -16988,16 +17120,16 @@
         <v>90</v>
       </c>
       <c r="I10" t="n">
-        <v>14.1</v>
+        <v>21.2</v>
       </c>
       <c r="J10" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="K10" t="n">
-        <v>154.5</v>
+        <v>488</v>
       </c>
       <c r="L10" t="n">
-        <v>7.29</v>
+        <v>14.55</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -17006,12 +17138,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>7.29</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -17020,41 +17152,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103</v>
+        <v>61.1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="I11" t="n">
-        <v>12.4</v>
+        <v>21.3</v>
       </c>
       <c r="J11" t="n">
-        <v>0.73</v>
+        <v>1.35</v>
       </c>
       <c r="K11" t="n">
-        <v>110</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>6.8</v>
+        <v>14.4</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -17063,12 +17195,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>6.8</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -17077,16 +17209,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>87.8</v>
+        <v>896</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -17095,23 +17227,23 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I12" t="n">
-        <v>8.6</v>
+        <v>21.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.36</v>
+        <v>0.75</v>
       </c>
       <c r="K12" t="n">
-        <v>93</v>
+        <v>1010</v>
       </c>
       <c r="L12" t="n">
-        <v>5.92</v>
+        <v>12.72</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -17120,12 +17252,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>5.92</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46203</v>
+        <v>46210</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -17134,20 +17266,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4635</v>
+        <v>237</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -17156,19 +17288,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="I13" t="n">
-        <v>9.6</v>
+        <v>15.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0.26</v>
+        <v>1.16</v>
       </c>
       <c r="K13" t="n">
-        <v>4900</v>
+        <v>264.5</v>
       </c>
       <c r="L13" t="n">
-        <v>5.72</v>
+        <v>11.6</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -17177,12 +17309,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>5.72</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -17191,16 +17323,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1175</v>
+        <v>154.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -17209,23 +17341,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J14" t="n">
-        <v>0.67</v>
+        <v>0.31</v>
       </c>
       <c r="K14" t="n">
-        <v>1235</v>
+        <v>169.5</v>
       </c>
       <c r="L14" t="n">
-        <v>5.11</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -17234,7 +17366,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>5.11</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -17248,37 +17380,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>404</v>
+        <v>970</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>77</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="I15" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.75</v>
+      </c>
       <c r="K15" t="n">
-        <v>421</v>
+        <v>1060</v>
       </c>
       <c r="L15" t="n">
-        <v>4.21</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -17287,12 +17423,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>4.21</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -17301,41 +17437,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>42.4</v>
+        <v>239</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I16" t="n">
-        <v>7.6</v>
+        <v>15.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.84</v>
+        <v>1.16</v>
       </c>
       <c r="K16" t="n">
-        <v>43.25</v>
+        <v>259.5</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>8.58</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -17344,12 +17480,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -17358,16 +17494,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>97.40000000000001</v>
+        <v>38.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -17380,19 +17516,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="I17" t="n">
-        <v>12.4</v>
+        <v>6.2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.73</v>
+        <v>0.2</v>
       </c>
       <c r="K17" t="n">
-        <v>99.3</v>
+        <v>41.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.95</v>
+        <v>8.31</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -17401,12 +17537,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>1.95</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -17415,20 +17551,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>119.5</v>
+        <v>103</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -17437,19 +17573,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>12.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1.26</v>
+        <v>0.73</v>
       </c>
       <c r="K18" t="n">
-        <v>120.5</v>
+        <v>111.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0.84</v>
+        <v>8.25</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -17458,7 +17594,7 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>0.84</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="19">
@@ -17472,16 +17608,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>178.5</v>
+        <v>144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -17494,19 +17630,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
-        <v>11.4</v>
+        <v>14.1</v>
       </c>
       <c r="J19" t="n">
-        <v>0.59</v>
+        <v>0.73</v>
       </c>
       <c r="K19" t="n">
-        <v>179.5</v>
+        <v>154.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5600000000000001</v>
+        <v>7.29</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -17515,7 +17651,7 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>0.5600000000000001</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="20">
@@ -17529,41 +17665,41 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>65.40000000000001</v>
+        <v>103</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="I20" t="n">
-        <v>21.3</v>
+        <v>12.4</v>
       </c>
       <c r="J20" t="n">
-        <v>1.35</v>
+        <v>0.73</v>
       </c>
       <c r="K20" t="n">
-        <v>65.5</v>
+        <v>110</v>
       </c>
       <c r="L20" t="n">
-        <v>0.15</v>
+        <v>6.8</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -17572,7 +17708,7 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>0.15</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="21">
@@ -17586,16 +17722,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>75.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -17608,19 +17744,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I21" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="K21" t="n">
-        <v>74.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.66</v>
+        <v>5.92</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -17629,7 +17765,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-0.66</v>
+        <v>5.92</v>
       </c>
     </row>
   </sheetData>
@@ -17916,7 +18052,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -17925,16 +18061,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>344.5</v>
+        <v>158</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -17943,23 +18079,23 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I5" t="n">
-        <v>27.5</v>
+        <v>16.4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="K5" t="n">
-        <v>277.5</v>
+        <v>125.5</v>
       </c>
       <c r="L5" t="n">
-        <v>-19.45</v>
+        <v>-20.57</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -17968,7 +18104,7 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-19.45</v>
+        <v>-20.57</v>
       </c>
     </row>
     <row r="6">
@@ -17982,20 +18118,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1215</v>
+        <v>344.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -18007,16 +18143,16 @@
         <v>90</v>
       </c>
       <c r="I6" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.67</v>
+        <v>1.22</v>
       </c>
       <c r="K6" t="n">
-        <v>981</v>
+        <v>277.5</v>
       </c>
       <c r="L6" t="n">
-        <v>-19.26</v>
+        <v>-19.45</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -18025,7 +18161,7 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>-19.26</v>
+        <v>-19.45</v>
       </c>
     </row>
     <row r="7">
@@ -18039,41 +18175,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>143</v>
+        <v>1215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I7" t="n">
-        <v>16.4</v>
+        <v>25</v>
       </c>
       <c r="J7" t="n">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="K7" t="n">
-        <v>115.5</v>
+        <v>981</v>
       </c>
       <c r="L7" t="n">
-        <v>-19.23</v>
+        <v>-19.26</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -18082,7 +18218,7 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>-19.23</v>
+        <v>-19.26</v>
       </c>
     </row>
     <row r="8">
@@ -18096,41 +18232,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>34.2</v>
+        <v>143</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>16.4</v>
       </c>
       <c r="J8" t="n">
-        <v>0.42</v>
+        <v>1.11</v>
       </c>
       <c r="K8" t="n">
-        <v>27.65</v>
+        <v>115.5</v>
       </c>
       <c r="L8" t="n">
-        <v>-19.15</v>
+        <v>-19.23</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -18139,12 +18275,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>-19.15</v>
+        <v>-19.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -18153,16 +18289,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>373</v>
+        <v>34.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -18171,23 +18307,23 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="I9" t="n">
-        <v>13.2</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="K9" t="n">
-        <v>302</v>
+        <v>27.65</v>
       </c>
       <c r="L9" t="n">
-        <v>-19.03</v>
+        <v>-19.15</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -18196,7 +18332,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>-19.03</v>
+        <v>-19.15</v>
       </c>
     </row>
     <row r="10">
@@ -18210,16 +18346,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>34.15</v>
+        <v>373</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -18228,23 +18364,23 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>13.2</v>
       </c>
       <c r="J10" t="n">
-        <v>0.42</v>
+        <v>0.49</v>
       </c>
       <c r="K10" t="n">
-        <v>27.75</v>
+        <v>302</v>
       </c>
       <c r="L10" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -18253,12 +18389,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -18267,16 +18403,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2340</v>
+        <v>34.15</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -18289,19 +18425,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I11" t="n">
-        <v>30.7</v>
+        <v>5.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.82</v>
+        <v>0.42</v>
       </c>
       <c r="K11" t="n">
-        <v>1910</v>
+        <v>27.75</v>
       </c>
       <c r="L11" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -18310,12 +18446,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -18324,16 +18460,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>475.5</v>
+        <v>2340</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -18346,19 +18482,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I12" t="n">
-        <v>21.2</v>
+        <v>30.7</v>
       </c>
       <c r="J12" t="n">
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
       <c r="K12" t="n">
-        <v>397.5</v>
+        <v>1910</v>
       </c>
       <c r="L12" t="n">
-        <v>-16.4</v>
+        <v>-18.38</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -18367,12 +18503,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-16.4</v>
+        <v>-18.38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -18381,16 +18517,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>367</v>
+        <v>475.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -18399,23 +18535,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
-        <v>13.2</v>
+        <v>21.2</v>
       </c>
       <c r="J13" t="n">
-        <v>0.49</v>
+        <v>0.92</v>
       </c>
       <c r="K13" t="n">
-        <v>309.5</v>
+        <v>397.5</v>
       </c>
       <c r="L13" t="n">
-        <v>-15.67</v>
+        <v>-16.4</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -18424,12 +18560,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-15.67</v>
+        <v>-16.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46205</v>
+        <v>46218</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -18438,20 +18574,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>37.6</v>
+        <v>72.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -18460,15 +18596,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>75</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="K14" t="n">
-        <v>31.95</v>
+        <v>61</v>
       </c>
       <c r="L14" t="n">
-        <v>-15.03</v>
+        <v>-16.09</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -18477,7 +18617,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-15.03</v>
+        <v>-16.09</v>
       </c>
     </row>
     <row r="15">
@@ -18491,20 +18631,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>996</v>
+        <v>367</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -18513,19 +18653,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="I15" t="n">
-        <v>38.8</v>
+        <v>13.2</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>0.49</v>
       </c>
       <c r="K15" t="n">
-        <v>847</v>
+        <v>309.5</v>
       </c>
       <c r="L15" t="n">
-        <v>-14.96</v>
+        <v>-15.67</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -18534,12 +18674,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-14.96</v>
+        <v>-15.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -18548,20 +18688,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>66.2</v>
+        <v>37.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -18570,19 +18710,15 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>77</v>
-      </c>
-      <c r="I16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.71</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>56.8</v>
+        <v>31.95</v>
       </c>
       <c r="L16" t="n">
-        <v>-14.2</v>
+        <v>-15.03</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -18591,7 +18727,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-14.2</v>
+        <v>-15.03</v>
       </c>
     </row>
     <row r="17">
@@ -18605,41 +18741,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I17" t="n">
-        <v>21.8</v>
+        <v>38.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="K17" t="n">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="L17" t="n">
-        <v>-14.07</v>
+        <v>-14.96</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -18648,12 +18784,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-14.07</v>
+        <v>-14.96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -18662,16 +18798,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>114.5</v>
+        <v>66.2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -18680,23 +18816,23 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="I18" t="n">
-        <v>12.3</v>
+        <v>10.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="K18" t="n">
-        <v>99.3</v>
+        <v>56.8</v>
       </c>
       <c r="L18" t="n">
-        <v>-13.28</v>
+        <v>-14.2</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -18705,12 +18841,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-13.28</v>
+        <v>-14.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -18719,20 +18855,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>360</v>
+        <v>995</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -18741,19 +18877,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I19" t="n">
-        <v>27.5</v>
+        <v>21.8</v>
       </c>
       <c r="J19" t="n">
-        <v>1.22</v>
+        <v>0.75</v>
       </c>
       <c r="K19" t="n">
-        <v>316.5</v>
+        <v>855</v>
       </c>
       <c r="L19" t="n">
-        <v>-12.08</v>
+        <v>-14.07</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -18762,12 +18898,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-12.08</v>
+        <v>-14.07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -18776,20 +18912,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>147</v>
+        <v>381</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -18798,19 +18934,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="I20" t="n">
-        <v>16.4</v>
+        <v>13.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1.11</v>
+        <v>0.49</v>
       </c>
       <c r="K20" t="n">
-        <v>129.5</v>
+        <v>327.5</v>
       </c>
       <c r="L20" t="n">
-        <v>-11.9</v>
+        <v>-14.04</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -18819,12 +18955,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-11.9</v>
+        <v>-14.04</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -18833,37 +18969,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>79.3</v>
+        <v>114.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>79</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="I21" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.64</v>
+      </c>
       <c r="K21" t="n">
-        <v>70.09999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="L21" t="n">
-        <v>-11.6</v>
+        <v>-13.28</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -18872,7 +19012,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-11.6</v>
+        <v>-13.28</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C2" t="n">
-        <v>30.8</v>
+        <v>31.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.05</v>
+        <v>-2.74</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.34</v>
+        <v>-5.33</v>
       </c>
       <c r="F2" t="n">
         <v>49.42</v>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>30.8</v>
+        <v>31.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.05</v>
+        <v>-2.74</v>
       </c>
     </row>
   </sheetData>
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R312"/>
+  <dimension ref="A1:R313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11318,8 +11318,12 @@
       <c r="J207" t="n">
         <v>0.26</v>
       </c>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
+      <c r="K207" t="n">
+        <v>6620</v>
+      </c>
+      <c r="L207" t="n">
+        <v>29.42</v>
+      </c>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
@@ -16528,6 +16532,52 @@
       <c r="P312" t="inlineStr"/>
       <c r="Q312" t="inlineStr"/>
       <c r="R312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>信立</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H313" t="n">
+        <v>75</v>
+      </c>
+      <c r="I313" t="inlineStr"/>
+      <c r="J313" t="inlineStr"/>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr"/>
+      <c r="O313" t="inlineStr"/>
+      <c r="P313" t="inlineStr"/>
+      <c r="Q313" t="inlineStr"/>
+      <c r="R313" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16809,7 +16859,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -16818,20 +16868,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>181.5</v>
+        <v>5115</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -16840,15 +16890,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>69</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.26</v>
+      </c>
       <c r="K5" t="n">
-        <v>233</v>
+        <v>6620</v>
       </c>
       <c r="L5" t="n">
-        <v>28.37</v>
+        <v>29.42</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -16857,12 +16911,12 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>28.37</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -16871,20 +16925,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5050</v>
+        <v>181.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -16893,19 +16947,15 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>65</v>
-      </c>
-      <c r="I6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.26</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>6265</v>
+        <v>233</v>
       </c>
       <c r="L6" t="n">
-        <v>24.06</v>
+        <v>28.37</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -16914,12 +16964,12 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>24.06</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -16928,16 +16978,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>155.5</v>
+        <v>5050</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -16946,23 +16996,23 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="K7" t="n">
-        <v>189.5</v>
+        <v>6265</v>
       </c>
       <c r="L7" t="n">
-        <v>21.86</v>
+        <v>24.06</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -16971,7 +17021,7 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>21.86</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="8">
@@ -16985,16 +17035,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2450</v>
+        <v>155.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -17003,23 +17053,23 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="I8" t="n">
-        <v>24.6</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>0.66</v>
+        <v>0.31</v>
       </c>
       <c r="K8" t="n">
-        <v>2940</v>
+        <v>189.5</v>
       </c>
       <c r="L8" t="n">
-        <v>20</v>
+        <v>21.86</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -17028,12 +17078,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -17042,37 +17092,41 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>193.5</v>
+        <v>2450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>69</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I9" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.66</v>
+      </c>
       <c r="K9" t="n">
-        <v>222.5</v>
+        <v>2940</v>
       </c>
       <c r="L9" t="n">
-        <v>14.99</v>
+        <v>20</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -17081,12 +17135,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>14.99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -17095,41 +17149,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>426</v>
+        <v>193.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
-      </c>
-      <c r="I10" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.92</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>488</v>
+        <v>222.5</v>
       </c>
       <c r="L10" t="n">
-        <v>14.55</v>
+        <v>14.99</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -17138,7 +17188,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>14.55</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="11">
@@ -17152,41 +17202,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>61.1</v>
+        <v>426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="J11" t="n">
-        <v>1.35</v>
+        <v>0.92</v>
       </c>
       <c r="K11" t="n">
-        <v>69.90000000000001</v>
+        <v>488</v>
       </c>
       <c r="L11" t="n">
-        <v>14.4</v>
+        <v>14.55</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -17195,7 +17245,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>14.4</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="12">
@@ -17209,41 +17259,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>896</v>
+        <v>61.1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="I12" t="n">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="J12" t="n">
-        <v>0.75</v>
+        <v>1.35</v>
       </c>
       <c r="K12" t="n">
-        <v>1010</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>12.72</v>
+        <v>14.4</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -17252,12 +17302,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12.72</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -17266,41 +17316,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>237</v>
+        <v>896</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I13" t="n">
-        <v>15.3</v>
+        <v>21.8</v>
       </c>
       <c r="J13" t="n">
-        <v>1.16</v>
+        <v>0.75</v>
       </c>
       <c r="K13" t="n">
-        <v>264.5</v>
+        <v>1010</v>
       </c>
       <c r="L13" t="n">
-        <v>11.6</v>
+        <v>12.72</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -17309,12 +17359,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>11.6</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -17323,41 +17373,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>154.5</v>
+        <v>237</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>15.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0.31</v>
+        <v>1.16</v>
       </c>
       <c r="K14" t="n">
-        <v>169.5</v>
+        <v>264.5</v>
       </c>
       <c r="L14" t="n">
-        <v>9.710000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -17366,12 +17416,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9.710000000000001</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -17380,16 +17430,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>970</v>
+        <v>154.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -17398,23 +17448,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="I15" t="n">
-        <v>21.8</v>
+        <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>0.75</v>
+        <v>0.31</v>
       </c>
       <c r="K15" t="n">
-        <v>1060</v>
+        <v>169.5</v>
       </c>
       <c r="L15" t="n">
-        <v>9.279999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -17423,12 +17473,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9.279999999999999</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -17437,41 +17487,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>239</v>
+        <v>970</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I16" t="n">
-        <v>15.3</v>
+        <v>21.8</v>
       </c>
       <c r="J16" t="n">
-        <v>1.16</v>
+        <v>0.75</v>
       </c>
       <c r="K16" t="n">
-        <v>259.5</v>
+        <v>1060</v>
       </c>
       <c r="L16" t="n">
-        <v>8.58</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -17480,7 +17530,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>8.58</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -17494,41 +17544,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>38.5</v>
+        <v>239</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>15.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2</v>
+        <v>1.16</v>
       </c>
       <c r="K17" t="n">
-        <v>41.7</v>
+        <v>259.5</v>
       </c>
       <c r="L17" t="n">
-        <v>8.31</v>
+        <v>8.58</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -17537,7 +17587,7 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>8.31</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="18">
@@ -17551,16 +17601,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103</v>
+        <v>38.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -17573,19 +17623,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="I18" t="n">
-        <v>12.4</v>
+        <v>6.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.73</v>
+        <v>0.2</v>
       </c>
       <c r="K18" t="n">
-        <v>111.5</v>
+        <v>41.7</v>
       </c>
       <c r="L18" t="n">
-        <v>8.25</v>
+        <v>8.31</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -17594,12 +17644,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>8.25</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -17608,16 +17658,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -17630,19 +17680,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I19" t="n">
-        <v>14.1</v>
+        <v>12.4</v>
       </c>
       <c r="J19" t="n">
         <v>0.73</v>
       </c>
       <c r="K19" t="n">
-        <v>154.5</v>
+        <v>111.5</v>
       </c>
       <c r="L19" t="n">
-        <v>7.29</v>
+        <v>8.25</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -17651,7 +17701,7 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>7.29</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="20">
@@ -17665,16 +17715,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -17687,19 +17737,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="I20" t="n">
-        <v>12.4</v>
+        <v>14.1</v>
       </c>
       <c r="J20" t="n">
         <v>0.73</v>
       </c>
       <c r="K20" t="n">
-        <v>110</v>
+        <v>154.5</v>
       </c>
       <c r="L20" t="n">
-        <v>6.8</v>
+        <v>7.29</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -17708,7 +17758,7 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>6.8</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="21">
@@ -17722,16 +17772,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>87.8</v>
+        <v>103</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -17740,23 +17790,23 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="I21" t="n">
-        <v>8.6</v>
+        <v>12.4</v>
       </c>
       <c r="J21" t="n">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="K21" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="L21" t="n">
-        <v>5.92</v>
+        <v>6.8</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -17765,7 +17815,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>5.92</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R313"/>
+  <dimension ref="A1:R348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16578,6 +16578,1736 @@
       <c r="P313" t="inlineStr"/>
       <c r="Q313" t="inlineStr"/>
       <c r="R313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>155</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H314" t="n">
+        <v>97</v>
+      </c>
+      <c r="I314" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J314" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr"/>
+      <c r="O314" t="inlineStr"/>
+      <c r="P314" t="inlineStr"/>
+      <c r="Q314" t="inlineStr"/>
+      <c r="R314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>553</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H315" t="n">
+        <v>96</v>
+      </c>
+      <c r="I315" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J315" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr"/>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr"/>
+      <c r="O315" t="inlineStr"/>
+      <c r="P315" t="inlineStr"/>
+      <c r="Q315" t="inlineStr"/>
+      <c r="R315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>123</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H316" t="n">
+        <v>91</v>
+      </c>
+      <c r="I316" t="n">
+        <v>15</v>
+      </c>
+      <c r="J316" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr"/>
+      <c r="O316" t="inlineStr"/>
+      <c r="P316" t="inlineStr"/>
+      <c r="Q316" t="inlineStr"/>
+      <c r="R316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>294</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H317" t="n">
+        <v>90</v>
+      </c>
+      <c r="I317" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J317" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr"/>
+      <c r="O317" t="inlineStr"/>
+      <c r="P317" t="inlineStr"/>
+      <c r="Q317" t="inlineStr"/>
+      <c r="R317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H318" t="n">
+        <v>87</v>
+      </c>
+      <c r="I318" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J318" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
+      <c r="O318" t="inlineStr"/>
+      <c r="P318" t="inlineStr"/>
+      <c r="Q318" t="inlineStr"/>
+      <c r="R318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H319" t="n">
+        <v>77</v>
+      </c>
+      <c r="I319" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J319" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr"/>
+      <c r="P319" t="inlineStr"/>
+      <c r="Q319" t="inlineStr"/>
+      <c r="R319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>249</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H320" t="n">
+        <v>77</v>
+      </c>
+      <c r="I320" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J320" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr"/>
+      <c r="P320" t="inlineStr"/>
+      <c r="Q320" t="inlineStr"/>
+      <c r="R320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>1025</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H321" t="n">
+        <v>76</v>
+      </c>
+      <c r="I321" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J321" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr"/>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
+      <c r="O321" t="inlineStr"/>
+      <c r="P321" t="inlineStr"/>
+      <c r="Q321" t="inlineStr"/>
+      <c r="R321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H322" t="n">
+        <v>68</v>
+      </c>
+      <c r="I322" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J322" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr"/>
+      <c r="P322" t="inlineStr"/>
+      <c r="Q322" t="inlineStr"/>
+      <c r="R322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>3035</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H323" t="n">
+        <v>100</v>
+      </c>
+      <c r="I323" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J323" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr"/>
+      <c r="P323" t="inlineStr"/>
+      <c r="Q323" t="inlineStr"/>
+      <c r="R323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>782</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H324" t="n">
+        <v>100</v>
+      </c>
+      <c r="I324" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J324" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr"/>
+      <c r="P324" t="inlineStr"/>
+      <c r="Q324" t="inlineStr"/>
+      <c r="R324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>2380</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H325" t="n">
+        <v>100</v>
+      </c>
+      <c r="I325" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J325" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr"/>
+      <c r="P325" t="inlineStr"/>
+      <c r="Q325" t="inlineStr"/>
+      <c r="R325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H326" t="n">
+        <v>97</v>
+      </c>
+      <c r="I326" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J326" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
+      <c r="O326" t="inlineStr"/>
+      <c r="P326" t="inlineStr"/>
+      <c r="Q326" t="inlineStr"/>
+      <c r="R326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H327" t="n">
+        <v>94</v>
+      </c>
+      <c r="I327" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J327" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
+      <c r="O327" t="inlineStr"/>
+      <c r="P327" t="inlineStr"/>
+      <c r="Q327" t="inlineStr"/>
+      <c r="R327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H328" t="n">
+        <v>94</v>
+      </c>
+      <c r="I328" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J328" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
+      <c r="O328" t="inlineStr"/>
+      <c r="P328" t="inlineStr"/>
+      <c r="Q328" t="inlineStr"/>
+      <c r="R328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>110</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H329" t="n">
+        <v>94</v>
+      </c>
+      <c r="I329" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J329" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
+      <c r="O329" t="inlineStr"/>
+      <c r="P329" t="inlineStr"/>
+      <c r="Q329" t="inlineStr"/>
+      <c r="R329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H330" t="n">
+        <v>94</v>
+      </c>
+      <c r="I330" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J330" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
+      <c r="O330" t="inlineStr"/>
+      <c r="P330" t="inlineStr"/>
+      <c r="Q330" t="inlineStr"/>
+      <c r="R330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H331" t="n">
+        <v>92</v>
+      </c>
+      <c r="I331" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J331" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
+      <c r="O331" t="inlineStr"/>
+      <c r="P331" t="inlineStr"/>
+      <c r="Q331" t="inlineStr"/>
+      <c r="R331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>1025</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H332" t="n">
+        <v>90</v>
+      </c>
+      <c r="I332" t="n">
+        <v>25</v>
+      </c>
+      <c r="J332" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr"/>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
+      <c r="O332" t="inlineStr"/>
+      <c r="P332" t="inlineStr"/>
+      <c r="Q332" t="inlineStr"/>
+      <c r="R332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>488.5</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H333" t="n">
+        <v>90</v>
+      </c>
+      <c r="I333" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J333" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K333" t="inlineStr"/>
+      <c r="L333" t="inlineStr"/>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr"/>
+      <c r="O333" t="inlineStr"/>
+      <c r="P333" t="inlineStr"/>
+      <c r="Q333" t="inlineStr"/>
+      <c r="R333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H334" t="n">
+        <v>90</v>
+      </c>
+      <c r="I334" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J334" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr"/>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
+      <c r="O334" t="inlineStr"/>
+      <c r="P334" t="inlineStr"/>
+      <c r="Q334" t="inlineStr"/>
+      <c r="R334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H335" t="n">
+        <v>84</v>
+      </c>
+      <c r="I335" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J335" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr"/>
+      <c r="O335" t="inlineStr"/>
+      <c r="P335" t="inlineStr"/>
+      <c r="Q335" t="inlineStr"/>
+      <c r="R335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>2225</v>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H336" t="n">
+        <v>80</v>
+      </c>
+      <c r="I336" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J336" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr"/>
+      <c r="O336" t="inlineStr"/>
+      <c r="P336" t="inlineStr"/>
+      <c r="Q336" t="inlineStr"/>
+      <c r="R336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>1005</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H337" t="n">
+        <v>80</v>
+      </c>
+      <c r="I337" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J337" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr"/>
+      <c r="O337" t="inlineStr"/>
+      <c r="P337" t="inlineStr"/>
+      <c r="Q337" t="inlineStr"/>
+      <c r="R337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H338" t="n">
+        <v>79</v>
+      </c>
+      <c r="I338" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J338" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
+      <c r="O338" t="inlineStr"/>
+      <c r="P338" t="inlineStr"/>
+      <c r="Q338" t="inlineStr"/>
+      <c r="R338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>60</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H339" t="n">
+        <v>78</v>
+      </c>
+      <c r="I339" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J339" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
+      <c r="O339" t="inlineStr"/>
+      <c r="P339" t="inlineStr"/>
+      <c r="Q339" t="inlineStr"/>
+      <c r="R339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H340" t="n">
+        <v>77</v>
+      </c>
+      <c r="I340" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J340" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K340" t="inlineStr"/>
+      <c r="L340" t="inlineStr"/>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr"/>
+      <c r="O340" t="inlineStr"/>
+      <c r="P340" t="inlineStr"/>
+      <c r="Q340" t="inlineStr"/>
+      <c r="R340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>327</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H341" t="n">
+        <v>65</v>
+      </c>
+      <c r="I341" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J341" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr"/>
+      <c r="O341" t="inlineStr"/>
+      <c r="P341" t="inlineStr"/>
+      <c r="Q341" t="inlineStr"/>
+      <c r="R341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>181</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H342" t="n">
+        <v>62</v>
+      </c>
+      <c r="I342" t="n">
+        <v>10</v>
+      </c>
+      <c r="J342" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K342" t="inlineStr"/>
+      <c r="L342" t="inlineStr"/>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
+      <c r="O342" t="inlineStr"/>
+      <c r="P342" t="inlineStr"/>
+      <c r="Q342" t="inlineStr"/>
+      <c r="R342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>1360</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H343" t="n">
+        <v>60</v>
+      </c>
+      <c r="I343" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J343" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr"/>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
+      <c r="O343" t="inlineStr"/>
+      <c r="P343" t="inlineStr"/>
+      <c r="Q343" t="inlineStr"/>
+      <c r="R343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H344" t="n">
+        <v>79</v>
+      </c>
+      <c r="I344" t="inlineStr"/>
+      <c r="J344" t="inlineStr"/>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr"/>
+      <c r="O344" t="inlineStr"/>
+      <c r="P344" t="inlineStr"/>
+      <c r="Q344" t="inlineStr"/>
+      <c r="R344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>400</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H345" t="n">
+        <v>77</v>
+      </c>
+      <c r="I345" t="inlineStr"/>
+      <c r="J345" t="inlineStr"/>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr"/>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr"/>
+      <c r="O345" t="inlineStr"/>
+      <c r="P345" t="inlineStr"/>
+      <c r="Q345" t="inlineStr"/>
+      <c r="R345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H346" t="n">
+        <v>77</v>
+      </c>
+      <c r="I346" t="inlineStr"/>
+      <c r="J346" t="inlineStr"/>
+      <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr"/>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr"/>
+      <c r="O346" t="inlineStr"/>
+      <c r="P346" t="inlineStr"/>
+      <c r="Q346" t="inlineStr"/>
+      <c r="R346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>223</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H347" t="n">
+        <v>69</v>
+      </c>
+      <c r="I347" t="inlineStr"/>
+      <c r="J347" t="inlineStr"/>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr"/>
+      <c r="O347" t="inlineStr"/>
+      <c r="P347" t="inlineStr"/>
+      <c r="Q347" t="inlineStr"/>
+      <c r="R347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>豐藝</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H348" t="n">
+        <v>32</v>
+      </c>
+      <c r="I348" t="inlineStr"/>
+      <c r="J348" t="inlineStr"/>
+      <c r="K348" t="inlineStr"/>
+      <c r="L348" t="inlineStr"/>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr"/>
+      <c r="O348" t="inlineStr"/>
+      <c r="P348" t="inlineStr"/>
+      <c r="Q348" t="inlineStr"/>
+      <c r="R348" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R348"/>
+  <dimension ref="A1:R349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18308,6 +18308,56 @@
       <c r="P348" t="inlineStr"/>
       <c r="Q348" t="inlineStr"/>
       <c r="R348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>6325</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H349" t="n">
+        <v>65</v>
+      </c>
+      <c r="I349" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J349" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr"/>
+      <c r="O349" t="inlineStr"/>
+      <c r="P349" t="inlineStr"/>
+      <c r="Q349" t="inlineStr"/>
+      <c r="R349" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="C2" t="n">
-        <v>31.5</v>
+        <v>35.9</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.74</v>
+        <v>-2.17</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.33</v>
+        <v>-3.16</v>
       </c>
       <c r="F2" t="n">
         <v>49.42</v>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="D2" t="n">
-        <v>31.5</v>
+        <v>35.9</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.74</v>
+        <v>-2.17</v>
       </c>
     </row>
   </sheetData>
@@ -11372,8 +11372,12 @@
       <c r="J208" t="n">
         <v>1.29</v>
       </c>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
+      <c r="K208" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="L208" t="n">
+        <v>6.87</v>
+      </c>
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
@@ -11422,8 +11426,12 @@
       <c r="J209" t="n">
         <v>1.11</v>
       </c>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
+      <c r="K209" t="n">
+        <v>521</v>
+      </c>
+      <c r="L209" t="n">
+        <v>-6.8</v>
+      </c>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
@@ -11472,8 +11480,12 @@
       <c r="J210" t="n">
         <v>1.26</v>
       </c>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
+      <c r="K210" t="n">
+        <v>123</v>
+      </c>
+      <c r="L210" t="n">
+        <v>2.5</v>
+      </c>
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
@@ -11522,8 +11534,12 @@
       <c r="J211" t="n">
         <v>1.22</v>
       </c>
-      <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
+      <c r="K211" t="n">
+        <v>290</v>
+      </c>
+      <c r="L211" t="n">
+        <v>-8.08</v>
+      </c>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
@@ -11572,8 +11588,12 @@
       <c r="J212" t="n">
         <v>1.36</v>
       </c>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
+      <c r="K212" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0.23</v>
+      </c>
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
@@ -11622,8 +11642,12 @@
       <c r="J213" t="n">
         <v>1.11</v>
       </c>
-      <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
+      <c r="K213" t="n">
+        <v>120</v>
+      </c>
+      <c r="L213" t="n">
+        <v>-16.08</v>
+      </c>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
@@ -11672,8 +11696,12 @@
       <c r="J214" t="n">
         <v>1.16</v>
       </c>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
+      <c r="K214" t="n">
+        <v>243.5</v>
+      </c>
+      <c r="L214" t="n">
+        <v>-5.44</v>
+      </c>
       <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
@@ -11722,8 +11750,12 @@
       <c r="J215" t="n">
         <v>1.03</v>
       </c>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
+      <c r="K215" t="n">
+        <v>967</v>
+      </c>
+      <c r="L215" t="n">
+        <v>-18.74</v>
+      </c>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
@@ -11772,8 +11804,12 @@
       <c r="J216" t="n">
         <v>1.35</v>
       </c>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
+      <c r="K216" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="L216" t="n">
+        <v>4.92</v>
+      </c>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
@@ -11822,8 +11858,12 @@
       <c r="J217" t="n">
         <v>0.66</v>
       </c>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
+      <c r="K217" t="n">
+        <v>2855</v>
+      </c>
+      <c r="L217" t="n">
+        <v>17.01</v>
+      </c>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
@@ -11872,8 +11912,12 @@
       <c r="J218" t="n">
         <v>0.4</v>
       </c>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
+      <c r="K218" t="n">
+        <v>758</v>
+      </c>
+      <c r="L218" t="n">
+        <v>-11.66</v>
+      </c>
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
@@ -11922,8 +11966,12 @@
       <c r="J219" t="n">
         <v>0.78</v>
       </c>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
+      <c r="K219" t="n">
+        <v>2375</v>
+      </c>
+      <c r="L219" t="n">
+        <v>-1.25</v>
+      </c>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
@@ -11972,8 +12020,12 @@
       <c r="J220" t="n">
         <v>0.73</v>
       </c>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
+      <c r="K220" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="L220" t="n">
+        <v>9.130000000000001</v>
+      </c>
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
@@ -12022,8 +12074,12 @@
       <c r="J221" t="n">
         <v>0.64</v>
       </c>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
+      <c r="K221" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="L221" t="n">
+        <v>-3.18</v>
+      </c>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
@@ -12072,8 +12128,12 @@
       <c r="J222" t="n">
         <v>0.42</v>
       </c>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
+      <c r="K222" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="L222" t="n">
+        <v>-0.36</v>
+      </c>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
@@ -12122,8 +12182,12 @@
       <c r="J223" t="n">
         <v>0.76</v>
       </c>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
+      <c r="K223" t="n">
+        <v>109</v>
+      </c>
+      <c r="L223" t="n">
+        <v>-0.46</v>
+      </c>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
@@ -12172,8 +12236,12 @@
       <c r="J224" t="n">
         <v>0.59</v>
       </c>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
+      <c r="K224" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="L224" t="n">
+        <v>7.1</v>
+      </c>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
@@ -12222,8 +12290,12 @@
       <c r="J225" t="n">
         <v>0.84</v>
       </c>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
+      <c r="K225" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="L225" t="n">
+        <v>4.41</v>
+      </c>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
@@ -12272,8 +12344,12 @@
       <c r="J226" t="n">
         <v>0.67</v>
       </c>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
+      <c r="K226" t="n">
+        <v>967</v>
+      </c>
+      <c r="L226" t="n">
+        <v>-18.05</v>
+      </c>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
@@ -12322,8 +12398,12 @@
       <c r="J227" t="n">
         <v>0.92</v>
       </c>
-      <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr"/>
+      <c r="K227" t="n">
+        <v>450</v>
+      </c>
+      <c r="L227" t="n">
+        <v>10.84</v>
+      </c>
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
@@ -12372,8 +12452,12 @@
       <c r="J228" t="n">
         <v>0.73</v>
       </c>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
+      <c r="K228" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="L228" t="n">
+        <v>7.49</v>
+      </c>
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
@@ -12422,8 +12506,12 @@
       <c r="J229" t="n">
         <v>0.2</v>
       </c>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
+      <c r="K229" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="L229" t="n">
+        <v>2.34</v>
+      </c>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr"/>
@@ -12472,8 +12560,12 @@
       <c r="J230" t="n">
         <v>0.82</v>
       </c>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
+      <c r="K230" t="n">
+        <v>2070</v>
+      </c>
+      <c r="L230" t="n">
+        <v>-10.97</v>
+      </c>
       <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
@@ -12522,8 +12614,12 @@
       <c r="J231" t="n">
         <v>0.75</v>
       </c>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
+      <c r="K231" t="n">
+        <v>969</v>
+      </c>
+      <c r="L231" t="n">
+        <v>4.98</v>
+      </c>
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
@@ -12572,8 +12668,12 @@
       <c r="J232" t="n">
         <v>0.36</v>
       </c>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
+      <c r="K232" t="n">
+        <v>91</v>
+      </c>
+      <c r="L232" t="n">
+        <v>2.82</v>
+      </c>
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
@@ -12622,8 +12722,12 @@
       <c r="J233" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
+      <c r="K233" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="L233" t="n">
+        <v>-17.91</v>
+      </c>
       <c r="M233" t="inlineStr"/>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr"/>
@@ -12672,8 +12776,12 @@
       <c r="J234" t="n">
         <v>0.71</v>
       </c>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
+      <c r="K234" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="L234" t="n">
+        <v>-3.39</v>
+      </c>
       <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
@@ -12722,8 +12830,12 @@
       <c r="J235" t="n">
         <v>0.49</v>
       </c>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
+      <c r="K235" t="n">
+        <v>325</v>
+      </c>
+      <c r="L235" t="n">
+        <v>-3.27</v>
+      </c>
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
@@ -12772,8 +12884,12 @@
       <c r="J236" t="n">
         <v>0.31</v>
       </c>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
+      <c r="K236" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="L236" t="n">
+        <v>1.15</v>
+      </c>
       <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
@@ -12822,8 +12938,12 @@
       <c r="J237" t="n">
         <v>0.36</v>
       </c>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
+      <c r="K237" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L237" t="n">
+        <v>-0.36</v>
+      </c>
       <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
@@ -12868,8 +12988,12 @@
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
+      <c r="K238" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="L238" t="n">
+        <v>-1.62</v>
+      </c>
       <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr"/>
@@ -12914,8 +13038,12 @@
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
+      <c r="K239" t="n">
+        <v>422.5</v>
+      </c>
+      <c r="L239" t="n">
+        <v>11.62</v>
+      </c>
       <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr"/>
@@ -13006,8 +13134,12 @@
       </c>
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
+      <c r="K241" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="L241" t="n">
+        <v>12.14</v>
+      </c>
       <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
@@ -13056,8 +13188,12 @@
       <c r="J242" t="n">
         <v>0.26</v>
       </c>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
+      <c r="K242" t="n">
+        <v>6300</v>
+      </c>
+      <c r="L242" t="n">
+        <v>9.949999999999999</v>
+      </c>
       <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr"/>
@@ -18920,7 +19056,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46202</v>
+        <v>46226</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -18929,37 +19065,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>193.5</v>
+        <v>2440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>69</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I10" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.66</v>
+      </c>
       <c r="K10" t="n">
-        <v>222.5</v>
+        <v>2855</v>
       </c>
       <c r="L10" t="n">
-        <v>14.99</v>
+        <v>17.01</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -18968,12 +19108,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>14.99</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -18982,41 +19122,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>426</v>
+        <v>193.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>90</v>
-      </c>
-      <c r="I11" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.92</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>488</v>
+        <v>222.5</v>
       </c>
       <c r="L11" t="n">
-        <v>14.55</v>
+        <v>14.99</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -19025,7 +19161,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>14.55</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="12">
@@ -19039,41 +19175,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>61.1</v>
+        <v>426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1.35</v>
+        <v>0.92</v>
       </c>
       <c r="K12" t="n">
-        <v>69.90000000000001</v>
+        <v>488</v>
       </c>
       <c r="L12" t="n">
-        <v>14.4</v>
+        <v>14.55</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -19082,7 +19218,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>14.4</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="13">
@@ -19096,41 +19232,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>896</v>
+        <v>61.1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="I13" t="n">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0.75</v>
+        <v>1.35</v>
       </c>
       <c r="K13" t="n">
-        <v>1010</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>12.72</v>
+        <v>14.4</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -19139,12 +19275,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12.72</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -19153,41 +19289,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>237</v>
+        <v>896</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I14" t="n">
-        <v>15.3</v>
+        <v>21.8</v>
       </c>
       <c r="J14" t="n">
-        <v>1.16</v>
+        <v>0.75</v>
       </c>
       <c r="K14" t="n">
-        <v>264.5</v>
+        <v>1010</v>
       </c>
       <c r="L14" t="n">
-        <v>11.6</v>
+        <v>12.72</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -19196,12 +19332,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>11.6</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46202</v>
+        <v>46226</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -19210,41 +19346,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>154.5</v>
+        <v>210</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>62</v>
-      </c>
-      <c r="I15" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.31</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>169.5</v>
+        <v>235.5</v>
       </c>
       <c r="L15" t="n">
-        <v>9.710000000000001</v>
+        <v>12.14</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -19253,12 +19385,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9.710000000000001</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46210</v>
+        <v>46226</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -19267,41 +19399,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>970</v>
+        <v>378.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>80</v>
-      </c>
-      <c r="I16" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.75</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>1060</v>
+        <v>422.5</v>
       </c>
       <c r="L16" t="n">
-        <v>9.279999999999999</v>
+        <v>11.62</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -19310,12 +19438,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>9.279999999999999</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -19333,7 +19461,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -19355,10 +19483,10 @@
         <v>1.16</v>
       </c>
       <c r="K17" t="n">
-        <v>259.5</v>
+        <v>264.5</v>
       </c>
       <c r="L17" t="n">
-        <v>8.58</v>
+        <v>11.6</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -19367,12 +19495,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>8.58</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -19381,16 +19509,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>38.5</v>
+        <v>406</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -19403,19 +19531,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I18" t="n">
-        <v>6.2</v>
+        <v>21.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="K18" t="n">
-        <v>41.7</v>
+        <v>450</v>
       </c>
       <c r="L18" t="n">
-        <v>8.31</v>
+        <v>10.84</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -19424,12 +19552,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>8.31</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46218</v>
+        <v>46227</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -19438,16 +19566,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103</v>
+        <v>5730</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -19456,23 +19584,23 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="I19" t="n">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="J19" t="n">
-        <v>0.73</v>
+        <v>0.26</v>
       </c>
       <c r="K19" t="n">
-        <v>111.5</v>
+        <v>6300</v>
       </c>
       <c r="L19" t="n">
-        <v>8.25</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -19481,12 +19609,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>8.25</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -19495,16 +19623,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>144</v>
+        <v>154.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -19513,23 +19641,23 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="I20" t="n">
-        <v>14.1</v>
+        <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>0.73</v>
+        <v>0.31</v>
       </c>
       <c r="K20" t="n">
-        <v>154.5</v>
+        <v>169.5</v>
       </c>
       <c r="L20" t="n">
-        <v>7.29</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -19538,7 +19666,7 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>7.29</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -19552,16 +19680,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103</v>
+        <v>970</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -19574,19 +19702,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="I21" t="n">
-        <v>12.4</v>
+        <v>21.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="K21" t="n">
-        <v>110</v>
+        <v>1060</v>
       </c>
       <c r="L21" t="n">
-        <v>6.8</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -19595,7 +19723,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>6.8</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -20224,7 +20352,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46210</v>
+        <v>46226</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -20233,38 +20361,38 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>34.15</v>
+        <v>1190</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="I11" t="n">
-        <v>5.9</v>
+        <v>38.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.42</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>27.75</v>
+        <v>967</v>
       </c>
       <c r="L11" t="n">
         <v>-18.74</v>
@@ -20281,7 +20409,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -20290,16 +20418,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2340</v>
+        <v>34.15</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -20312,19 +20440,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I12" t="n">
-        <v>30.7</v>
+        <v>5.9</v>
       </c>
       <c r="J12" t="n">
-        <v>0.82</v>
+        <v>0.42</v>
       </c>
       <c r="K12" t="n">
-        <v>1910</v>
+        <v>27.75</v>
       </c>
       <c r="L12" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -20333,12 +20461,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -20347,16 +20475,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>475.5</v>
+        <v>2340</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -20369,19 +20497,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I13" t="n">
-        <v>21.2</v>
+        <v>30.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0.92</v>
+        <v>0.82</v>
       </c>
       <c r="K13" t="n">
-        <v>397.5</v>
+        <v>1910</v>
       </c>
       <c r="L13" t="n">
-        <v>-16.4</v>
+        <v>-18.38</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -20390,12 +20518,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-16.4</v>
+        <v>-18.38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -20404,16 +20532,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>72.7</v>
+        <v>1180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -20422,23 +20550,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="K14" t="n">
-        <v>61</v>
+        <v>967</v>
       </c>
       <c r="L14" t="n">
-        <v>-16.09</v>
+        <v>-18.05</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -20447,12 +20575,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-16.09</v>
+        <v>-18.05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46202</v>
+        <v>46226</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -20461,16 +20589,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>367</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -20483,19 +20611,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="I15" t="n">
-        <v>13.2</v>
+        <v>6.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>309.5</v>
+        <v>59.6</v>
       </c>
       <c r="L15" t="n">
-        <v>-15.67</v>
+        <v>-17.91</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -20504,12 +20632,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-15.67</v>
+        <v>-17.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -20518,37 +20646,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>37.6</v>
+        <v>475.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>75</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="I16" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.92</v>
+      </c>
       <c r="K16" t="n">
-        <v>31.95</v>
+        <v>397.5</v>
       </c>
       <c r="L16" t="n">
-        <v>-15.03</v>
+        <v>-16.4</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -20557,12 +20689,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-15.03</v>
+        <v>-16.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -20571,20 +20703,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>996</v>
+        <v>72.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -20593,19 +20725,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I17" t="n">
-        <v>38.8</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>847</v>
+        <v>61</v>
       </c>
       <c r="L17" t="n">
-        <v>-14.96</v>
+        <v>-16.09</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -20614,12 +20746,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-14.96</v>
+        <v>-16.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46210</v>
+        <v>46226</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -20628,20 +20760,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>66.2</v>
+        <v>143</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -20653,16 +20785,16 @@
         <v>77</v>
       </c>
       <c r="I18" t="n">
-        <v>10.4</v>
+        <v>16.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.71</v>
+        <v>1.11</v>
       </c>
       <c r="K18" t="n">
-        <v>56.8</v>
+        <v>120</v>
       </c>
       <c r="L18" t="n">
-        <v>-14.2</v>
+        <v>-16.08</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -20671,7 +20803,7 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-14.2</v>
+        <v>-16.08</v>
       </c>
     </row>
     <row r="19">
@@ -20685,16 +20817,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>995</v>
+        <v>367</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -20703,23 +20835,23 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="I19" t="n">
-        <v>21.8</v>
+        <v>13.2</v>
       </c>
       <c r="J19" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="K19" t="n">
-        <v>855</v>
+        <v>309.5</v>
       </c>
       <c r="L19" t="n">
-        <v>-14.07</v>
+        <v>-15.67</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -20728,12 +20860,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-14.07</v>
+        <v>-15.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46218</v>
+        <v>46205</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -20742,20 +20874,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>381</v>
+        <v>37.6</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -20764,19 +20896,15 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>65</v>
-      </c>
-      <c r="I20" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.49</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>327.5</v>
+        <v>31.95</v>
       </c>
       <c r="L20" t="n">
-        <v>-14.04</v>
+        <v>-15.03</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -20785,7 +20913,7 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-14.04</v>
+        <v>-15.03</v>
       </c>
     </row>
     <row r="21">
@@ -20799,41 +20927,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>114.5</v>
+        <v>996</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="I21" t="n">
-        <v>12.3</v>
+        <v>38.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.64</v>
+        <v>1.03</v>
       </c>
       <c r="K21" t="n">
-        <v>99.3</v>
+        <v>847</v>
       </c>
       <c r="L21" t="n">
-        <v>-13.28</v>
+        <v>-14.96</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -20842,7 +20970,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-13.28</v>
+        <v>-14.96</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C2" t="n">
-        <v>35.9</v>
+        <v>36.4</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.17</v>
+        <v>-2.14</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.16</v>
+        <v>-3.14</v>
       </c>
       <c r="F2" t="n">
         <v>49.42</v>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D2" t="n">
-        <v>35.9</v>
+        <v>36.4</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.17</v>
+        <v>-2.14</v>
       </c>
     </row>
   </sheetData>
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R349"/>
+  <dimension ref="A1:R350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13088,8 +13088,12 @@
       </c>
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
+      <c r="K240" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="L240" t="n">
+        <v>1.9</v>
+      </c>
       <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
@@ -18494,6 +18498,52 @@
       <c r="P349" t="inlineStr"/>
       <c r="Q349" t="inlineStr"/>
       <c r="R349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>信立</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H350" t="n">
+        <v>75</v>
+      </c>
+      <c r="I350" t="inlineStr"/>
+      <c r="J350" t="inlineStr"/>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr"/>
+      <c r="O350" t="inlineStr"/>
+      <c r="P350" t="inlineStr"/>
+      <c r="Q350" t="inlineStr"/>
+      <c r="R350" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R350"/>
+  <dimension ref="A1:R384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18544,6 +18544,1690 @@
       <c r="P350" t="inlineStr"/>
       <c r="Q350" t="inlineStr"/>
       <c r="R350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>157</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H351" t="n">
+        <v>97</v>
+      </c>
+      <c r="I351" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J351" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr"/>
+      <c r="O351" t="inlineStr"/>
+      <c r="P351" t="inlineStr"/>
+      <c r="Q351" t="inlineStr"/>
+      <c r="R351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>536</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H352" t="n">
+        <v>96</v>
+      </c>
+      <c r="I352" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J352" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
+      <c r="O352" t="inlineStr"/>
+      <c r="P352" t="inlineStr"/>
+      <c r="Q352" t="inlineStr"/>
+      <c r="R352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H353" t="n">
+        <v>91</v>
+      </c>
+      <c r="I353" t="n">
+        <v>15</v>
+      </c>
+      <c r="J353" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
+      <c r="O353" t="inlineStr"/>
+      <c r="P353" t="inlineStr"/>
+      <c r="Q353" t="inlineStr"/>
+      <c r="R353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>307</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H354" t="n">
+        <v>90</v>
+      </c>
+      <c r="I354" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J354" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
+      <c r="O354" t="inlineStr"/>
+      <c r="P354" t="inlineStr"/>
+      <c r="Q354" t="inlineStr"/>
+      <c r="R354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>87</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H355" t="n">
+        <v>87</v>
+      </c>
+      <c r="I355" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J355" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
+      <c r="O355" t="inlineStr"/>
+      <c r="P355" t="inlineStr"/>
+      <c r="Q355" t="inlineStr"/>
+      <c r="R355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H356" t="n">
+        <v>77</v>
+      </c>
+      <c r="I356" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J356" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
+      <c r="O356" t="inlineStr"/>
+      <c r="P356" t="inlineStr"/>
+      <c r="Q356" t="inlineStr"/>
+      <c r="R356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>246.5</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H357" t="n">
+        <v>77</v>
+      </c>
+      <c r="I357" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J357" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr"/>
+      <c r="O357" t="inlineStr"/>
+      <c r="P357" t="inlineStr"/>
+      <c r="Q357" t="inlineStr"/>
+      <c r="R357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>960</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H358" t="n">
+        <v>76</v>
+      </c>
+      <c r="I358" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J358" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr"/>
+      <c r="O358" t="inlineStr"/>
+      <c r="P358" t="inlineStr"/>
+      <c r="Q358" t="inlineStr"/>
+      <c r="R358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H359" t="n">
+        <v>68</v>
+      </c>
+      <c r="I359" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J359" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr"/>
+      <c r="O359" t="inlineStr"/>
+      <c r="P359" t="inlineStr"/>
+      <c r="Q359" t="inlineStr"/>
+      <c r="R359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>3155</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H360" t="n">
+        <v>100</v>
+      </c>
+      <c r="I360" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J360" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
+      <c r="O360" t="inlineStr"/>
+      <c r="P360" t="inlineStr"/>
+      <c r="Q360" t="inlineStr"/>
+      <c r="R360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>800</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H361" t="n">
+        <v>100</v>
+      </c>
+      <c r="I361" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J361" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr"/>
+      <c r="O361" t="inlineStr"/>
+      <c r="P361" t="inlineStr"/>
+      <c r="Q361" t="inlineStr"/>
+      <c r="R361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>2415</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H362" t="n">
+        <v>100</v>
+      </c>
+      <c r="I362" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J362" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
+      <c r="O362" t="inlineStr"/>
+      <c r="P362" t="inlineStr"/>
+      <c r="Q362" t="inlineStr"/>
+      <c r="R362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>110</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H363" t="n">
+        <v>97</v>
+      </c>
+      <c r="I363" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J363" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr"/>
+      <c r="O363" t="inlineStr"/>
+      <c r="P363" t="inlineStr"/>
+      <c r="Q363" t="inlineStr"/>
+      <c r="R363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>106</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H364" t="n">
+        <v>94</v>
+      </c>
+      <c r="I364" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J364" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr"/>
+      <c r="O364" t="inlineStr"/>
+      <c r="P364" t="inlineStr"/>
+      <c r="Q364" t="inlineStr"/>
+      <c r="R364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>28</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H365" t="n">
+        <v>94</v>
+      </c>
+      <c r="I365" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J365" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr"/>
+      <c r="O365" t="inlineStr"/>
+      <c r="P365" t="inlineStr"/>
+      <c r="Q365" t="inlineStr"/>
+      <c r="R365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>109</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H366" t="n">
+        <v>94</v>
+      </c>
+      <c r="I366" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J366" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr"/>
+      <c r="O366" t="inlineStr"/>
+      <c r="P366" t="inlineStr"/>
+      <c r="Q366" t="inlineStr"/>
+      <c r="R366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>179</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H367" t="n">
+        <v>94</v>
+      </c>
+      <c r="I367" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J367" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr"/>
+      <c r="O367" t="inlineStr"/>
+      <c r="P367" t="inlineStr"/>
+      <c r="Q367" t="inlineStr"/>
+      <c r="R367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>43</v>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H368" t="n">
+        <v>92</v>
+      </c>
+      <c r="I368" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J368" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr"/>
+      <c r="O368" t="inlineStr"/>
+      <c r="P368" t="inlineStr"/>
+      <c r="Q368" t="inlineStr"/>
+      <c r="R368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>974</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H369" t="n">
+        <v>90</v>
+      </c>
+      <c r="I369" t="n">
+        <v>25</v>
+      </c>
+      <c r="J369" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr"/>
+      <c r="O369" t="inlineStr"/>
+      <c r="P369" t="inlineStr"/>
+      <c r="Q369" t="inlineStr"/>
+      <c r="R369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>481</v>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H370" t="n">
+        <v>90</v>
+      </c>
+      <c r="I370" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J370" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K370" t="inlineStr"/>
+      <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr"/>
+      <c r="O370" t="inlineStr"/>
+      <c r="P370" t="inlineStr"/>
+      <c r="Q370" t="inlineStr"/>
+      <c r="R370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H371" t="n">
+        <v>90</v>
+      </c>
+      <c r="I371" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J371" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr"/>
+      <c r="O371" t="inlineStr"/>
+      <c r="P371" t="inlineStr"/>
+      <c r="Q371" t="inlineStr"/>
+      <c r="R371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H372" t="n">
+        <v>84</v>
+      </c>
+      <c r="I372" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J372" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr"/>
+      <c r="O372" t="inlineStr"/>
+      <c r="P372" t="inlineStr"/>
+      <c r="Q372" t="inlineStr"/>
+      <c r="R372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>2055</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H373" t="n">
+        <v>80</v>
+      </c>
+      <c r="I373" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J373" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr"/>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr"/>
+      <c r="O373" t="inlineStr"/>
+      <c r="P373" t="inlineStr"/>
+      <c r="Q373" t="inlineStr"/>
+      <c r="R373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>1065</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H374" t="n">
+        <v>80</v>
+      </c>
+      <c r="I374" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J374" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr"/>
+      <c r="O374" t="inlineStr"/>
+      <c r="P374" t="inlineStr"/>
+      <c r="Q374" t="inlineStr"/>
+      <c r="R374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H375" t="n">
+        <v>79</v>
+      </c>
+      <c r="I375" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J375" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr"/>
+      <c r="O375" t="inlineStr"/>
+      <c r="P375" t="inlineStr"/>
+      <c r="Q375" t="inlineStr"/>
+      <c r="R375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H376" t="n">
+        <v>78</v>
+      </c>
+      <c r="I376" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J376" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr"/>
+      <c r="O376" t="inlineStr"/>
+      <c r="P376" t="inlineStr"/>
+      <c r="Q376" t="inlineStr"/>
+      <c r="R376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H377" t="n">
+        <v>77</v>
+      </c>
+      <c r="I377" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J377" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="inlineStr"/>
+      <c r="O377" t="inlineStr"/>
+      <c r="P377" t="inlineStr"/>
+      <c r="Q377" t="inlineStr"/>
+      <c r="R377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H378" t="n">
+        <v>65</v>
+      </c>
+      <c r="I378" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J378" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K378" t="inlineStr"/>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr"/>
+      <c r="O378" t="inlineStr"/>
+      <c r="P378" t="inlineStr"/>
+      <c r="Q378" t="inlineStr"/>
+      <c r="R378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>182</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H379" t="n">
+        <v>62</v>
+      </c>
+      <c r="I379" t="n">
+        <v>10</v>
+      </c>
+      <c r="J379" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr"/>
+      <c r="O379" t="inlineStr"/>
+      <c r="P379" t="inlineStr"/>
+      <c r="Q379" t="inlineStr"/>
+      <c r="R379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>1455</v>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H380" t="n">
+        <v>60</v>
+      </c>
+      <c r="I380" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J380" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K380" t="inlineStr"/>
+      <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr"/>
+      <c r="O380" t="inlineStr"/>
+      <c r="P380" t="inlineStr"/>
+      <c r="Q380" t="inlineStr"/>
+      <c r="R380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H381" t="n">
+        <v>79</v>
+      </c>
+      <c r="I381" t="inlineStr"/>
+      <c r="J381" t="inlineStr"/>
+      <c r="K381" t="inlineStr"/>
+      <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr"/>
+      <c r="O381" t="inlineStr"/>
+      <c r="P381" t="inlineStr"/>
+      <c r="Q381" t="inlineStr"/>
+      <c r="R381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>418.5</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H382" t="n">
+        <v>77</v>
+      </c>
+      <c r="I382" t="inlineStr"/>
+      <c r="J382" t="inlineStr"/>
+      <c r="K382" t="inlineStr"/>
+      <c r="L382" t="inlineStr"/>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr"/>
+      <c r="O382" t="inlineStr"/>
+      <c r="P382" t="inlineStr"/>
+      <c r="Q382" t="inlineStr"/>
+      <c r="R382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H383" t="n">
+        <v>77</v>
+      </c>
+      <c r="I383" t="inlineStr"/>
+      <c r="J383" t="inlineStr"/>
+      <c r="K383" t="inlineStr"/>
+      <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr"/>
+      <c r="N383" t="inlineStr"/>
+      <c r="O383" t="inlineStr"/>
+      <c r="P383" t="inlineStr"/>
+      <c r="Q383" t="inlineStr"/>
+      <c r="R383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>231</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H384" t="n">
+        <v>69</v>
+      </c>
+      <c r="I384" t="inlineStr"/>
+      <c r="J384" t="inlineStr"/>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr"/>
+      <c r="O384" t="inlineStr"/>
+      <c r="P384" t="inlineStr"/>
+      <c r="Q384" t="inlineStr"/>
+      <c r="R384" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R384"/>
+  <dimension ref="A1:R386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20228,6 +20228,102 @@
       <c r="P384" t="inlineStr"/>
       <c r="Q384" t="inlineStr"/>
       <c r="R384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>6815</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H385" t="n">
+        <v>65</v>
+      </c>
+      <c r="I385" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J385" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr"/>
+      <c r="M385" t="inlineStr"/>
+      <c r="N385" t="inlineStr"/>
+      <c r="O385" t="inlineStr"/>
+      <c r="P385" t="inlineStr"/>
+      <c r="Q385" t="inlineStr"/>
+      <c r="R385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>豐藝</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H386" t="n">
+        <v>32</v>
+      </c>
+      <c r="I386" t="inlineStr"/>
+      <c r="J386" t="inlineStr"/>
+      <c r="K386" t="inlineStr"/>
+      <c r="L386" t="inlineStr"/>
+      <c r="M386" t="inlineStr"/>
+      <c r="N386" t="inlineStr"/>
+      <c r="O386" t="inlineStr"/>
+      <c r="P386" t="inlineStr"/>
+      <c r="Q386" t="inlineStr"/>
+      <c r="R386" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="C2" t="n">
-        <v>36.4</v>
+        <v>42.9</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.14</v>
+        <v>-0.26</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.14</v>
+        <v>-1.47</v>
       </c>
       <c r="F2" t="n">
         <v>49.42</v>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="D2" t="n">
-        <v>36.4</v>
+        <v>42.9</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.14</v>
+        <v>-0.26</v>
       </c>
     </row>
   </sheetData>
@@ -13246,8 +13246,12 @@
       <c r="J243" t="n">
         <v>1.29</v>
       </c>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
+      <c r="K243" t="n">
+        <v>157</v>
+      </c>
+      <c r="L243" t="n">
+        <v>6.08</v>
+      </c>
       <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr"/>
@@ -13296,8 +13300,12 @@
       <c r="J244" t="n">
         <v>1.11</v>
       </c>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
+      <c r="K244" t="n">
+        <v>515</v>
+      </c>
+      <c r="L244" t="n">
+        <v>3</v>
+      </c>
       <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr"/>
@@ -13346,8 +13354,12 @@
       <c r="J245" t="n">
         <v>1.26</v>
       </c>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
+      <c r="K245" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="L245" t="n">
+        <v>-1.22</v>
+      </c>
       <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
@@ -13396,8 +13408,12 @@
       <c r="J246" t="n">
         <v>1.22</v>
       </c>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
+      <c r="K246" t="n">
+        <v>302.5</v>
+      </c>
+      <c r="L246" t="n">
+        <v>4.67</v>
+      </c>
       <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
@@ -13446,8 +13462,12 @@
       <c r="J247" t="n">
         <v>1.36</v>
       </c>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
+      <c r="K247" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="L247" t="n">
+        <v>-2.16</v>
+      </c>
       <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
@@ -13496,8 +13516,12 @@
       <c r="J248" t="n">
         <v>1.11</v>
       </c>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
+      <c r="K248" t="n">
+        <v>121</v>
+      </c>
+      <c r="L248" t="n">
+        <v>-0.82</v>
+      </c>
       <c r="M248" t="inlineStr"/>
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr"/>
@@ -13546,8 +13570,12 @@
       <c r="J249" t="n">
         <v>1.16</v>
       </c>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
+      <c r="K249" t="n">
+        <v>250</v>
+      </c>
+      <c r="L249" t="n">
+        <v>-0.2</v>
+      </c>
       <c r="M249" t="inlineStr"/>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr"/>
@@ -13596,8 +13624,12 @@
       <c r="J250" t="n">
         <v>1.03</v>
       </c>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
+      <c r="K250" t="n">
+        <v>1180</v>
+      </c>
+      <c r="L250" t="n">
+        <v>43.73</v>
+      </c>
       <c r="M250" t="inlineStr"/>
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr"/>
@@ -13646,8 +13678,12 @@
       <c r="J251" t="n">
         <v>1.35</v>
       </c>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
+      <c r="K251" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="L251" t="n">
+        <v>7.93</v>
+      </c>
       <c r="M251" t="inlineStr"/>
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr"/>
@@ -13696,8 +13732,12 @@
       <c r="J252" t="n">
         <v>0.66</v>
       </c>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
+      <c r="K252" t="n">
+        <v>3425</v>
+      </c>
+      <c r="L252" t="n">
+        <v>47.63</v>
+      </c>
       <c r="M252" t="inlineStr"/>
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr"/>
@@ -13746,8 +13786,12 @@
       <c r="J253" t="n">
         <v>0.4</v>
       </c>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
+      <c r="K253" t="n">
+        <v>755</v>
+      </c>
+      <c r="L253" t="n">
+        <v>6.79</v>
+      </c>
       <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr"/>
@@ -13796,8 +13840,12 @@
       <c r="J254" t="n">
         <v>0.78</v>
       </c>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
+      <c r="K254" t="n">
+        <v>2405</v>
+      </c>
+      <c r="L254" t="n">
+        <v>-0.82</v>
+      </c>
       <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr"/>
@@ -13846,8 +13894,12 @@
       <c r="J255" t="n">
         <v>0.73</v>
       </c>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
+      <c r="K255" t="n">
+        <v>113</v>
+      </c>
+      <c r="L255" t="n">
+        <v>3.2</v>
+      </c>
       <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr"/>
@@ -13896,8 +13948,12 @@
       <c r="J256" t="n">
         <v>0.64</v>
       </c>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr"/>
+      <c r="K256" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="L256" t="n">
+        <v>12.86</v>
+      </c>
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr"/>
@@ -13946,8 +14002,12 @@
       <c r="J257" t="n">
         <v>0.42</v>
       </c>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
+      <c r="K257" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="L257" t="n">
+        <v>-1.77</v>
+      </c>
       <c r="M257" t="inlineStr"/>
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr"/>
@@ -13996,8 +14056,12 @@
       <c r="J258" t="n">
         <v>0.76</v>
       </c>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
+      <c r="K258" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="L258" t="n">
+        <v>3.37</v>
+      </c>
       <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr"/>
@@ -14046,8 +14110,12 @@
       <c r="J259" t="n">
         <v>0.59</v>
       </c>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
+      <c r="K259" t="n">
+        <v>182</v>
+      </c>
+      <c r="L259" t="n">
+        <v>0.28</v>
+      </c>
       <c r="M259" t="inlineStr"/>
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr"/>
@@ -14096,8 +14164,12 @@
       <c r="J260" t="n">
         <v>0.84</v>
       </c>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
+      <c r="K260" t="n">
+        <v>42</v>
+      </c>
+      <c r="L260" t="n">
+        <v>-3</v>
+      </c>
       <c r="M260" t="inlineStr"/>
       <c r="N260" t="inlineStr"/>
       <c r="O260" t="inlineStr"/>
@@ -14146,8 +14218,12 @@
       <c r="J261" t="n">
         <v>0.67</v>
       </c>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
+      <c r="K261" t="n">
+        <v>969</v>
+      </c>
+      <c r="L261" t="n">
+        <v>-7.27</v>
+      </c>
       <c r="M261" t="inlineStr"/>
       <c r="N261" t="inlineStr"/>
       <c r="O261" t="inlineStr"/>
@@ -14196,8 +14272,12 @@
       <c r="J262" t="n">
         <v>0.92</v>
       </c>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
+      <c r="K262" t="n">
+        <v>496.5</v>
+      </c>
+      <c r="L262" t="n">
+        <v>34.55</v>
+      </c>
       <c r="M262" t="inlineStr"/>
       <c r="N262" t="inlineStr"/>
       <c r="O262" t="inlineStr"/>
@@ -14246,8 +14326,12 @@
       <c r="J263" t="n">
         <v>0.73</v>
       </c>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
+      <c r="K263" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="L263" t="n">
+        <v>37.02</v>
+      </c>
       <c r="M263" t="inlineStr"/>
       <c r="N263" t="inlineStr"/>
       <c r="O263" t="inlineStr"/>
@@ -14296,8 +14380,12 @@
       <c r="J264" t="n">
         <v>0.2</v>
       </c>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
+      <c r="K264" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="L264" t="n">
+        <v>5.25</v>
+      </c>
       <c r="M264" t="inlineStr"/>
       <c r="N264" t="inlineStr"/>
       <c r="O264" t="inlineStr"/>
@@ -14346,8 +14434,12 @@
       <c r="J265" t="n">
         <v>0.82</v>
       </c>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
+      <c r="K265" t="n">
+        <v>2035</v>
+      </c>
+      <c r="L265" t="n">
+        <v>-4.24</v>
+      </c>
       <c r="M265" t="inlineStr"/>
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr"/>
@@ -14396,8 +14488,12 @@
       <c r="J266" t="n">
         <v>0.75</v>
       </c>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
+      <c r="K266" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L266" t="n">
+        <v>38.58</v>
+      </c>
       <c r="M266" t="inlineStr"/>
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr"/>
@@ -14446,8 +14542,12 @@
       <c r="J267" t="n">
         <v>0.36</v>
       </c>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
+      <c r="K267" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="L267" t="n">
+        <v>2.38</v>
+      </c>
       <c r="M267" t="inlineStr"/>
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr"/>
@@ -14496,8 +14596,12 @@
       <c r="J268" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
+      <c r="K268" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="L268" t="n">
+        <v>-16.69</v>
+      </c>
       <c r="M268" t="inlineStr"/>
       <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr"/>
@@ -14546,8 +14650,12 @@
       <c r="J269" t="n">
         <v>0.71</v>
       </c>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
+      <c r="K269" t="n">
+        <v>55</v>
+      </c>
+      <c r="L269" t="n">
+        <v>1.48</v>
+      </c>
       <c r="M269" t="inlineStr"/>
       <c r="N269" t="inlineStr"/>
       <c r="O269" t="inlineStr"/>
@@ -14596,8 +14704,12 @@
       <c r="J270" t="n">
         <v>0.49</v>
       </c>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
+      <c r="K270" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="L270" t="n">
+        <v>16.12</v>
+      </c>
       <c r="M270" t="inlineStr"/>
       <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr"/>
@@ -14646,8 +14758,12 @@
       <c r="J271" t="n">
         <v>0.31</v>
       </c>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
+      <c r="K271" t="n">
+        <v>178</v>
+      </c>
+      <c r="L271" t="n">
+        <v>1.14</v>
+      </c>
       <c r="M271" t="inlineStr"/>
       <c r="N271" t="inlineStr"/>
       <c r="O271" t="inlineStr"/>
@@ -14696,8 +14812,12 @@
       <c r="J272" t="n">
         <v>0.36</v>
       </c>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
+      <c r="K272" t="n">
+        <v>1425</v>
+      </c>
+      <c r="L272" t="n">
+        <v>8.369999999999999</v>
+      </c>
       <c r="M272" t="inlineStr"/>
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr"/>
@@ -14742,8 +14862,12 @@
       </c>
       <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
+      <c r="K273" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="L273" t="n">
+        <v>1.43</v>
+      </c>
       <c r="M273" t="inlineStr"/>
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr"/>
@@ -14788,8 +14912,12 @@
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
+      <c r="K274" t="n">
+        <v>413.5</v>
+      </c>
+      <c r="L274" t="n">
+        <v>3.76</v>
+      </c>
       <c r="M274" t="inlineStr"/>
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr"/>
@@ -14834,8 +14962,12 @@
       </c>
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
+      <c r="K275" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L275" t="n">
+        <v>7.16</v>
+      </c>
       <c r="M275" t="inlineStr"/>
       <c r="N275" t="inlineStr"/>
       <c r="O275" t="inlineStr"/>
@@ -14880,8 +15012,12 @@
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
+      <c r="K276" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="L276" t="n">
+        <v>2.02</v>
+      </c>
       <c r="M276" t="inlineStr"/>
       <c r="N276" t="inlineStr"/>
       <c r="O276" t="inlineStr"/>
@@ -20495,7 +20631,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46210</v>
+        <v>46234</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -20504,37 +20640,41 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185.5</v>
+        <v>2320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>69</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.66</v>
+      </c>
       <c r="K3" t="n">
-        <v>247</v>
+        <v>3425</v>
       </c>
       <c r="L3" t="n">
-        <v>33.15</v>
+        <v>47.63</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -20543,12 +20683,12 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>33.15</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -20557,41 +20697,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>145.5</v>
+        <v>821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>38.8</v>
       </c>
       <c r="J4" t="n">
-        <v>0.31</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>193.5</v>
+        <v>1180</v>
       </c>
       <c r="L4" t="n">
-        <v>32.99</v>
+        <v>43.73</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -20600,12 +20740,12 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>32.99</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46219</v>
+        <v>46234</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -20614,16 +20754,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5115</v>
+        <v>902</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -20632,23 +20772,23 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I5" t="n">
-        <v>9.6</v>
+        <v>21.8</v>
       </c>
       <c r="J5" t="n">
-        <v>0.26</v>
+        <v>0.75</v>
       </c>
       <c r="K5" t="n">
-        <v>6620</v>
+        <v>1250</v>
       </c>
       <c r="L5" t="n">
-        <v>29.42</v>
+        <v>38.58</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -20657,12 +20797,12 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>29.42</v>
+        <v>38.58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -20671,37 +20811,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>181.5</v>
+        <v>131</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>69</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="I6" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.73</v>
+      </c>
       <c r="K6" t="n">
-        <v>233</v>
+        <v>179.5</v>
       </c>
       <c r="L6" t="n">
-        <v>28.37</v>
+        <v>37.02</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -20710,12 +20854,12 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>28.37</v>
+        <v>37.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46211</v>
+        <v>46234</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -20724,16 +20868,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5050</v>
+        <v>369</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -20742,23 +20886,23 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="I7" t="n">
-        <v>9.6</v>
+        <v>21.2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.26</v>
+        <v>0.92</v>
       </c>
       <c r="K7" t="n">
-        <v>6265</v>
+        <v>496.5</v>
       </c>
       <c r="L7" t="n">
-        <v>24.06</v>
+        <v>34.55</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -20767,7 +20911,7 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>24.06</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="8">
@@ -20781,41 +20925,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>155.5</v>
+        <v>185.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>62</v>
-      </c>
-      <c r="I8" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.31</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>189.5</v>
+        <v>247</v>
       </c>
       <c r="L8" t="n">
-        <v>21.86</v>
+        <v>33.15</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -20824,12 +20964,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>21.86</v>
+        <v>33.15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -20838,16 +20978,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2450</v>
+        <v>145.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -20856,23 +20996,23 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="I9" t="n">
-        <v>24.6</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
-        <v>0.66</v>
+        <v>0.31</v>
       </c>
       <c r="K9" t="n">
-        <v>2940</v>
+        <v>193.5</v>
       </c>
       <c r="L9" t="n">
-        <v>20</v>
+        <v>32.99</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -20881,12 +21021,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46226</v>
+        <v>46219</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -20895,16 +21035,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2440</v>
+        <v>5115</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -20913,23 +21053,23 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I10" t="n">
-        <v>24.6</v>
+        <v>9.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.66</v>
+        <v>0.26</v>
       </c>
       <c r="K10" t="n">
-        <v>2855</v>
+        <v>6620</v>
       </c>
       <c r="L10" t="n">
-        <v>17.01</v>
+        <v>29.42</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -20938,12 +21078,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>17.01</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -20961,7 +21101,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>193.5</v>
+        <v>181.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -20979,10 +21119,10 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>222.5</v>
+        <v>233</v>
       </c>
       <c r="L11" t="n">
-        <v>14.99</v>
+        <v>28.37</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -20991,12 +21131,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>14.99</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46218</v>
+        <v>46211</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -21005,16 +21145,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>426</v>
+        <v>5050</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -21023,23 +21163,23 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I12" t="n">
-        <v>21.2</v>
+        <v>9.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.92</v>
+        <v>0.26</v>
       </c>
       <c r="K12" t="n">
-        <v>488</v>
+        <v>6265</v>
       </c>
       <c r="L12" t="n">
-        <v>14.55</v>
+        <v>24.06</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -21048,12 +21188,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>14.55</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -21062,41 +21202,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>61.1</v>
+        <v>155.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="I13" t="n">
-        <v>21.3</v>
+        <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>1.35</v>
+        <v>0.31</v>
       </c>
       <c r="K13" t="n">
-        <v>69.90000000000001</v>
+        <v>189.5</v>
       </c>
       <c r="L13" t="n">
-        <v>14.4</v>
+        <v>21.86</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -21105,12 +21245,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>14.4</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -21119,16 +21259,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>896</v>
+        <v>2450</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -21141,19 +21281,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>21.8</v>
+        <v>24.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="K14" t="n">
-        <v>1010</v>
+        <v>2940</v>
       </c>
       <c r="L14" t="n">
-        <v>12.72</v>
+        <v>20</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -21162,7 +21302,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12.72</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -21176,37 +21316,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>210</v>
+        <v>2440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>69</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I15" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.66</v>
+      </c>
       <c r="K15" t="n">
-        <v>235.5</v>
+        <v>2855</v>
       </c>
       <c r="L15" t="n">
-        <v>12.14</v>
+        <v>17.01</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -21215,12 +21359,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>12.14</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46226</v>
+        <v>46234</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -21229,20 +21373,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>378.5</v>
+        <v>291.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -21251,15 +21395,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>77</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I16" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.49</v>
+      </c>
       <c r="K16" t="n">
-        <v>422.5</v>
+        <v>338.5</v>
       </c>
       <c r="L16" t="n">
-        <v>11.62</v>
+        <v>16.12</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -21268,12 +21416,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>11.62</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -21282,20 +21430,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>237</v>
+        <v>193.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -21304,19 +21452,15 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>77</v>
-      </c>
-      <c r="I17" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.16</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>264.5</v>
+        <v>222.5</v>
       </c>
       <c r="L17" t="n">
-        <v>11.6</v>
+        <v>14.99</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -21325,12 +21469,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>11.6</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46226</v>
+        <v>46218</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -21348,7 +21492,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -21370,10 +21514,10 @@
         <v>0.92</v>
       </c>
       <c r="K18" t="n">
-        <v>450</v>
+        <v>488</v>
       </c>
       <c r="L18" t="n">
-        <v>10.84</v>
+        <v>14.55</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -21382,12 +21526,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>10.84</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46227</v>
+        <v>46218</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -21396,20 +21540,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5730</v>
+        <v>61.1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -21418,19 +21562,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I19" t="n">
-        <v>9.6</v>
+        <v>21.3</v>
       </c>
       <c r="J19" t="n">
-        <v>0.26</v>
+        <v>1.35</v>
       </c>
       <c r="K19" t="n">
-        <v>6300</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>9.949999999999999</v>
+        <v>14.4</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -21439,12 +21583,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>9.949999999999999</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46202</v>
+        <v>46234</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -21453,16 +21597,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>154.5</v>
+        <v>105</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -21471,23 +21615,23 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="I20" t="n">
-        <v>10</v>
+        <v>12.3</v>
       </c>
       <c r="J20" t="n">
-        <v>0.31</v>
+        <v>0.64</v>
       </c>
       <c r="K20" t="n">
-        <v>169.5</v>
+        <v>118.5</v>
       </c>
       <c r="L20" t="n">
-        <v>9.710000000000001</v>
+        <v>12.86</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -21496,12 +21640,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>9.710000000000001</v>
+        <v>12.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -21519,7 +21663,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>970</v>
+        <v>896</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -21541,10 +21685,10 @@
         <v>0.75</v>
       </c>
       <c r="K21" t="n">
-        <v>1060</v>
+        <v>1010</v>
       </c>
       <c r="L21" t="n">
-        <v>9.279999999999999</v>
+        <v>12.72</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -21553,7 +21697,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>9.279999999999999</v>
+        <v>12.72</v>
       </c>
     </row>
   </sheetData>
@@ -22467,7 +22611,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46210</v>
+        <v>46234</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -22476,16 +22620,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>475.5</v>
+        <v>72.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -22494,23 +22638,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I16" t="n">
-        <v>21.2</v>
+        <v>6.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>397.5</v>
+        <v>60.4</v>
       </c>
       <c r="L16" t="n">
-        <v>-16.4</v>
+        <v>-16.69</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -22519,12 +22663,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-16.4</v>
+        <v>-16.69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -22533,16 +22677,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>72.7</v>
+        <v>475.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -22551,23 +22695,23 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>21.2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="K17" t="n">
-        <v>61</v>
+        <v>397.5</v>
       </c>
       <c r="L17" t="n">
-        <v>-16.09</v>
+        <v>-16.4</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -22576,12 +22720,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-16.09</v>
+        <v>-16.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46226</v>
+        <v>46218</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -22590,20 +22734,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>143</v>
+        <v>72.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -22612,19 +22756,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I18" t="n">
-        <v>16.4</v>
+        <v>6.8</v>
       </c>
       <c r="J18" t="n">
-        <v>1.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="L18" t="n">
-        <v>-16.08</v>
+        <v>-16.09</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -22633,12 +22777,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-16.08</v>
+        <v>-16.09</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46202</v>
+        <v>46226</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -22647,20 +22791,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>367</v>
+        <v>143</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -22669,19 +22813,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="I19" t="n">
-        <v>13.2</v>
+        <v>16.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0.49</v>
+        <v>1.11</v>
       </c>
       <c r="K19" t="n">
-        <v>309.5</v>
+        <v>120</v>
       </c>
       <c r="L19" t="n">
-        <v>-15.67</v>
+        <v>-16.08</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -22690,12 +22834,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-15.67</v>
+        <v>-16.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46205</v>
+        <v>46202</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -22704,20 +22848,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>37.6</v>
+        <v>367</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -22726,15 +22870,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>75</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I20" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.49</v>
+      </c>
       <c r="K20" t="n">
-        <v>31.95</v>
+        <v>309.5</v>
       </c>
       <c r="L20" t="n">
-        <v>-15.03</v>
+        <v>-15.67</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -22743,12 +22891,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-15.03</v>
+        <v>-15.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -22757,20 +22905,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>996</v>
+        <v>37.6</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -22779,19 +22927,15 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>76</v>
-      </c>
-      <c r="I21" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.03</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>847</v>
+        <v>31.95</v>
       </c>
       <c r="L21" t="n">
-        <v>-14.96</v>
+        <v>-15.03</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -22800,7 +22944,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-14.96</v>
+        <v>-15.03</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,22 +468,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C2" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.26</v>
+        <v>-0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.47</v>
+        <v>-1.54</v>
       </c>
       <c r="F2" t="n">
         <v>49.42</v>
       </c>
       <c r="G2" t="n">
-        <v>-32.03</v>
+        <v>-55.95</v>
       </c>
     </row>
     <row r="3">
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D2" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.26</v>
+        <v>-0.57</v>
       </c>
     </row>
   </sheetData>
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R386"/>
+  <dimension ref="A1:R387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15066,8 +15066,12 @@
       <c r="J277" t="n">
         <v>0.26</v>
       </c>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
+      <c r="K277" t="n">
+        <v>2610</v>
+      </c>
+      <c r="L277" t="n">
+        <v>-55.95</v>
+      </c>
       <c r="M277" t="inlineStr"/>
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr"/>
@@ -20460,6 +20464,52 @@
       <c r="P386" t="inlineStr"/>
       <c r="Q386" t="inlineStr"/>
       <c r="R386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>信立</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H387" t="n">
+        <v>75</v>
+      </c>
+      <c r="I387" t="inlineStr"/>
+      <c r="J387" t="inlineStr"/>
+      <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr"/>
+      <c r="M387" t="inlineStr"/>
+      <c r="N387" t="inlineStr"/>
+      <c r="O387" t="inlineStr"/>
+      <c r="P387" t="inlineStr"/>
+      <c r="Q387" t="inlineStr"/>
+      <c r="R387" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21813,7 +21863,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46202</v>
+        <v>46237</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -21822,16 +21872,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>499.5</v>
+        <v>5925</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -21840,23 +21890,23 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I2" t="n">
-        <v>21.2</v>
+        <v>9.6</v>
       </c>
       <c r="J2" t="n">
-        <v>0.92</v>
+        <v>0.26</v>
       </c>
       <c r="K2" t="n">
-        <v>339.5</v>
+        <v>2610</v>
       </c>
       <c r="L2" t="n">
-        <v>-32.03</v>
+        <v>-55.95</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -21865,7 +21915,7 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-32.03</v>
+        <v>-55.95</v>
       </c>
     </row>
     <row r="3">
@@ -21879,16 +21929,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>955</v>
+        <v>499.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -21901,19 +21951,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I3" t="n">
-        <v>14.2</v>
+        <v>21.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4</v>
+        <v>0.92</v>
       </c>
       <c r="K3" t="n">
-        <v>671</v>
+        <v>339.5</v>
       </c>
       <c r="L3" t="n">
-        <v>-29.74</v>
+        <v>-32.03</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -21922,7 +21972,7 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>-29.74</v>
+        <v>-32.03</v>
       </c>
     </row>
     <row r="4">
@@ -21936,16 +21986,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65.5</v>
+        <v>955</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -21954,23 +22004,23 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>10.4</v>
+        <v>14.2</v>
       </c>
       <c r="J4" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="K4" t="n">
-        <v>51.7</v>
+        <v>671</v>
       </c>
       <c r="L4" t="n">
-        <v>-21.07</v>
+        <v>-29.74</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -21979,12 +22029,12 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>-21.07</v>
+        <v>-29.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -21993,20 +22043,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>158</v>
+        <v>65.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -22018,16 +22068,16 @@
         <v>77</v>
       </c>
       <c r="I5" t="n">
-        <v>16.4</v>
+        <v>10.4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.11</v>
+        <v>0.71</v>
       </c>
       <c r="K5" t="n">
-        <v>125.5</v>
+        <v>51.7</v>
       </c>
       <c r="L5" t="n">
-        <v>-20.57</v>
+        <v>-21.07</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -22036,12 +22086,12 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-20.57</v>
+        <v>-21.07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -22050,16 +22100,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>344.5</v>
+        <v>158</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -22068,23 +22118,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I6" t="n">
-        <v>27.5</v>
+        <v>16.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="K6" t="n">
-        <v>277.5</v>
+        <v>125.5</v>
       </c>
       <c r="L6" t="n">
-        <v>-19.45</v>
+        <v>-20.57</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -22093,7 +22143,7 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>-19.45</v>
+        <v>-20.57</v>
       </c>
     </row>
     <row r="7">
@@ -22107,20 +22157,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1215</v>
+        <v>344.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -22132,16 +22182,16 @@
         <v>90</v>
       </c>
       <c r="I7" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.67</v>
+        <v>1.22</v>
       </c>
       <c r="K7" t="n">
-        <v>981</v>
+        <v>277.5</v>
       </c>
       <c r="L7" t="n">
-        <v>-19.26</v>
+        <v>-19.45</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -22150,7 +22200,7 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>-19.26</v>
+        <v>-19.45</v>
       </c>
     </row>
     <row r="8">
@@ -22164,41 +22214,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>143</v>
+        <v>1215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I8" t="n">
-        <v>16.4</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="K8" t="n">
-        <v>115.5</v>
+        <v>981</v>
       </c>
       <c r="L8" t="n">
-        <v>-19.23</v>
+        <v>-19.26</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -22207,7 +22257,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>-19.23</v>
+        <v>-19.26</v>
       </c>
     </row>
     <row r="9">
@@ -22221,41 +22271,41 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>34.2</v>
+        <v>143</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>16.4</v>
       </c>
       <c r="J9" t="n">
-        <v>0.42</v>
+        <v>1.11</v>
       </c>
       <c r="K9" t="n">
-        <v>27.65</v>
+        <v>115.5</v>
       </c>
       <c r="L9" t="n">
-        <v>-19.15</v>
+        <v>-19.23</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -22264,12 +22314,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>-19.15</v>
+        <v>-19.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -22278,16 +22328,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>373</v>
+        <v>34.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -22296,23 +22346,23 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="I10" t="n">
-        <v>13.2</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="K10" t="n">
-        <v>302</v>
+        <v>27.65</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.03</v>
+        <v>-19.15</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -22321,12 +22371,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-19.03</v>
+        <v>-19.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46226</v>
+        <v>46210</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -22335,20 +22385,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1190</v>
+        <v>373</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -22357,19 +22407,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="I11" t="n">
-        <v>38.8</v>
+        <v>13.2</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>0.49</v>
       </c>
       <c r="K11" t="n">
-        <v>967</v>
+        <v>302</v>
       </c>
       <c r="L11" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -22378,7 +22428,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
     </row>
     <row r="12">
@@ -22440,7 +22490,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46202</v>
+        <v>46226</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -22449,41 +22499,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2340</v>
+        <v>1190</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I13" t="n">
-        <v>30.7</v>
+        <v>38.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.82</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
-        <v>1910</v>
+        <v>967</v>
       </c>
       <c r="L13" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -22492,12 +22542,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46226</v>
+        <v>46202</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -22506,16 +22556,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1180</v>
+        <v>2340</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -22528,19 +22578,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>30.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
       <c r="K14" t="n">
-        <v>967</v>
+        <v>1910</v>
       </c>
       <c r="L14" t="n">
-        <v>-18.05</v>
+        <v>-18.38</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -22549,7 +22599,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-18.05</v>
+        <v>-18.38</v>
       </c>
     </row>
     <row r="15">
@@ -22563,16 +22613,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>72.59999999999999</v>
+        <v>1180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -22581,23 +22631,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I15" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="K15" t="n">
-        <v>59.6</v>
+        <v>967</v>
       </c>
       <c r="L15" t="n">
-        <v>-17.91</v>
+        <v>-18.05</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -22606,12 +22656,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-17.91</v>
+        <v>-18.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -22629,7 +22679,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -22651,10 +22701,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>60.4</v>
+        <v>59.6</v>
       </c>
       <c r="L16" t="n">
-        <v>-16.69</v>
+        <v>-17.91</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -22663,12 +22713,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-16.69</v>
+        <v>-17.91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46210</v>
+        <v>46234</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -22677,16 +22727,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>475.5</v>
+        <v>72.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -22695,23 +22745,23 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I17" t="n">
-        <v>21.2</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>397.5</v>
+        <v>60.4</v>
       </c>
       <c r="L17" t="n">
-        <v>-16.4</v>
+        <v>-16.69</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -22720,12 +22770,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-16.4</v>
+        <v>-16.69</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -22734,16 +22784,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>72.7</v>
+        <v>475.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -22752,23 +22802,23 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I18" t="n">
-        <v>6.8</v>
+        <v>21.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="K18" t="n">
-        <v>61</v>
+        <v>397.5</v>
       </c>
       <c r="L18" t="n">
-        <v>-16.09</v>
+        <v>-16.4</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -22777,12 +22827,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-16.09</v>
+        <v>-16.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46226</v>
+        <v>46218</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -22791,20 +22841,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>143</v>
+        <v>72.7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -22813,19 +22863,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I19" t="n">
-        <v>16.4</v>
+        <v>6.8</v>
       </c>
       <c r="J19" t="n">
-        <v>1.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="L19" t="n">
-        <v>-16.08</v>
+        <v>-16.09</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -22834,12 +22884,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-16.08</v>
+        <v>-16.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46202</v>
+        <v>46226</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -22848,20 +22898,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>367</v>
+        <v>143</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -22870,19 +22920,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="I20" t="n">
-        <v>13.2</v>
+        <v>16.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0.49</v>
+        <v>1.11</v>
       </c>
       <c r="K20" t="n">
-        <v>309.5</v>
+        <v>120</v>
       </c>
       <c r="L20" t="n">
-        <v>-15.67</v>
+        <v>-16.08</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -22891,12 +22941,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-15.67</v>
+        <v>-16.08</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46205</v>
+        <v>46202</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -22905,20 +22955,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>37.6</v>
+        <v>367</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -22927,15 +22977,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>75</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I21" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.49</v>
+      </c>
       <c r="K21" t="n">
-        <v>31.95</v>
+        <v>309.5</v>
       </c>
       <c r="L21" t="n">
-        <v>-15.03</v>
+        <v>-15.67</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -22944,7 +22998,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-15.03</v>
+        <v>-15.67</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R387"/>
+  <dimension ref="A1:R421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20510,6 +20510,1690 @@
       <c r="P387" t="inlineStr"/>
       <c r="Q387" t="inlineStr"/>
       <c r="R387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H388" t="n">
+        <v>97</v>
+      </c>
+      <c r="I388" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J388" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr"/>
+      <c r="N388" t="inlineStr"/>
+      <c r="O388" t="inlineStr"/>
+      <c r="P388" t="inlineStr"/>
+      <c r="Q388" t="inlineStr"/>
+      <c r="R388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>527</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H389" t="n">
+        <v>96</v>
+      </c>
+      <c r="I389" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J389" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr"/>
+      <c r="N389" t="inlineStr"/>
+      <c r="O389" t="inlineStr"/>
+      <c r="P389" t="inlineStr"/>
+      <c r="Q389" t="inlineStr"/>
+      <c r="R389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>122</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H390" t="n">
+        <v>91</v>
+      </c>
+      <c r="I390" t="n">
+        <v>15</v>
+      </c>
+      <c r="J390" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr"/>
+      <c r="M390" t="inlineStr"/>
+      <c r="N390" t="inlineStr"/>
+      <c r="O390" t="inlineStr"/>
+      <c r="P390" t="inlineStr"/>
+      <c r="Q390" t="inlineStr"/>
+      <c r="R390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>299</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H391" t="n">
+        <v>90</v>
+      </c>
+      <c r="I391" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J391" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K391" t="inlineStr"/>
+      <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr"/>
+      <c r="N391" t="inlineStr"/>
+      <c r="O391" t="inlineStr"/>
+      <c r="P391" t="inlineStr"/>
+      <c r="Q391" t="inlineStr"/>
+      <c r="R391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H392" t="n">
+        <v>87</v>
+      </c>
+      <c r="I392" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J392" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K392" t="inlineStr"/>
+      <c r="L392" t="inlineStr"/>
+      <c r="M392" t="inlineStr"/>
+      <c r="N392" t="inlineStr"/>
+      <c r="O392" t="inlineStr"/>
+      <c r="P392" t="inlineStr"/>
+      <c r="Q392" t="inlineStr"/>
+      <c r="R392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>120</v>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H393" t="n">
+        <v>77</v>
+      </c>
+      <c r="I393" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J393" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K393" t="inlineStr"/>
+      <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr"/>
+      <c r="N393" t="inlineStr"/>
+      <c r="O393" t="inlineStr"/>
+      <c r="P393" t="inlineStr"/>
+      <c r="Q393" t="inlineStr"/>
+      <c r="R393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>247.5</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H394" t="n">
+        <v>77</v>
+      </c>
+      <c r="I394" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J394" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr"/>
+      <c r="N394" t="inlineStr"/>
+      <c r="O394" t="inlineStr"/>
+      <c r="P394" t="inlineStr"/>
+      <c r="Q394" t="inlineStr"/>
+      <c r="R394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>1075</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H395" t="n">
+        <v>76</v>
+      </c>
+      <c r="I395" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J395" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr"/>
+      <c r="O395" t="inlineStr"/>
+      <c r="P395" t="inlineStr"/>
+      <c r="Q395" t="inlineStr"/>
+      <c r="R395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>65</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H396" t="n">
+        <v>68</v>
+      </c>
+      <c r="I396" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J396" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr"/>
+      <c r="N396" t="inlineStr"/>
+      <c r="O396" t="inlineStr"/>
+      <c r="P396" t="inlineStr"/>
+      <c r="Q396" t="inlineStr"/>
+      <c r="R396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H397" t="n">
+        <v>100</v>
+      </c>
+      <c r="I397" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J397" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K397" t="inlineStr"/>
+      <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="inlineStr"/>
+      <c r="O397" t="inlineStr"/>
+      <c r="P397" t="inlineStr"/>
+      <c r="Q397" t="inlineStr"/>
+      <c r="R397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>712</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H398" t="n">
+        <v>100</v>
+      </c>
+      <c r="I398" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J398" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K398" t="inlineStr"/>
+      <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr"/>
+      <c r="N398" t="inlineStr"/>
+      <c r="O398" t="inlineStr"/>
+      <c r="P398" t="inlineStr"/>
+      <c r="Q398" t="inlineStr"/>
+      <c r="R398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>2390</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H399" t="n">
+        <v>100</v>
+      </c>
+      <c r="I399" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J399" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K399" t="inlineStr"/>
+      <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr"/>
+      <c r="O399" t="inlineStr"/>
+      <c r="P399" t="inlineStr"/>
+      <c r="Q399" t="inlineStr"/>
+      <c r="R399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>109</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H400" t="n">
+        <v>97</v>
+      </c>
+      <c r="I400" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J400" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="inlineStr"/>
+      <c r="O400" t="inlineStr"/>
+      <c r="P400" t="inlineStr"/>
+      <c r="Q400" t="inlineStr"/>
+      <c r="R400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H401" t="n">
+        <v>94</v>
+      </c>
+      <c r="I401" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J401" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="inlineStr"/>
+      <c r="O401" t="inlineStr"/>
+      <c r="P401" t="inlineStr"/>
+      <c r="Q401" t="inlineStr"/>
+      <c r="R401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H402" t="n">
+        <v>94</v>
+      </c>
+      <c r="I402" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J402" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr"/>
+      <c r="N402" t="inlineStr"/>
+      <c r="O402" t="inlineStr"/>
+      <c r="P402" t="inlineStr"/>
+      <c r="Q402" t="inlineStr"/>
+      <c r="R402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>110</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H403" t="n">
+        <v>94</v>
+      </c>
+      <c r="I403" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J403" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="inlineStr"/>
+      <c r="O403" t="inlineStr"/>
+      <c r="P403" t="inlineStr"/>
+      <c r="Q403" t="inlineStr"/>
+      <c r="R403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>180</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H404" t="n">
+        <v>94</v>
+      </c>
+      <c r="I404" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J404" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr"/>
+      <c r="O404" t="inlineStr"/>
+      <c r="P404" t="inlineStr"/>
+      <c r="Q404" t="inlineStr"/>
+      <c r="R404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H405" t="n">
+        <v>92</v>
+      </c>
+      <c r="I405" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J405" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr"/>
+      <c r="O405" t="inlineStr"/>
+      <c r="P405" t="inlineStr"/>
+      <c r="Q405" t="inlineStr"/>
+      <c r="R405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>948</v>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H406" t="n">
+        <v>90</v>
+      </c>
+      <c r="I406" t="n">
+        <v>25</v>
+      </c>
+      <c r="J406" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr"/>
+      <c r="M406" t="inlineStr"/>
+      <c r="N406" t="inlineStr"/>
+      <c r="O406" t="inlineStr"/>
+      <c r="P406" t="inlineStr"/>
+      <c r="Q406" t="inlineStr"/>
+      <c r="R406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H407" t="n">
+        <v>90</v>
+      </c>
+      <c r="I407" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J407" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K407" t="inlineStr"/>
+      <c r="L407" t="inlineStr"/>
+      <c r="M407" t="inlineStr"/>
+      <c r="N407" t="inlineStr"/>
+      <c r="O407" t="inlineStr"/>
+      <c r="P407" t="inlineStr"/>
+      <c r="Q407" t="inlineStr"/>
+      <c r="R407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H408" t="n">
+        <v>90</v>
+      </c>
+      <c r="I408" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J408" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K408" t="inlineStr"/>
+      <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="inlineStr"/>
+      <c r="O408" t="inlineStr"/>
+      <c r="P408" t="inlineStr"/>
+      <c r="Q408" t="inlineStr"/>
+      <c r="R408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H409" t="n">
+        <v>84</v>
+      </c>
+      <c r="I409" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J409" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K409" t="inlineStr"/>
+      <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr"/>
+      <c r="O409" t="inlineStr"/>
+      <c r="P409" t="inlineStr"/>
+      <c r="Q409" t="inlineStr"/>
+      <c r="R409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>2090</v>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H410" t="n">
+        <v>80</v>
+      </c>
+      <c r="I410" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J410" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr"/>
+      <c r="O410" t="inlineStr"/>
+      <c r="P410" t="inlineStr"/>
+      <c r="Q410" t="inlineStr"/>
+      <c r="R410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H411" t="n">
+        <v>80</v>
+      </c>
+      <c r="I411" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J411" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="inlineStr"/>
+      <c r="O411" t="inlineStr"/>
+      <c r="P411" t="inlineStr"/>
+      <c r="Q411" t="inlineStr"/>
+      <c r="R411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H412" t="n">
+        <v>79</v>
+      </c>
+      <c r="I412" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J412" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="inlineStr"/>
+      <c r="O412" t="inlineStr"/>
+      <c r="P412" t="inlineStr"/>
+      <c r="Q412" t="inlineStr"/>
+      <c r="R412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>61</v>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H413" t="n">
+        <v>78</v>
+      </c>
+      <c r="I413" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J413" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="inlineStr"/>
+      <c r="O413" t="inlineStr"/>
+      <c r="P413" t="inlineStr"/>
+      <c r="Q413" t="inlineStr"/>
+      <c r="R413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H414" t="n">
+        <v>77</v>
+      </c>
+      <c r="I414" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J414" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
+      <c r="N414" t="inlineStr"/>
+      <c r="O414" t="inlineStr"/>
+      <c r="P414" t="inlineStr"/>
+      <c r="Q414" t="inlineStr"/>
+      <c r="R414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>335</v>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H415" t="n">
+        <v>65</v>
+      </c>
+      <c r="I415" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J415" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" t="inlineStr"/>
+      <c r="O415" t="inlineStr"/>
+      <c r="P415" t="inlineStr"/>
+      <c r="Q415" t="inlineStr"/>
+      <c r="R415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H416" t="n">
+        <v>62</v>
+      </c>
+      <c r="I416" t="n">
+        <v>10</v>
+      </c>
+      <c r="J416" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr"/>
+      <c r="N416" t="inlineStr"/>
+      <c r="O416" t="inlineStr"/>
+      <c r="P416" t="inlineStr"/>
+      <c r="Q416" t="inlineStr"/>
+      <c r="R416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H417" t="n">
+        <v>60</v>
+      </c>
+      <c r="I417" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J417" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr"/>
+      <c r="N417" t="inlineStr"/>
+      <c r="O417" t="inlineStr"/>
+      <c r="P417" t="inlineStr"/>
+      <c r="Q417" t="inlineStr"/>
+      <c r="R417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>70</v>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H418" t="n">
+        <v>79</v>
+      </c>
+      <c r="I418" t="inlineStr"/>
+      <c r="J418" t="inlineStr"/>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr"/>
+      <c r="M418" t="inlineStr"/>
+      <c r="N418" t="inlineStr"/>
+      <c r="O418" t="inlineStr"/>
+      <c r="P418" t="inlineStr"/>
+      <c r="Q418" t="inlineStr"/>
+      <c r="R418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>395</v>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H419" t="n">
+        <v>77</v>
+      </c>
+      <c r="I419" t="inlineStr"/>
+      <c r="J419" t="inlineStr"/>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr"/>
+      <c r="N419" t="inlineStr"/>
+      <c r="O419" t="inlineStr"/>
+      <c r="P419" t="inlineStr"/>
+      <c r="Q419" t="inlineStr"/>
+      <c r="R419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H420" t="n">
+        <v>77</v>
+      </c>
+      <c r="I420" t="inlineStr"/>
+      <c r="J420" t="inlineStr"/>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr"/>
+      <c r="N420" t="inlineStr"/>
+      <c r="O420" t="inlineStr"/>
+      <c r="P420" t="inlineStr"/>
+      <c r="Q420" t="inlineStr"/>
+      <c r="R420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>217</v>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H421" t="n">
+        <v>69</v>
+      </c>
+      <c r="I421" t="inlineStr"/>
+      <c r="J421" t="inlineStr"/>
+      <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr"/>
+      <c r="N421" t="inlineStr"/>
+      <c r="O421" t="inlineStr"/>
+      <c r="P421" t="inlineStr"/>
+      <c r="Q421" t="inlineStr"/>
+      <c r="R421" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R421"/>
+  <dimension ref="A1:R423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22194,6 +22194,102 @@
       <c r="P421" t="inlineStr"/>
       <c r="Q421" t="inlineStr"/>
       <c r="R421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>2490</v>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H422" t="n">
+        <v>65</v>
+      </c>
+      <c r="I422" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J422" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr"/>
+      <c r="N422" t="inlineStr"/>
+      <c r="O422" t="inlineStr"/>
+      <c r="P422" t="inlineStr"/>
+      <c r="Q422" t="inlineStr"/>
+      <c r="R422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>豐藝</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H423" t="n">
+        <v>32</v>
+      </c>
+      <c r="I423" t="inlineStr"/>
+      <c r="J423" t="inlineStr"/>
+      <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr"/>
+      <c r="N423" t="inlineStr"/>
+      <c r="O423" t="inlineStr"/>
+      <c r="P423" t="inlineStr"/>
+      <c r="Q423" t="inlineStr"/>
+      <c r="R423" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="C2" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.57</v>
+        <v>-0.24</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.54</v>
+        <v>-1.44</v>
       </c>
       <c r="F2" t="n">
         <v>49.42</v>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="D2" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.57</v>
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -15120,8 +15120,12 @@
       <c r="J278" t="n">
         <v>1.29</v>
       </c>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
+      <c r="K278" t="n">
+        <v>154</v>
+      </c>
+      <c r="L278" t="n">
+        <v>4.76</v>
+      </c>
       <c r="M278" t="inlineStr"/>
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr"/>
@@ -15170,8 +15174,12 @@
       <c r="J279" t="n">
         <v>1.11</v>
       </c>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
+      <c r="K279" t="n">
+        <v>535</v>
+      </c>
+      <c r="L279" t="n">
+        <v>4.09</v>
+      </c>
       <c r="M279" t="inlineStr"/>
       <c r="N279" t="inlineStr"/>
       <c r="O279" t="inlineStr"/>
@@ -15220,8 +15228,12 @@
       <c r="J280" t="n">
         <v>1.26</v>
       </c>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
+      <c r="K280" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="L280" t="n">
+        <v>0</v>
+      </c>
       <c r="M280" t="inlineStr"/>
       <c r="N280" t="inlineStr"/>
       <c r="O280" t="inlineStr"/>
@@ -15270,8 +15282,12 @@
       <c r="J281" t="n">
         <v>1.22</v>
       </c>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
+      <c r="K281" t="n">
+        <v>302.5</v>
+      </c>
+      <c r="L281" t="n">
+        <v>-2.1</v>
+      </c>
       <c r="M281" t="inlineStr"/>
       <c r="N281" t="inlineStr"/>
       <c r="O281" t="inlineStr"/>
@@ -15320,8 +15336,12 @@
       <c r="J282" t="n">
         <v>1.36</v>
       </c>
-      <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
+      <c r="K282" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="L282" t="n">
+        <v>-3.95</v>
+      </c>
       <c r="M282" t="inlineStr"/>
       <c r="N282" t="inlineStr"/>
       <c r="O282" t="inlineStr"/>
@@ -15370,8 +15390,12 @@
       <c r="J283" t="n">
         <v>1.11</v>
       </c>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
+      <c r="K283" t="n">
+        <v>126</v>
+      </c>
+      <c r="L283" t="n">
+        <v>-2.7</v>
+      </c>
       <c r="M283" t="inlineStr"/>
       <c r="N283" t="inlineStr"/>
       <c r="O283" t="inlineStr"/>
@@ -15420,8 +15444,12 @@
       <c r="J284" t="n">
         <v>1.16</v>
       </c>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
+      <c r="K284" t="n">
+        <v>252</v>
+      </c>
+      <c r="L284" t="n">
+        <v>-4.73</v>
+      </c>
       <c r="M284" t="inlineStr"/>
       <c r="N284" t="inlineStr"/>
       <c r="O284" t="inlineStr"/>
@@ -15470,8 +15498,12 @@
       <c r="J285" t="n">
         <v>1.03</v>
       </c>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
+      <c r="K285" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L285" t="n">
+        <v>14.29</v>
+      </c>
       <c r="M285" t="inlineStr"/>
       <c r="N285" t="inlineStr"/>
       <c r="O285" t="inlineStr"/>
@@ -15520,8 +15552,12 @@
       <c r="J286" t="n">
         <v>1.35</v>
       </c>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
+      <c r="K286" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="L286" t="n">
+        <v>-2.58</v>
+      </c>
       <c r="M286" t="inlineStr"/>
       <c r="N286" t="inlineStr"/>
       <c r="O286" t="inlineStr"/>
@@ -15570,8 +15606,12 @@
       <c r="J287" t="n">
         <v>0.66</v>
       </c>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
+      <c r="K287" t="n">
+        <v>3380</v>
+      </c>
+      <c r="L287" t="n">
+        <v>22.24</v>
+      </c>
       <c r="M287" t="inlineStr"/>
       <c r="N287" t="inlineStr"/>
       <c r="O287" t="inlineStr"/>
@@ -15620,8 +15660,12 @@
       <c r="J288" t="n">
         <v>0.4</v>
       </c>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
+      <c r="K288" t="n">
+        <v>750</v>
+      </c>
+      <c r="L288" t="n">
+        <v>-7.18</v>
+      </c>
       <c r="M288" t="inlineStr"/>
       <c r="N288" t="inlineStr"/>
       <c r="O288" t="inlineStr"/>
@@ -15670,8 +15714,12 @@
       <c r="J289" t="n">
         <v>0.78</v>
       </c>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
+      <c r="K289" t="n">
+        <v>2465</v>
+      </c>
+      <c r="L289" t="n">
+        <v>3.57</v>
+      </c>
       <c r="M289" t="inlineStr"/>
       <c r="N289" t="inlineStr"/>
       <c r="O289" t="inlineStr"/>
@@ -15720,8 +15768,12 @@
       <c r="J290" t="n">
         <v>0.73</v>
       </c>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
+      <c r="K290" t="n">
+        <v>111</v>
+      </c>
+      <c r="L290" t="n">
+        <v>1.83</v>
+      </c>
       <c r="M290" t="inlineStr"/>
       <c r="N290" t="inlineStr"/>
       <c r="O290" t="inlineStr"/>
@@ -15770,8 +15822,12 @@
       <c r="J291" t="n">
         <v>0.64</v>
       </c>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
+      <c r="K291" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="L291" t="n">
+        <v>1.81</v>
+      </c>
       <c r="M291" t="inlineStr"/>
       <c r="N291" t="inlineStr"/>
       <c r="O291" t="inlineStr"/>
@@ -15820,8 +15876,12 @@
       <c r="J292" t="n">
         <v>0.42</v>
       </c>
-      <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
+      <c r="K292" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="L292" t="n">
+        <v>-4.31</v>
+      </c>
       <c r="M292" t="inlineStr"/>
       <c r="N292" t="inlineStr"/>
       <c r="O292" t="inlineStr"/>
@@ -15870,8 +15930,12 @@
       <c r="J293" t="n">
         <v>0.76</v>
       </c>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
+      <c r="K293" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="L293" t="n">
+        <v>1.38</v>
+      </c>
       <c r="M293" t="inlineStr"/>
       <c r="N293" t="inlineStr"/>
       <c r="O293" t="inlineStr"/>
@@ -15920,8 +15984,12 @@
       <c r="J294" t="n">
         <v>0.59</v>
       </c>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
+      <c r="K294" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="L294" t="n">
+        <v>-3.25</v>
+      </c>
       <c r="M294" t="inlineStr"/>
       <c r="N294" t="inlineStr"/>
       <c r="O294" t="inlineStr"/>
@@ -15970,8 +16038,12 @@
       <c r="J295" t="n">
         <v>0.84</v>
       </c>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
+      <c r="K295" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="L295" t="n">
+        <v>-0.23</v>
+      </c>
       <c r="M295" t="inlineStr"/>
       <c r="N295" t="inlineStr"/>
       <c r="O295" t="inlineStr"/>
@@ -16020,8 +16092,12 @@
       <c r="J296" t="n">
         <v>0.67</v>
       </c>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
+      <c r="K296" t="n">
+        <v>916</v>
+      </c>
+      <c r="L296" t="n">
+        <v>-14.79</v>
+      </c>
       <c r="M296" t="inlineStr"/>
       <c r="N296" t="inlineStr"/>
       <c r="O296" t="inlineStr"/>
@@ -16070,8 +16146,12 @@
       <c r="J297" t="n">
         <v>0.92</v>
       </c>
-      <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
+      <c r="K297" t="n">
+        <v>509</v>
+      </c>
+      <c r="L297" t="n">
+        <v>26.77</v>
+      </c>
       <c r="M297" t="inlineStr"/>
       <c r="N297" t="inlineStr"/>
       <c r="O297" t="inlineStr"/>
@@ -16120,8 +16200,12 @@
       <c r="J298" t="n">
         <v>0.73</v>
       </c>
-      <c r="K298" t="inlineStr"/>
-      <c r="L298" t="inlineStr"/>
+      <c r="K298" t="n">
+        <v>167.5</v>
+      </c>
+      <c r="L298" t="n">
+        <v>12.04</v>
+      </c>
       <c r="M298" t="inlineStr"/>
       <c r="N298" t="inlineStr"/>
       <c r="O298" t="inlineStr"/>
@@ -16170,8 +16254,12 @@
       <c r="J299" t="n">
         <v>0.2</v>
       </c>
-      <c r="K299" t="inlineStr"/>
-      <c r="L299" t="inlineStr"/>
+      <c r="K299" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="L299" t="n">
+        <v>-2.96</v>
+      </c>
       <c r="M299" t="inlineStr"/>
       <c r="N299" t="inlineStr"/>
       <c r="O299" t="inlineStr"/>
@@ -16220,8 +16308,12 @@
       <c r="J300" t="n">
         <v>0.82</v>
       </c>
-      <c r="K300" t="inlineStr"/>
-      <c r="L300" t="inlineStr"/>
+      <c r="K300" t="n">
+        <v>2015</v>
+      </c>
+      <c r="L300" t="n">
+        <v>-6.93</v>
+      </c>
       <c r="M300" t="inlineStr"/>
       <c r="N300" t="inlineStr"/>
       <c r="O300" t="inlineStr"/>
@@ -16270,8 +16362,12 @@
       <c r="J301" t="n">
         <v>0.75</v>
       </c>
-      <c r="K301" t="inlineStr"/>
-      <c r="L301" t="inlineStr"/>
+      <c r="K301" t="n">
+        <v>1385</v>
+      </c>
+      <c r="L301" t="n">
+        <v>37.13</v>
+      </c>
       <c r="M301" t="inlineStr"/>
       <c r="N301" t="inlineStr"/>
       <c r="O301" t="inlineStr"/>
@@ -16320,8 +16416,12 @@
       <c r="J302" t="n">
         <v>0.36</v>
       </c>
-      <c r="K302" t="inlineStr"/>
-      <c r="L302" t="inlineStr"/>
+      <c r="K302" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="L302" t="n">
+        <v>-1.99</v>
+      </c>
       <c r="M302" t="inlineStr"/>
       <c r="N302" t="inlineStr"/>
       <c r="O302" t="inlineStr"/>
@@ -16370,8 +16470,12 @@
       <c r="J303" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="K303" t="inlineStr"/>
-      <c r="L303" t="inlineStr"/>
+      <c r="K303" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="L303" t="n">
+        <v>-19.19</v>
+      </c>
       <c r="M303" t="inlineStr"/>
       <c r="N303" t="inlineStr"/>
       <c r="O303" t="inlineStr"/>
@@ -16420,8 +16524,12 @@
       <c r="J304" t="n">
         <v>0.71</v>
       </c>
-      <c r="K304" t="inlineStr"/>
-      <c r="L304" t="inlineStr"/>
+      <c r="K304" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L304" t="n">
+        <v>-6.17</v>
+      </c>
       <c r="M304" t="inlineStr"/>
       <c r="N304" t="inlineStr"/>
       <c r="O304" t="inlineStr"/>
@@ -16470,8 +16578,12 @@
       <c r="J305" t="n">
         <v>0.49</v>
       </c>
-      <c r="K305" t="inlineStr"/>
-      <c r="L305" t="inlineStr"/>
+      <c r="K305" t="n">
+        <v>342</v>
+      </c>
+      <c r="L305" t="n">
+        <v>9.09</v>
+      </c>
       <c r="M305" t="inlineStr"/>
       <c r="N305" t="inlineStr"/>
       <c r="O305" t="inlineStr"/>
@@ -16520,8 +16632,12 @@
       <c r="J306" t="n">
         <v>0.31</v>
       </c>
-      <c r="K306" t="inlineStr"/>
-      <c r="L306" t="inlineStr"/>
+      <c r="K306" t="n">
+        <v>189</v>
+      </c>
+      <c r="L306" t="n">
+        <v>-2.07</v>
+      </c>
       <c r="M306" t="inlineStr"/>
       <c r="N306" t="inlineStr"/>
       <c r="O306" t="inlineStr"/>
@@ -16570,8 +16686,12 @@
       <c r="J307" t="n">
         <v>0.36</v>
       </c>
-      <c r="K307" t="inlineStr"/>
-      <c r="L307" t="inlineStr"/>
+      <c r="K307" t="n">
+        <v>1395</v>
+      </c>
+      <c r="L307" t="n">
+        <v>-0.36</v>
+      </c>
       <c r="M307" t="inlineStr"/>
       <c r="N307" t="inlineStr"/>
       <c r="O307" t="inlineStr"/>
@@ -16616,8 +16736,12 @@
       </c>
       <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr"/>
-      <c r="K308" t="inlineStr"/>
-      <c r="L308" t="inlineStr"/>
+      <c r="K308" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="L308" t="n">
+        <v>-1.4</v>
+      </c>
       <c r="M308" t="inlineStr"/>
       <c r="N308" t="inlineStr"/>
       <c r="O308" t="inlineStr"/>
@@ -16662,8 +16786,12 @@
       </c>
       <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr"/>
-      <c r="K309" t="inlineStr"/>
-      <c r="L309" t="inlineStr"/>
+      <c r="K309" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="L309" t="n">
+        <v>0.85</v>
+      </c>
       <c r="M309" t="inlineStr"/>
       <c r="N309" t="inlineStr"/>
       <c r="O309" t="inlineStr"/>
@@ -16708,8 +16836,12 @@
       </c>
       <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr"/>
-      <c r="K310" t="inlineStr"/>
-      <c r="L310" t="inlineStr"/>
+      <c r="K310" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="L310" t="n">
+        <v>5.42</v>
+      </c>
       <c r="M310" t="inlineStr"/>
       <c r="N310" t="inlineStr"/>
       <c r="O310" t="inlineStr"/>
@@ -16754,8 +16886,12 @@
       </c>
       <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr"/>
-      <c r="K311" t="inlineStr"/>
-      <c r="L311" t="inlineStr"/>
+      <c r="K311" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="L311" t="n">
+        <v>-7.64</v>
+      </c>
       <c r="M311" t="inlineStr"/>
       <c r="N311" t="inlineStr"/>
       <c r="O311" t="inlineStr"/>
@@ -22632,7 +22768,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -22641,16 +22777,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>131</v>
+        <v>1010</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -22663,19 +22799,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I6" t="n">
-        <v>14.1</v>
+        <v>21.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="K6" t="n">
-        <v>179.5</v>
+        <v>1385</v>
       </c>
       <c r="L6" t="n">
-        <v>37.02</v>
+        <v>37.13</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -22684,7 +22820,7 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>37.02</v>
+        <v>37.13</v>
       </c>
     </row>
     <row r="7">
@@ -22698,16 +22834,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>369</v>
+        <v>131</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -22723,16 +22859,16 @@
         <v>90</v>
       </c>
       <c r="I7" t="n">
-        <v>21.2</v>
+        <v>14.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="K7" t="n">
-        <v>496.5</v>
+        <v>179.5</v>
       </c>
       <c r="L7" t="n">
-        <v>34.55</v>
+        <v>37.02</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -22741,12 +22877,12 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>34.55</v>
+        <v>37.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46210</v>
+        <v>46234</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -22755,37 +22891,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185.5</v>
+        <v>369</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>69</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="I8" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.92</v>
+      </c>
       <c r="K8" t="n">
-        <v>247</v>
+        <v>496.5</v>
       </c>
       <c r="L8" t="n">
-        <v>33.15</v>
+        <v>34.55</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -22794,12 +22934,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>33.15</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -22808,41 +22948,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>145.5</v>
+        <v>185.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>62</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.31</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>193.5</v>
+        <v>247</v>
       </c>
       <c r="L9" t="n">
-        <v>32.99</v>
+        <v>33.15</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -22851,12 +22987,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>32.99</v>
+        <v>33.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -22865,16 +23001,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5115</v>
+        <v>145.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -22883,23 +23019,23 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="K10" t="n">
-        <v>6620</v>
+        <v>193.5</v>
       </c>
       <c r="L10" t="n">
-        <v>29.42</v>
+        <v>32.99</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -22908,12 +23044,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>29.42</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -22922,20 +23058,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>181.5</v>
+        <v>5115</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -22944,15 +23080,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>69</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.26</v>
+      </c>
       <c r="K11" t="n">
-        <v>233</v>
+        <v>6620</v>
       </c>
       <c r="L11" t="n">
-        <v>28.37</v>
+        <v>29.42</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -22961,12 +23101,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>28.37</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -22975,20 +23115,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5050</v>
+        <v>181.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -22997,19 +23137,15 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>65</v>
-      </c>
-      <c r="I12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.26</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>6265</v>
+        <v>233</v>
       </c>
       <c r="L12" t="n">
-        <v>24.06</v>
+        <v>28.37</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -23018,12 +23154,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>24.06</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46210</v>
+        <v>46244</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -23032,16 +23168,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>155.5</v>
+        <v>401.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -23050,23 +23186,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>21.2</v>
       </c>
       <c r="J13" t="n">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
       <c r="K13" t="n">
-        <v>189.5</v>
+        <v>509</v>
       </c>
       <c r="L13" t="n">
-        <v>21.86</v>
+        <v>26.77</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -23075,12 +23211,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>21.86</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -23089,16 +23225,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2450</v>
+        <v>5050</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -23107,23 +23243,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I14" t="n">
-        <v>24.6</v>
+        <v>9.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0.66</v>
+        <v>0.26</v>
       </c>
       <c r="K14" t="n">
-        <v>2940</v>
+        <v>6265</v>
       </c>
       <c r="L14" t="n">
-        <v>20</v>
+        <v>24.06</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -23132,12 +23268,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46226</v>
+        <v>46244</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -23155,7 +23291,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2440</v>
+        <v>2765</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -23177,10 +23313,10 @@
         <v>0.66</v>
       </c>
       <c r="K15" t="n">
-        <v>2855</v>
+        <v>3380</v>
       </c>
       <c r="L15" t="n">
-        <v>17.01</v>
+        <v>22.24</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -23189,12 +23325,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>17.01</v>
+        <v>22.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46234</v>
+        <v>46210</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -23203,16 +23339,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>291.5</v>
+        <v>155.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -23221,23 +23357,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I16" t="n">
-        <v>13.2</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>0.49</v>
+        <v>0.31</v>
       </c>
       <c r="K16" t="n">
-        <v>338.5</v>
+        <v>189.5</v>
       </c>
       <c r="L16" t="n">
-        <v>16.12</v>
+        <v>21.86</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -23246,12 +23382,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>16.12</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -23260,37 +23396,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>193.5</v>
+        <v>2450</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>69</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I17" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.66</v>
+      </c>
       <c r="K17" t="n">
-        <v>222.5</v>
+        <v>2940</v>
       </c>
       <c r="L17" t="n">
-        <v>14.99</v>
+        <v>20</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -23299,12 +23439,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>14.99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -23313,16 +23453,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>426</v>
+        <v>2440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -23335,19 +23475,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>21.2</v>
+        <v>24.6</v>
       </c>
       <c r="J18" t="n">
-        <v>0.92</v>
+        <v>0.66</v>
       </c>
       <c r="K18" t="n">
-        <v>488</v>
+        <v>2855</v>
       </c>
       <c r="L18" t="n">
-        <v>14.55</v>
+        <v>17.01</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -23356,12 +23496,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>14.55</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -23370,20 +23510,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>61.1</v>
+        <v>291.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -23392,19 +23532,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I19" t="n">
-        <v>21.3</v>
+        <v>13.2</v>
       </c>
       <c r="J19" t="n">
-        <v>1.35</v>
+        <v>0.49</v>
       </c>
       <c r="K19" t="n">
-        <v>69.90000000000001</v>
+        <v>338.5</v>
       </c>
       <c r="L19" t="n">
-        <v>14.4</v>
+        <v>16.12</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -23413,12 +23553,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>14.4</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46234</v>
+        <v>46202</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -23427,41 +23567,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105</v>
+        <v>193.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>94</v>
-      </c>
-      <c r="I20" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.64</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>118.5</v>
+        <v>222.5</v>
       </c>
       <c r="L20" t="n">
-        <v>12.86</v>
+        <v>14.99</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -23470,7 +23606,7 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>12.86</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="21">
@@ -23484,16 +23620,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>896</v>
+        <v>426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -23506,19 +23642,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I21" t="n">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="K21" t="n">
-        <v>1010</v>
+        <v>488</v>
       </c>
       <c r="L21" t="n">
-        <v>12.72</v>
+        <v>14.55</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -23527,7 +23663,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>12.72</v>
+        <v>14.55</v>
       </c>
     </row>
   </sheetData>
@@ -24099,7 +24235,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46202</v>
+        <v>46244</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -24108,16 +24244,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>34.2</v>
+        <v>66.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -24126,23 +24262,23 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>27.65</v>
+        <v>53.9</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.15</v>
+        <v>-19.19</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -24151,12 +24287,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-19.15</v>
+        <v>-19.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -24165,16 +24301,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>373</v>
+        <v>34.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -24183,23 +24319,23 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="I11" t="n">
-        <v>13.2</v>
+        <v>5.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="K11" t="n">
-        <v>302</v>
+        <v>27.65</v>
       </c>
       <c r="L11" t="n">
-        <v>-19.03</v>
+        <v>-19.15</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -24208,7 +24344,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-19.03</v>
+        <v>-19.15</v>
       </c>
     </row>
     <row r="12">
@@ -24222,16 +24358,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>34.15</v>
+        <v>373</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -24240,23 +24376,23 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="I12" t="n">
-        <v>5.9</v>
+        <v>13.2</v>
       </c>
       <c r="J12" t="n">
-        <v>0.42</v>
+        <v>0.49</v>
       </c>
       <c r="K12" t="n">
-        <v>27.75</v>
+        <v>302</v>
       </c>
       <c r="L12" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -24265,7 +24401,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
     </row>
     <row r="13">
@@ -24327,7 +24463,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -24336,16 +24472,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2340</v>
+        <v>34.15</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -24358,19 +24494,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I14" t="n">
-        <v>30.7</v>
+        <v>5.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0.82</v>
+        <v>0.42</v>
       </c>
       <c r="K14" t="n">
-        <v>1910</v>
+        <v>27.75</v>
       </c>
       <c r="L14" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -24379,12 +24515,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46226</v>
+        <v>46202</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -24393,16 +24529,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1180</v>
+        <v>2340</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -24415,19 +24551,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>30.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
       <c r="K15" t="n">
-        <v>967</v>
+        <v>1910</v>
       </c>
       <c r="L15" t="n">
-        <v>-18.05</v>
+        <v>-18.38</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -24436,7 +24572,7 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-18.05</v>
+        <v>-18.38</v>
       </c>
     </row>
     <row r="16">
@@ -24450,16 +24586,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>72.59999999999999</v>
+        <v>1180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -24468,23 +24604,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I16" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="K16" t="n">
-        <v>59.6</v>
+        <v>967</v>
       </c>
       <c r="L16" t="n">
-        <v>-17.91</v>
+        <v>-18.05</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -24493,12 +24629,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-17.91</v>
+        <v>-18.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -24516,7 +24652,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -24538,10 +24674,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>60.4</v>
+        <v>59.6</v>
       </c>
       <c r="L17" t="n">
-        <v>-16.69</v>
+        <v>-17.91</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -24550,12 +24686,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-16.69</v>
+        <v>-17.91</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46210</v>
+        <v>46234</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -24564,16 +24700,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>475.5</v>
+        <v>72.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -24582,23 +24718,23 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I18" t="n">
-        <v>21.2</v>
+        <v>6.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>397.5</v>
+        <v>60.4</v>
       </c>
       <c r="L18" t="n">
-        <v>-16.4</v>
+        <v>-16.69</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -24607,12 +24743,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-16.4</v>
+        <v>-16.69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -24621,16 +24757,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>72.7</v>
+        <v>475.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -24639,23 +24775,23 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
-        <v>6.8</v>
+        <v>21.2</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="K19" t="n">
-        <v>61</v>
+        <v>397.5</v>
       </c>
       <c r="L19" t="n">
-        <v>-16.09</v>
+        <v>-16.4</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -24664,12 +24800,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-16.09</v>
+        <v>-16.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46226</v>
+        <v>46218</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -24678,20 +24814,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>143</v>
+        <v>72.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -24700,19 +24836,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I20" t="n">
-        <v>16.4</v>
+        <v>6.8</v>
       </c>
       <c r="J20" t="n">
-        <v>1.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="L20" t="n">
-        <v>-16.08</v>
+        <v>-16.09</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -24721,12 +24857,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-16.08</v>
+        <v>-16.09</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46202</v>
+        <v>46226</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -24735,20 +24871,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>367</v>
+        <v>143</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -24757,19 +24893,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="I21" t="n">
-        <v>13.2</v>
+        <v>16.4</v>
       </c>
       <c r="J21" t="n">
-        <v>0.49</v>
+        <v>1.11</v>
       </c>
       <c r="K21" t="n">
-        <v>309.5</v>
+        <v>120</v>
       </c>
       <c r="L21" t="n">
-        <v>-15.67</v>
+        <v>-16.08</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -24778,7 +24914,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-15.67</v>
+        <v>-16.08</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R423"/>
+  <dimension ref="A1:R424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22426,6 +22426,52 @@
       <c r="P423" t="inlineStr"/>
       <c r="Q423" t="inlineStr"/>
       <c r="R423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>信立</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H424" t="n">
+        <v>75</v>
+      </c>
+      <c r="I424" t="inlineStr"/>
+      <c r="J424" t="inlineStr"/>
+      <c r="K424" t="inlineStr"/>
+      <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr"/>
+      <c r="N424" t="inlineStr"/>
+      <c r="O424" t="inlineStr"/>
+      <c r="P424" t="inlineStr"/>
+      <c r="Q424" t="inlineStr"/>
+      <c r="R424" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R424"/>
+  <dimension ref="A1:R430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22472,6 +22472,306 @@
       <c r="P424" t="inlineStr"/>
       <c r="Q424" t="inlineStr"/>
       <c r="R424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H425" t="n">
+        <v>97</v>
+      </c>
+      <c r="I425" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J425" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K425" t="inlineStr"/>
+      <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr"/>
+      <c r="N425" t="inlineStr"/>
+      <c r="O425" t="inlineStr"/>
+      <c r="P425" t="inlineStr"/>
+      <c r="Q425" t="inlineStr"/>
+      <c r="R425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>120</v>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H426" t="n">
+        <v>91</v>
+      </c>
+      <c r="I426" t="n">
+        <v>15</v>
+      </c>
+      <c r="J426" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr"/>
+      <c r="N426" t="inlineStr"/>
+      <c r="O426" t="inlineStr"/>
+      <c r="P426" t="inlineStr"/>
+      <c r="Q426" t="inlineStr"/>
+      <c r="R426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H427" t="n">
+        <v>97</v>
+      </c>
+      <c r="I427" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J427" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr"/>
+      <c r="N427" t="inlineStr"/>
+      <c r="O427" t="inlineStr"/>
+      <c r="P427" t="inlineStr"/>
+      <c r="Q427" t="inlineStr"/>
+      <c r="R427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H428" t="n">
+        <v>94</v>
+      </c>
+      <c r="I428" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J428" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr"/>
+      <c r="N428" t="inlineStr"/>
+      <c r="O428" t="inlineStr"/>
+      <c r="P428" t="inlineStr"/>
+      <c r="Q428" t="inlineStr"/>
+      <c r="R428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H429" t="n">
+        <v>94</v>
+      </c>
+      <c r="I429" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J429" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K429" t="inlineStr"/>
+      <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr"/>
+      <c r="N429" t="inlineStr"/>
+      <c r="O429" t="inlineStr"/>
+      <c r="P429" t="inlineStr"/>
+      <c r="Q429" t="inlineStr"/>
+      <c r="R429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>53</v>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H430" t="n">
+        <v>78</v>
+      </c>
+      <c r="I430" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J430" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K430" t="inlineStr"/>
+      <c r="L430" t="inlineStr"/>
+      <c r="M430" t="inlineStr"/>
+      <c r="N430" t="inlineStr"/>
+      <c r="O430" t="inlineStr"/>
+      <c r="P430" t="inlineStr"/>
+      <c r="Q430" t="inlineStr"/>
+      <c r="R430" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
